--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduumb-my.sharepoint.com/personal/meselu_tegenie_mellaku_nmbu_no/Documents/Documents/GitHub/MANU2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{695CB326-1C9F-4FDF-8009-B92C838E177A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{237C71FA-D898-449B-A9EC-EF7403480433}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFE134E-9BA5-4A4B-8671-84DB74AF8E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EBF TJ" sheetId="144" r:id="rId1"/>
@@ -1558,7 +1558,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="267">
   <si>
     <t>CommName</t>
   </si>
@@ -2235,9 +2235,6 @@
     <t>%</t>
   </si>
   <si>
-    <t>Annual</t>
-  </si>
-  <si>
     <t>NCAP_BND</t>
   </si>
   <si>
@@ -2253,9 +2250,6 @@
     <t>MANHEAT</t>
   </si>
   <si>
-    <t>HEAT</t>
-  </si>
-  <si>
     <t>START</t>
   </si>
   <si>
@@ -2341,36 +2335,6 @@
   </si>
   <si>
     <t>ktCO₂/GWh</t>
-  </si>
-  <si>
-    <r>
-      <t>Share-I~UP</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~2050</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Share-I~UP</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~2022</t>
-    </r>
   </si>
   <si>
     <r>
@@ -2475,10 +2439,58 @@
     <t>Variable O&amp;M Cost</t>
   </si>
   <si>
-    <t>2024THUSD/GWh</t>
-  </si>
-  <si>
     <t>2024THUSD/MW</t>
+  </si>
+  <si>
+    <t>Peak</t>
+  </si>
+  <si>
+    <t>% contribution</t>
+  </si>
+  <si>
+    <t>MANCOALMIN</t>
+  </si>
+  <si>
+    <t>MANCOALIMP</t>
+  </si>
+  <si>
+    <t>MANOILIMP</t>
+  </si>
+  <si>
+    <r>
+      <t>Share-I~LO</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~2050</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Share-I~FX</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~2022</t>
+    </r>
+  </si>
+  <si>
+    <t>MANELC_TECH</t>
+  </si>
+  <si>
+    <t>2024THUSD/MWh</t>
   </si>
 </sst>
 </file>
@@ -3485,9 +3497,9 @@
     <cellStyle name="Normal 8 2" xfId="28" xr:uid="{C94D68A9-0F9F-49C7-A496-97D6E4CFF1B0}"/>
     <cellStyle name="Normal 9 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
     <cellStyle name="Normale_B2020" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Per cent" xfId="16" builtinId="5"/>
     <cellStyle name="Per cent 2" xfId="24" xr:uid="{2C564A4B-D800-4EE4-B939-9255D7A664BB}"/>
     <cellStyle name="Per cent 3" xfId="36" xr:uid="{030604DF-87E3-428A-B61C-D3C093606D31}"/>
-    <cellStyle name="Percent" xfId="16" builtinId="5"/>
     <cellStyle name="Percent 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
     <cellStyle name="Percent 3" xfId="18" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
     <cellStyle name="Percent 3 2" xfId="29" xr:uid="{E6B199C5-EFD9-4EA1-A159-C95FD8F6F260}"/>
@@ -4332,31 +4344,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A40EA534-E44A-461C-9315-2313911B2BEB}">
   <dimension ref="B1:R67"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" customWidth="1"/>
-    <col min="5" max="8" width="15.42578125" customWidth="1"/>
-    <col min="9" max="10" width="13.28515625" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="8" width="15.44140625" customWidth="1"/>
+    <col min="9" max="10" width="13.33203125" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" customWidth="1"/>
+    <col min="12" max="12" width="10.88671875" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="O1" s="12"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D2" s="27" t="s">
         <v>44</v>
       </c>
@@ -4380,7 +4392,7 @@
       </c>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C3" s="4"/>
       <c r="D3" s="28" t="s">
         <v>155</v>
@@ -4407,7 +4419,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C4" s="57" t="s">
         <v>49</v>
       </c>
@@ -4419,7 +4431,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="2:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B5" s="29" t="s">
         <v>50</v>
       </c>
@@ -4454,7 +4466,7 @@
       </c>
       <c r="O5" s="5"/>
     </row>
-    <row r="6" spans="2:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B6" s="29" t="s">
         <v>52</v>
       </c>
@@ -4479,7 +4491,7 @@
         <v>225037.94899999999</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B7" s="29" t="s">
         <v>116</v>
       </c>
@@ -4497,7 +4509,7 @@
       </c>
       <c r="K7" s="26"/>
     </row>
-    <row r="8" spans="2:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B8" s="53" t="s">
         <v>110</v>
       </c>
@@ -4537,7 +4549,7 @@
         <v>2102286.7409999999</v>
       </c>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="23"/>
       <c r="C9" s="59" t="s">
         <v>54</v>
@@ -4551,7 +4563,7 @@
       <c r="J9" s="4"/>
       <c r="K9" s="39"/>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="29" t="s">
         <v>55</v>
       </c>
@@ -4572,7 +4584,7 @@
         <v>-209</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="29" t="s">
         <v>46</v>
       </c>
@@ -4605,7 +4617,7 @@
         <v>6292.8000000000102</v>
       </c>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="29" t="s">
         <v>58</v>
       </c>
@@ -4634,7 +4646,7 @@
         <v>-1977483.48</v>
       </c>
     </row>
-    <row r="13" spans="2:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B13" s="23"/>
       <c r="C13" s="38" t="s">
         <v>59</v>
@@ -4672,7 +4684,7 @@
         <v>-1971399.6799999999</v>
       </c>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="23"/>
       <c r="C14" s="59" t="s">
         <v>60</v>
@@ -4686,7 +4698,7 @@
       <c r="J14" s="4"/>
       <c r="K14" s="39"/>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="29" t="s">
         <v>61</v>
       </c>
@@ -4711,7 +4723,7 @@
         <v>1415286.2489999998</v>
       </c>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="29" t="s">
         <v>63</v>
       </c>
@@ -4736,7 +4748,7 @@
         <v>27360.052000000003</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="29" t="s">
         <v>65</v>
       </c>
@@ -4755,7 +4767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="29" t="s">
         <v>121</v>
       </c>
@@ -4780,7 +4792,7 @@
         <v>47314.468500000003</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="29" t="s">
         <v>123</v>
       </c>
@@ -4803,7 +4815,7 @@
         <v>32155.458499999997</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="29" t="s">
         <v>67</v>
       </c>
@@ -4824,7 +4836,7 @@
         <v>7289.8130000000001</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="29" t="s">
         <v>68</v>
       </c>
@@ -4849,7 +4861,7 @@
         <v>100932.34299999999</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="29" t="s">
         <v>70</v>
       </c>
@@ -4870,7 +4882,7 @@
         <v>7289.8130000000001</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="29" t="s">
         <v>83</v>
       </c>
@@ -4891,7 +4903,7 @@
         <v>4304.424</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="29" t="s">
         <v>84</v>
       </c>
@@ -4912,7 +4924,7 @@
         <v>45897</v>
       </c>
     </row>
-    <row r="25" spans="2:11" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B25" s="53" t="s">
         <v>86</v>
       </c>
@@ -4943,7 +4955,7 @@
         <v>1687829.6209999998</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -4953,67 +4965,67 @@
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
     </row>
-    <row r="49" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J49" s="109"/>
       <c r="K49" s="112"/>
     </row>
-    <row r="50" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J50" s="109"/>
       <c r="K50" s="112"/>
     </row>
-    <row r="51" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J51" s="109"/>
       <c r="K51" s="112"/>
     </row>
-    <row r="52" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J52" s="109"/>
       <c r="K52" s="112"/>
     </row>
-    <row r="53" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J53" s="109"/>
       <c r="K53" s="112"/>
     </row>
-    <row r="54" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J54" s="109"/>
       <c r="K54" s="112"/>
     </row>
-    <row r="55" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J55" s="109"/>
       <c r="K55" s="112"/>
     </row>
-    <row r="56" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J56" s="109"/>
       <c r="K56" s="112"/>
     </row>
-    <row r="57" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J57" s="109"/>
       <c r="K57" s="112"/>
     </row>
-    <row r="58" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J58" s="109"/>
       <c r="K58" s="112"/>
     </row>
-    <row r="59" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J59" s="109"/>
       <c r="K59" s="112"/>
     </row>
-    <row r="60" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J60" s="109"/>
       <c r="K60" s="112"/>
     </row>
-    <row r="61" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J61" s="109"/>
       <c r="K61" s="112"/>
     </row>
-    <row r="62" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J62" s="109"/>
       <c r="K62" s="112"/>
     </row>
-    <row r="63" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J63" s="109"/>
       <c r="K63" s="112"/>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C65" s="78" t="s">
         <v>134</v>
       </c>
@@ -5024,7 +5036,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B66" s="12" t="s">
         <v>133</v>
       </c>
@@ -5038,7 +5050,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B67" s="29" t="s">
         <v>121</v>
       </c>
@@ -5056,27 +5068,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:Q55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" customWidth="1"/>
-    <col min="5" max="6" width="15.42578125" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" style="153" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" customWidth="1"/>
-    <col min="9" max="10" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="6" width="15.44140625" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" style="153" customWidth="1"/>
+    <col min="8" max="8" width="15.44140625" customWidth="1"/>
+    <col min="9" max="10" width="13.33203125" customWidth="1"/>
     <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="45.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="45.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N1" s="12" t="s">
         <v>90</v>
       </c>
@@ -5090,7 +5102,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D2" s="27" t="s">
         <v>44</v>
       </c>
@@ -5114,7 +5126,7 @@
       </c>
       <c r="K2" s="20"/>
       <c r="O2" s="24" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="P2" s="7" t="s">
         <v>148</v>
@@ -5123,7 +5135,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
       <c r="C3" s="4"/>
       <c r="D3" s="28" t="s">
         <v>155</v>
@@ -5150,7 +5162,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
       <c r="C4" s="57" t="s">
         <v>49</v>
       </c>
@@ -5162,7 +5174,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="29" t="s">
         <v>50</v>
       </c>
@@ -5203,7 +5215,7 @@
       </c>
       <c r="N5" s="5"/>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" s="29" t="s">
         <v>52</v>
       </c>
@@ -5243,7 +5255,7 @@
         <v>62510.546389732197</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="29" t="s">
         <v>116</v>
       </c>
@@ -5280,7 +5292,7 @@
       </c>
       <c r="K7" s="26"/>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="53" t="s">
         <v>110</v>
       </c>
@@ -5320,7 +5332,7 @@
         <v>583968.58588414988</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="23"/>
       <c r="C9" s="59" t="s">
         <v>54</v>
@@ -5334,7 +5346,7 @@
       <c r="J9" s="4"/>
       <c r="K9" s="39"/>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="29" t="s">
         <v>55</v>
       </c>
@@ -5353,7 +5365,7 @@
       </c>
       <c r="K10" s="31"/>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="29" t="s">
         <v>46</v>
       </c>
@@ -5375,7 +5387,7 @@
       <c r="J11" s="119"/>
       <c r="K11" s="119"/>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="29" t="s">
         <v>58</v>
       </c>
@@ -5415,7 +5427,7 @@
         <v>-549301.01061074401</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="23"/>
       <c r="C13" s="38" t="s">
         <v>59</v>
@@ -5441,7 +5453,7 @@
         <v>-549301.01061074401</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="23"/>
       <c r="C14" s="59" t="s">
         <v>60</v>
@@ -5455,7 +5467,7 @@
       <c r="J14" s="4"/>
       <c r="K14" s="39"/>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="29" t="s">
         <v>61</v>
       </c>
@@ -5495,7 +5507,7 @@
         <v>393135.1006174722</v>
       </c>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B16" s="29" t="s">
         <v>63</v>
       </c>
@@ -5535,7 +5547,7 @@
         <v>7600.0150524456003</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="29" t="s">
         <v>65</v>
       </c>
@@ -5575,7 +5587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:12" s="134" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" s="134" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="130" t="s">
         <v>121</v>
       </c>
@@ -5615,7 +5627,7 @@
         <v>13142.9089680993</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="29" t="s">
         <v>123</v>
       </c>
@@ -5655,7 +5667,7 @@
         <v>8932.0725201213008</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="29" t="s">
         <v>67</v>
       </c>
@@ -5695,7 +5707,7 @@
         <v>2024.9482175514001</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="29" t="s">
         <v>68</v>
       </c>
@@ -5735,7 +5747,7 @@
         <v>28036.764187385401</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="29" t="s">
         <v>70</v>
       </c>
@@ -5775,7 +5787,7 @@
         <v>2024.9482175514001</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="29" t="s">
         <v>83</v>
       </c>
@@ -5815,7 +5827,7 @@
         <v>1195.6734289872002</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="29" t="s">
         <v>84</v>
       </c>
@@ -5855,7 +5867,7 @@
         <v>12749.167686600002</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="53" t="s">
         <v>86</v>
       </c>
@@ -5886,7 +5898,7 @@
         <v>468841.59889621375</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -5896,7 +5908,7 @@
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -5907,7 +5919,7 @@
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C28" s="35"/>
       <c r="D28" s="35"/>
       <c r="E28" s="5"/>
@@ -5919,7 +5931,7 @@
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
@@ -5930,7 +5942,7 @@
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
@@ -5941,7 +5953,7 @@
       <c r="K30" s="5"/>
       <c r="L30" s="5"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
@@ -5952,7 +5964,7 @@
       <c r="K31" s="5"/>
       <c r="L31" s="5"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
@@ -5963,7 +5975,7 @@
       <c r="K32" s="5"/>
       <c r="L32" s="5"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
@@ -5974,7 +5986,7 @@
       <c r="K33" s="5"/>
       <c r="L33" s="5"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
@@ -5985,7 +5997,7 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
@@ -5996,7 +6008,7 @@
       <c r="K35" s="5"/>
       <c r="L35" s="5"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
@@ -6007,7 +6019,7 @@
       <c r="K36" s="5"/>
       <c r="L36" s="5"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C37" t="s">
         <v>146</v>
       </c>
@@ -6025,7 +6037,7 @@
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C38" s="14" t="s">
         <v>94</v>
       </c>
@@ -6042,7 +6054,7 @@
       <c r="K38" s="18"/>
       <c r="L38" s="18"/>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C39" s="16" t="s">
         <v>95</v>
       </c>
@@ -6059,7 +6071,7 @@
       <c r="K39" s="18"/>
       <c r="L39" s="18"/>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C40" s="1" t="s">
         <v>147</v>
       </c>
@@ -6075,7 +6087,7 @@
       <c r="G40" s="171"/>
       <c r="H40" s="5"/>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D44" s="27" t="s">
         <v>44</v>
       </c>
@@ -6098,7 +6110,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>132</v>
       </c>
@@ -6130,12 +6142,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>121</v>
       </c>
       <c r="C46" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D46" s="109">
         <f>D18/(D18+E18)</f>
@@ -6151,12 +6163,12 @@
         <v>DM1: Cement heat</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>121</v>
       </c>
       <c r="C47" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E47" s="109">
         <f>E18/(D18+E18)</f>
@@ -6172,12 +6184,12 @@
         <v>DM2: Non-cement process heat</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>121</v>
       </c>
       <c r="C48" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="J48" s="109">
         <v>1</v>
@@ -6191,19 +6203,19 @@
         <v>DM3 : Machine dive, lighting, cooling , refrigration etc</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
       <c r="J49" s="109"/>
       <c r="K49" s="112"/>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
       <c r="J50" s="109"/>
       <c r="K50" s="112"/>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
       <c r="J51" s="109"/>
       <c r="K51" s="112"/>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C53" s="78" t="s">
         <v>134</v>
       </c>
@@ -6214,7 +6226,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B54" s="12" t="s">
         <v>133</v>
       </c>
@@ -6228,7 +6240,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B55" s="29" t="s">
         <v>121</v>
       </c>
@@ -6248,32 +6260,32 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52FD602B-9017-48E8-B4D5-63841A58EBF0}">
   <dimension ref="A1:X44"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.85546875" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" style="158" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.88671875" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" style="158" customWidth="1"/>
     <col min="12" max="12" width="2" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.140625" customWidth="1"/>
-    <col min="15" max="15" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="45.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.140625" customWidth="1"/>
-    <col min="18" max="18" width="11.5703125" customWidth="1"/>
-    <col min="19" max="19" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.109375" customWidth="1"/>
+    <col min="15" max="15" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="45.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.109375" customWidth="1"/>
+    <col min="18" max="18" width="11.5546875" customWidth="1"/>
+    <col min="19" max="19" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B1" s="19" t="s">
         <v>75</v>
       </c>
@@ -6291,7 +6303,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="7"/>
       <c r="C2" s="7" t="str">
         <f>EBF!D2</f>
@@ -6320,7 +6332,7 @@
       <c r="T2" s="64"/>
       <c r="U2" s="64"/>
     </row>
-    <row r="3" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>45</v>
       </c>
@@ -6362,7 +6374,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:21" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C4" s="137" t="s">
         <v>199</v>
       </c>
@@ -6404,7 +6416,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C5" s="138"/>
       <c r="D5" s="138"/>
       <c r="E5" s="77"/>
@@ -6430,7 +6442,7 @@
       <c r="T5" s="64"/>
       <c r="U5" s="64"/>
     </row>
-    <row r="6" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C6" s="138"/>
       <c r="D6" s="138"/>
       <c r="E6" s="77"/>
@@ -6456,7 +6468,7 @@
       <c r="T6" s="64"/>
       <c r="U6" s="64"/>
     </row>
-    <row r="7" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C7" s="138"/>
       <c r="D7" s="138"/>
       <c r="E7" s="77"/>
@@ -6482,7 +6494,7 @@
       <c r="T7" s="64"/>
       <c r="U7" s="64"/>
     </row>
-    <row r="8" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C8" s="138"/>
       <c r="D8" s="138"/>
       <c r="E8" s="77"/>
@@ -6508,7 +6520,7 @@
       <c r="T8" s="64"/>
       <c r="U8" s="64"/>
     </row>
-    <row r="9" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C9" s="138"/>
       <c r="D9" s="138"/>
       <c r="E9" s="77"/>
@@ -6524,7 +6536,7 @@
       <c r="T9" s="64"/>
       <c r="U9" s="64"/>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
       <c r="M10" s="139"/>
       <c r="N10" s="139"/>
       <c r="O10" s="139"/>
@@ -6535,7 +6547,7 @@
       <c r="T10" s="64"/>
       <c r="U10" s="64"/>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
       <c r="M11" s="139"/>
       <c r="N11" s="139"/>
       <c r="O11" s="139"/>
@@ -6546,7 +6558,7 @@
       <c r="T11" s="64"/>
       <c r="U11" s="64"/>
     </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
       <c r="M12" s="136"/>
       <c r="N12" s="68"/>
       <c r="O12" s="136"/>
@@ -6557,7 +6569,7 @@
       <c r="T12" s="64"/>
       <c r="U12" s="64"/>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
       <c r="M13" s="136"/>
       <c r="N13" s="68"/>
       <c r="O13" s="136"/>
@@ -6568,7 +6580,7 @@
       <c r="T13" s="64"/>
       <c r="U13" s="64"/>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="M14" s="136"/>
       <c r="N14" s="68"/>
       <c r="O14" s="136"/>
@@ -6579,7 +6591,7 @@
       <c r="T14" s="64"/>
       <c r="U14" s="64"/>
     </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
       <c r="M15" s="150"/>
       <c r="N15" s="150"/>
       <c r="O15" s="150"/>
@@ -6590,7 +6602,7 @@
       <c r="T15" s="64"/>
       <c r="U15" s="64"/>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
       <c r="M16" s="150"/>
       <c r="N16" s="150"/>
       <c r="O16" s="150"/>
@@ -6601,7 +6613,7 @@
       <c r="T16" s="64"/>
       <c r="U16" s="64"/>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
       <c r="M17" s="136"/>
       <c r="N17" s="68"/>
       <c r="O17" s="136"/>
@@ -6612,7 +6624,7 @@
       <c r="T17" s="64"/>
       <c r="U17" s="64"/>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
       <c r="M18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
@@ -6622,7 +6634,7 @@
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
       <c r="F19" s="3" t="s">
         <v>13</v>
       </c>
@@ -6639,7 +6651,7 @@
       <c r="T19" s="68"/>
       <c r="U19" s="68"/>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>1</v>
       </c>
@@ -6696,7 +6708,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="2:21" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="9" t="s">
         <v>39</v>
       </c>
@@ -6749,7 +6761,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="2:21" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="9" t="s">
         <v>87</v>
       </c>
@@ -6762,7 +6774,7 @@
         <v>GWh</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="I22" s="8" t="str">
         <f>$E$2</f>
@@ -6782,7 +6794,7 @@
       <c r="T22" s="69"/>
       <c r="U22" s="69"/>
     </row>
-    <row r="23" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:21" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="64" t="str">
         <f>O23</f>
         <v>MINCOA</v>
@@ -6830,7 +6842,7 @@
       <c r="T23" s="68"/>
       <c r="U23" s="68"/>
     </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B24" s="64" t="str">
         <f t="shared" ref="B24:B25" si="0">O24</f>
         <v>IMPCOA</v>
@@ -6876,7 +6888,7 @@
       <c r="T24" s="68"/>
       <c r="U24" s="68"/>
     </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" s="64" t="str">
         <f t="shared" si="0"/>
         <v>IMPOIL</v>
@@ -6917,7 +6929,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B26" s="64" t="str">
         <f>O26</f>
         <v>ELCGRID</v>
@@ -6957,7 +6969,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B27" s="147"/>
       <c r="C27" s="147"/>
       <c r="D27" s="136"/>
@@ -6974,7 +6986,7 @@
       <c r="P27" s="140"/>
       <c r="Q27" s="138"/>
     </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B28" s="147"/>
       <c r="C28" s="147"/>
       <c r="D28" s="136"/>
@@ -6991,7 +7003,7 @@
       <c r="P28" s="149"/>
       <c r="Q28" s="146"/>
     </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B29" s="147"/>
       <c r="C29" s="147"/>
       <c r="D29" s="147"/>
@@ -7008,7 +7020,7 @@
       <c r="P29" s="149"/>
       <c r="Q29" s="146"/>
     </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B30" s="147"/>
       <c r="C30" s="147"/>
       <c r="D30" s="147"/>
@@ -7024,7 +7036,7 @@
       <c r="P30" s="149"/>
       <c r="Q30" s="146"/>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B31" s="147"/>
       <c r="C31" s="147"/>
       <c r="D31" s="147"/>
@@ -7040,7 +7052,7 @@
       <c r="P31" s="148"/>
       <c r="Q31" s="146"/>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B32" s="139"/>
       <c r="C32" s="139"/>
       <c r="D32" s="139"/>
@@ -7054,7 +7066,7 @@
       <c r="O32" s="68"/>
       <c r="P32" s="70"/>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B33" s="64"/>
       <c r="C33" s="68"/>
       <c r="D33" s="136"/>
@@ -7067,7 +7079,7 @@
       <c r="O33" s="68"/>
       <c r="P33" s="70"/>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B34" s="64"/>
       <c r="C34" s="68"/>
       <c r="D34" s="136"/>
@@ -7080,7 +7092,7 @@
       <c r="O34" s="68"/>
       <c r="P34" s="70"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B35" s="64"/>
       <c r="C35" s="68"/>
       <c r="D35" s="136"/>
@@ -7093,7 +7105,7 @@
       <c r="O35" s="68"/>
       <c r="P35" s="70"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B36" s="64"/>
       <c r="C36" s="68"/>
       <c r="D36" s="136"/>
@@ -7106,7 +7118,7 @@
       <c r="O36" s="68"/>
       <c r="P36" s="70"/>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B37" s="64"/>
       <c r="D37" s="64"/>
       <c r="E37" s="1"/>
@@ -7118,12 +7130,12 @@
       <c r="O37" s="68"/>
       <c r="P37" s="70"/>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H38" s="158"/>
       <c r="I38" s="158"/>
       <c r="J38" s="158"/>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B39" s="48"/>
       <c r="C39" s="1" t="s">
         <v>97</v>
@@ -7134,7 +7146,7 @@
       <c r="W39" s="150"/>
       <c r="X39" s="150"/>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B40" s="47"/>
       <c r="C40" s="1" t="s">
         <v>98</v>
@@ -7145,7 +7157,7 @@
       <c r="W40" s="150"/>
       <c r="X40" s="150"/>
     </row>
-    <row r="42" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="B42"/>
       <c r="C42"/>
@@ -7169,10 +7181,10 @@
       <c r="U42"/>
       <c r="V42"/>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="V43" s="1"/>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
     </row>
   </sheetData>
@@ -7187,35 +7199,35 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCAE1E4F-5A92-46AB-9A10-74ADD64337C0}">
   <dimension ref="B1:AF59"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="88" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="88" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.28515625" style="88" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" style="88" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="88" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.33203125" style="88" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" style="88" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="88" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" style="88" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" style="88" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="13.140625" style="88" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" style="88" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.44140625" style="88" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="13.109375" style="88" customWidth="1"/>
     <col min="13" max="13" width="12" style="88" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.85546875" style="88" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.140625" style="88" customWidth="1"/>
-    <col min="16" max="16" width="12.140625" style="88" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.88671875" style="88" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.109375" style="88" customWidth="1"/>
+    <col min="16" max="16" width="12.109375" style="88" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" style="88" bestFit="1" customWidth="1"/>
-    <col min="18" max="23" width="8.140625" style="88" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" style="88" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.140625" style="88" customWidth="1"/>
-    <col min="26" max="26" width="15.85546875" style="88" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="63.85546875" style="88" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.28515625" style="88" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.7109375" style="88" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="88" customWidth="1"/>
-    <col min="31" max="31" width="13.85546875" style="88" customWidth="1"/>
-    <col min="32" max="32" width="8.42578125" style="88" customWidth="1"/>
-    <col min="33" max="16384" width="8.85546875" style="88"/>
+    <col min="18" max="23" width="8.109375" style="88" customWidth="1"/>
+    <col min="24" max="24" width="12.6640625" style="88" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.109375" style="88" customWidth="1"/>
+    <col min="26" max="26" width="15.88671875" style="88" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="63.88671875" style="88" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.33203125" style="88" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.6640625" style="88" customWidth="1"/>
+    <col min="30" max="30" width="13.44140625" style="88" customWidth="1"/>
+    <col min="31" max="31" width="13.88671875" style="88" customWidth="1"/>
+    <col min="32" max="32" width="8.44140625" style="88" customWidth="1"/>
+    <col min="33" max="16384" width="8.88671875" style="88"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:32" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="6" t="s">
         <v>75</v>
       </c>
@@ -7242,7 +7254,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="2:32" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:32" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="str">
         <f>EBF!B18</f>
         <v>MAN</v>
@@ -7285,7 +7297,7 @@
       <c r="AE2" s="90"/>
       <c r="AF2" s="90"/>
     </row>
-    <row r="3" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:32" x14ac:dyDescent="0.25">
       <c r="X3" s="91" t="s">
         <v>7</v>
       </c>
@@ -7314,7 +7326,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:32" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:32" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
       <c r="D4" s="51"/>
@@ -7355,7 +7367,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="51"/>
       <c r="C5" s="51"/>
       <c r="D5" s="51"/>
@@ -7373,10 +7385,10 @@
       </c>
       <c r="Y5" s="142"/>
       <c r="Z5" s="142" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AA5" s="142" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AB5" s="90" t="s">
         <v>148</v>
@@ -7386,7 +7398,7 @@
       <c r="AE5" s="90"/>
       <c r="AF5" s="90"/>
     </row>
-    <row r="6" spans="2:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="51"/>
       <c r="C6" s="51"/>
       <c r="D6" s="51"/>
@@ -7417,7 +7429,7 @@
       <c r="AE6" s="90"/>
       <c r="AF6" s="90"/>
     </row>
-    <row r="7" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:32" x14ac:dyDescent="0.25">
       <c r="X7" s="90" t="s">
         <v>139</v>
       </c>
@@ -7439,16 +7451,16 @@
       <c r="AE7" s="90"/>
       <c r="AF7" s="90"/>
     </row>
-    <row r="8" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:32" x14ac:dyDescent="0.25">
       <c r="X8" s="142" t="s">
         <v>82</v>
       </c>
       <c r="Y8" s="142"/>
       <c r="Z8" s="142" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="AA8" s="142" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AB8" s="154" t="s">
         <v>148</v>
@@ -7458,7 +7470,7 @@
       <c r="AE8" s="90"/>
       <c r="AF8" s="90"/>
     </row>
-    <row r="9" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:32" x14ac:dyDescent="0.25">
       <c r="X9" s="142"/>
       <c r="Y9" s="142"/>
       <c r="Z9" s="142"/>
@@ -7469,7 +7481,7 @@
       <c r="AE9" s="90"/>
       <c r="AF9" s="90"/>
     </row>
-    <row r="10" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:32" x14ac:dyDescent="0.25">
       <c r="X10" s="165"/>
       <c r="Y10" s="165"/>
       <c r="Z10" s="165"/>
@@ -7480,7 +7492,7 @@
       <c r="AE10" s="90"/>
       <c r="AF10" s="90"/>
     </row>
-    <row r="11" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:32" x14ac:dyDescent="0.25">
       <c r="X11" s="154"/>
       <c r="Y11" s="90"/>
       <c r="Z11" s="154"/>
@@ -7491,7 +7503,7 @@
       <c r="AE11" s="90"/>
       <c r="AF11" s="90"/>
     </row>
-    <row r="12" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.25">
       <c r="X12" s="154"/>
       <c r="Y12" s="90"/>
       <c r="Z12" s="154"/>
@@ -7502,7 +7514,7 @@
       <c r="AE12" s="90"/>
       <c r="AF12" s="90"/>
     </row>
-    <row r="13" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:32" x14ac:dyDescent="0.25">
       <c r="X13" s="154"/>
       <c r="Y13" s="90"/>
       <c r="Z13" s="154"/>
@@ -7513,7 +7525,7 @@
       <c r="AE13" s="90"/>
       <c r="AF13" s="90"/>
     </row>
-    <row r="14" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:32" x14ac:dyDescent="0.25">
       <c r="X14" s="154"/>
       <c r="Y14" s="90"/>
       <c r="Z14" s="154"/>
@@ -7524,7 +7536,7 @@
       <c r="AE14" s="90"/>
       <c r="AF14" s="90"/>
     </row>
-    <row r="16" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:32" x14ac:dyDescent="0.25">
       <c r="D16" s="3" t="s">
         <v>13</v>
       </c>
@@ -7558,7 +7570,7 @@
       <c r="AE16" s="90"/>
       <c r="AF16" s="90"/>
     </row>
-    <row r="17" spans="2:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="52" t="s">
         <v>1</v>
       </c>
@@ -7569,28 +7581,28 @@
         <v>6</v>
       </c>
       <c r="E17" s="95" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F17" s="96" t="s">
+        <v>264</v>
+      </c>
+      <c r="G17" s="96" t="s">
+        <v>243</v>
+      </c>
+      <c r="H17" s="96" t="s">
+        <v>244</v>
+      </c>
+      <c r="I17" s="96" t="s">
+        <v>245</v>
+      </c>
+      <c r="J17" s="96" t="s">
         <v>246</v>
       </c>
-      <c r="G17" s="96" t="s">
+      <c r="K17" s="96" t="s">
         <v>247</v>
       </c>
-      <c r="H17" s="96" t="s">
-        <v>248</v>
-      </c>
-      <c r="I17" s="96" t="s">
-        <v>249</v>
-      </c>
-      <c r="J17" s="96" t="s">
-        <v>250</v>
-      </c>
-      <c r="K17" s="96" t="s">
-        <v>251</v>
-      </c>
       <c r="L17" s="96" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="M17" s="95" t="s">
         <v>102</v>
@@ -7602,7 +7614,7 @@
         <v>104</v>
       </c>
       <c r="P17" s="95" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q17" s="95" t="s">
         <v>156</v>
@@ -7611,15 +7623,17 @@
         <v>157</v>
       </c>
       <c r="S17" s="95" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="T17" s="95" t="s">
         <v>149</v>
       </c>
       <c r="U17" s="95" t="s">
-        <v>242</v>
-      </c>
-      <c r="V17" s="155"/>
+        <v>240</v>
+      </c>
+      <c r="V17" s="95" t="s">
+        <v>258</v>
+      </c>
       <c r="W17" s="155"/>
       <c r="X17" s="91" t="s">
         <v>11</v>
@@ -7649,7 +7663,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="2:32" ht="45.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:32" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="97" t="s">
         <v>39</v>
       </c>
@@ -7693,7 +7707,7 @@
         <v>113</v>
       </c>
       <c r="P18" s="97" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q18" s="97" t="s">
         <v>158</v>
@@ -7702,15 +7716,17 @@
         <v>159</v>
       </c>
       <c r="S18" s="98" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="T18" s="97" t="s">
         <v>150</v>
       </c>
       <c r="U18" s="97" t="s">
-        <v>243</v>
-      </c>
-      <c r="V18" s="156"/>
+        <v>241</v>
+      </c>
+      <c r="V18" s="97" t="s">
+        <v>259</v>
+      </c>
       <c r="W18" s="156"/>
       <c r="X18" s="93" t="s">
         <v>38</v>
@@ -7740,7 +7756,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="2:32" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:32" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="99" t="s">
         <v>87</v>
       </c>
@@ -7777,19 +7793,19 @@
       </c>
       <c r="P19" s="100"/>
       <c r="Q19" s="100" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="R19" s="100" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="S19" s="100" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="T19" s="100"/>
       <c r="U19" s="100" t="s">
-        <v>244</v>
-      </c>
-      <c r="V19" s="157"/>
+        <v>242</v>
+      </c>
+      <c r="V19" s="100"/>
       <c r="W19" s="157"/>
       <c r="X19" s="93" t="s">
         <v>81</v>
@@ -7803,7 +7819,7 @@
       <c r="AE19" s="93"/>
       <c r="AF19" s="93"/>
     </row>
-    <row r="20" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B20" s="88" t="str">
         <f>Z$20</f>
         <v>Kiln</v>
@@ -7827,7 +7843,7 @@
       <c r="K20" s="180"/>
       <c r="L20" s="180"/>
       <c r="M20" s="103">
-        <v>0.55000000000000004</v>
+        <v>0.55600000000000005</v>
       </c>
       <c r="N20" s="103">
         <v>1</v>
@@ -7849,10 +7865,10 @@
         <v>8.76</v>
       </c>
       <c r="U20" s="104"/>
-      <c r="V20" s="110"/>
+      <c r="V20" s="104"/>
       <c r="W20" s="110"/>
       <c r="X20" s="145" t="s">
-        <v>215</v>
+        <v>109</v>
       </c>
       <c r="Z20" s="88" t="s">
         <v>141</v>
@@ -7873,7 +7889,7 @@
       <c r="AE20" s="154"/>
       <c r="AF20" s="90"/>
     </row>
-    <row r="21" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B21" s="88" t="str">
         <f>Z$20</f>
         <v>Kiln</v>
@@ -7891,25 +7907,25 @@
         <v>0.41136476969163144</v>
       </c>
       <c r="G21" s="109">
-        <v>0.23585310113354352</v>
+        <v>0.25</v>
       </c>
       <c r="H21" s="109">
-        <v>7.3264515611810618E-2</v>
+        <v>0.25</v>
       </c>
       <c r="I21" s="109">
-        <v>1.9847450096360672E-2</v>
+        <v>0.25</v>
       </c>
       <c r="J21" s="109">
-        <v>5.1598550415568115E-3</v>
+        <v>0.25</v>
       </c>
       <c r="K21" s="109">
-        <v>1.3267245984926927E-3</v>
+        <v>0.25</v>
       </c>
       <c r="L21" s="109">
-        <v>3.4015961616990566E-4</v>
+        <v>0.25</v>
       </c>
       <c r="M21" s="103">
-        <v>0.55000000000000004</v>
+        <v>0.55600000000000005</v>
       </c>
       <c r="N21" s="103">
         <v>1</v>
@@ -7931,10 +7947,10 @@
         <v>8.76</v>
       </c>
       <c r="U21" s="104"/>
-      <c r="V21" s="110"/>
+      <c r="V21" s="104"/>
       <c r="W21" s="110"/>
       <c r="X21" s="145" t="s">
-        <v>215</v>
+        <v>109</v>
       </c>
       <c r="Z21" s="88" t="s">
         <v>143</v>
@@ -7955,7 +7971,7 @@
       <c r="AE21" s="154"/>
       <c r="AF21" s="90"/>
     </row>
-    <row r="22" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B22" s="88" t="str">
         <f>Z$21</f>
         <v>Boiler</v>
@@ -7972,24 +7988,12 @@
       <c r="F22" s="102">
         <v>1</v>
       </c>
-      <c r="G22" s="102">
-        <v>1</v>
-      </c>
-      <c r="H22" s="102">
-        <v>1</v>
-      </c>
-      <c r="I22" s="102">
-        <v>1</v>
-      </c>
-      <c r="J22" s="102">
-        <v>1</v>
-      </c>
-      <c r="K22" s="102">
-        <v>1</v>
-      </c>
-      <c r="L22" s="102">
-        <v>1</v>
-      </c>
+      <c r="G22" s="102"/>
+      <c r="H22" s="102"/>
+      <c r="I22" s="102"/>
+      <c r="J22" s="102"/>
+      <c r="K22" s="102"/>
+      <c r="L22" s="102"/>
       <c r="M22" s="103">
         <v>0.8</v>
       </c>
@@ -8013,13 +8017,13 @@
         <v>8.76</v>
       </c>
       <c r="U22" s="104"/>
-      <c r="V22" s="110"/>
+      <c r="V22" s="104"/>
       <c r="W22" s="110"/>
       <c r="X22" s="88" t="s">
         <v>109</v>
       </c>
       <c r="Z22" s="145" t="s">
-        <v>151</v>
+        <v>265</v>
       </c>
       <c r="AA22" s="88" t="s">
         <v>198</v>
@@ -8030,14 +8034,14 @@
       <c r="AC22" s="88" t="s">
         <v>142</v>
       </c>
-      <c r="AD22" s="151" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="23" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AD22" s="154" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="23" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="94" t="str">
         <f>Z22</f>
-        <v>MANELC</v>
+        <v>MANELC_TECH</v>
       </c>
       <c r="C23" s="94" t="str">
         <f>PRI_Sector_Fuels!O8</f>
@@ -8051,24 +8055,12 @@
       <c r="F23" s="144">
         <v>1</v>
       </c>
-      <c r="G23" s="144">
-        <v>1</v>
-      </c>
-      <c r="H23" s="144">
-        <v>1</v>
-      </c>
-      <c r="I23" s="144">
-        <v>1</v>
-      </c>
-      <c r="J23" s="144">
-        <v>1</v>
-      </c>
-      <c r="K23" s="144">
-        <v>1</v>
-      </c>
-      <c r="L23" s="144">
-        <v>1</v>
-      </c>
+      <c r="G23" s="144"/>
+      <c r="H23" s="144"/>
+      <c r="I23" s="144"/>
+      <c r="J23" s="144"/>
+      <c r="K23" s="144"/>
+      <c r="L23" s="144"/>
       <c r="M23" s="141">
         <v>1</v>
       </c>
@@ -8084,32 +8076,20 @@
         <v>8.76</v>
       </c>
       <c r="U23" s="104"/>
-      <c r="X23" s="141" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z23" s="141" t="s">
-        <v>252</v>
-      </c>
-      <c r="AA23" s="141" t="s">
-        <v>213</v>
-      </c>
-      <c r="AB23" s="88" t="s">
-        <v>148</v>
-      </c>
-      <c r="AC23" s="88" t="s">
-        <v>142</v>
-      </c>
-      <c r="AD23" s="151" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="24" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="V23" s="104">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="88"/>
+      <c r="AC23" s="88"/>
+      <c r="AD23" s="154"/>
+    </row>
+    <row r="24" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="94" t="s">
         <v>141</v>
       </c>
       <c r="C24" s="142"/>
       <c r="D24" s="154" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E24" s="143"/>
       <c r="F24" s="144"/>
@@ -8125,16 +8105,17 @@
       <c r="U24" s="104">
         <v>0.34100000000000003</v>
       </c>
+      <c r="V24" s="104"/>
       <c r="AB24" s="94"/>
       <c r="AC24" s="94"/>
     </row>
-    <row r="25" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="94" t="s">
         <v>143</v>
       </c>
       <c r="C25" s="142"/>
       <c r="D25" s="154" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E25" s="143"/>
       <c r="F25" s="144"/>
@@ -8150,10 +8131,11 @@
       <c r="U25" s="104">
         <v>0.25900000000000001</v>
       </c>
+      <c r="V25" s="104"/>
       <c r="AB25" s="94"/>
       <c r="AC25" s="94"/>
     </row>
-    <row r="26" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="94"/>
       <c r="C26" s="142"/>
       <c r="D26" s="154"/>
@@ -8172,7 +8154,7 @@
       <c r="AB26" s="94"/>
       <c r="AC26" s="94"/>
     </row>
-    <row r="27" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="94"/>
       <c r="C27" s="142"/>
       <c r="D27" s="154"/>
@@ -8191,15 +8173,15 @@
       <c r="AB27" s="94"/>
       <c r="AC27" s="94"/>
     </row>
-    <row r="28" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AB28" s="94"/>
       <c r="AC28" s="94"/>
       <c r="AD28" s="152"/>
     </row>
-    <row r="29" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AC29" s="94"/>
     </row>
-    <row r="30" spans="2:32" s="110" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:32" s="110" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="145"/>
       <c r="C30" s="90"/>
       <c r="D30" s="90"/>
@@ -8217,7 +8199,7 @@
       <c r="P30" s="141"/>
       <c r="Q30" s="141"/>
     </row>
-    <row r="31" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B31" s="145"/>
       <c r="C31" s="90"/>
       <c r="D31" s="90"/>
@@ -8235,7 +8217,7 @@
       <c r="P31" s="141"/>
       <c r="Q31" s="141"/>
     </row>
-    <row r="32" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B32" s="145"/>
       <c r="C32" s="90"/>
       <c r="D32" s="142"/>
@@ -8253,7 +8235,7 @@
       <c r="P32" s="141"/>
       <c r="Q32" s="141"/>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.25">
       <c r="E33" s="145"/>
       <c r="F33" s="106"/>
       <c r="G33" s="106"/>
@@ -8268,7 +8250,7 @@
       <c r="AC33" s="90"/>
       <c r="AD33" s="151"/>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.25">
       <c r="E34" s="145"/>
       <c r="F34" s="106"/>
       <c r="G34" s="106"/>
@@ -8284,7 +8266,7 @@
       <c r="AB34" s="111"/>
       <c r="AC34" s="111"/>
     </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:30" x14ac:dyDescent="0.25">
       <c r="E35" s="145"/>
       <c r="F35" s="106"/>
       <c r="G35" s="106"/>
@@ -8296,44 +8278,97 @@
       <c r="N35" s="107"/>
       <c r="Q35" s="164"/>
     </row>
-    <row r="36" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:30" x14ac:dyDescent="0.25">
       <c r="E36" s="145"/>
       <c r="N36" s="107"/>
       <c r="O36" s="106"/>
       <c r="Q36" s="164"/>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B37" s="104"/>
       <c r="C37" s="88" t="s">
         <v>97</v>
       </c>
       <c r="N37" s="107"/>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B38" s="108"/>
       <c r="C38" s="88" t="s">
         <v>98</v>
       </c>
       <c r="N38" s="107"/>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.25">
       <c r="N39" s="107"/>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.25">
       <c r="E42" s="21"/>
     </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B45" s="94"/>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B44" s="88" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="88" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="E44" s="88" t="s">
+        <v>105</v>
+      </c>
+      <c r="F44" s="88" t="s">
+        <v>140</v>
+      </c>
+      <c r="G44" s="88" t="s">
+        <v>140</v>
+      </c>
+      <c r="H44" s="88" t="s">
+        <v>140</v>
+      </c>
+      <c r="I44" s="88" t="s">
+        <v>140</v>
+      </c>
+      <c r="J44" s="88" t="s">
+        <v>140</v>
+      </c>
+      <c r="K44" s="88" t="s">
+        <v>140</v>
+      </c>
+      <c r="L44" s="88" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B45" s="94" t="s">
+        <v>87</v>
+      </c>
       <c r="C45" s="142"/>
       <c r="D45" s="90"/>
-      <c r="E45" s="143"/>
-      <c r="F45" s="144"/>
-      <c r="G45" s="144"/>
-      <c r="H45" s="144"/>
-      <c r="I45" s="144"/>
-      <c r="J45" s="144"/>
-      <c r="K45" s="144"/>
-      <c r="L45" s="144"/>
+      <c r="E45" s="143" t="s">
+        <v>192</v>
+      </c>
+      <c r="F45" s="144" t="s">
+        <v>208</v>
+      </c>
+      <c r="G45" s="144" t="s">
+        <v>208</v>
+      </c>
+      <c r="H45" s="144" t="s">
+        <v>208</v>
+      </c>
+      <c r="I45" s="144" t="s">
+        <v>208</v>
+      </c>
+      <c r="J45" s="144" t="s">
+        <v>208</v>
+      </c>
+      <c r="K45" s="144" t="s">
+        <v>208</v>
+      </c>
+      <c r="L45" s="144" t="s">
+        <v>208</v>
+      </c>
       <c r="M45" s="141"/>
       <c r="N45" s="141"/>
       <c r="O45" s="141"/>
@@ -8343,12 +8378,20 @@
       <c r="S45" s="141"/>
       <c r="T45" s="141"/>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B46" s="94"/>
-      <c r="C46" s="142"/>
-      <c r="D46" s="90"/>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B46" s="94" t="s">
+        <v>141</v>
+      </c>
+      <c r="C46" s="142" t="s">
+        <v>260</v>
+      </c>
+      <c r="D46" s="90" t="s">
+        <v>248</v>
+      </c>
       <c r="E46" s="143"/>
-      <c r="F46" s="144"/>
+      <c r="F46" s="144">
+        <v>0.59</v>
+      </c>
       <c r="G46" s="144"/>
       <c r="H46" s="144"/>
       <c r="I46" s="144"/>
@@ -8364,28 +8407,124 @@
       <c r="S46" s="141"/>
       <c r="T46" s="141"/>
     </row>
-    <row r="50" spans="6:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B47" s="88" t="s">
+        <v>141</v>
+      </c>
+      <c r="C47" s="88" t="s">
+        <v>261</v>
+      </c>
+      <c r="D47" s="88" t="s">
+        <v>248</v>
+      </c>
+      <c r="F47" s="88">
+        <v>0.41136476969163144</v>
+      </c>
+      <c r="G47" s="88">
+        <v>0.23585310113354352</v>
+      </c>
+      <c r="H47" s="88">
+        <v>7.3264515611810618E-2</v>
+      </c>
+      <c r="I47" s="88">
+        <v>1.9847450096360672E-2</v>
+      </c>
+      <c r="J47" s="88">
+        <v>5.1598550415568115E-3</v>
+      </c>
+      <c r="K47" s="88">
+        <v>1.3267245984926927E-3</v>
+      </c>
+      <c r="L47" s="88">
+        <v>3.4015961616990566E-4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B48" s="88" t="s">
+        <v>143</v>
+      </c>
+      <c r="C48" s="88" t="s">
+        <v>262</v>
+      </c>
+      <c r="D48" s="88" t="s">
+        <v>213</v>
+      </c>
+      <c r="F48" s="88">
+        <v>1</v>
+      </c>
+      <c r="G48" s="88">
+        <v>1</v>
+      </c>
+      <c r="H48" s="88">
+        <v>1</v>
+      </c>
+      <c r="I48" s="88">
+        <v>1</v>
+      </c>
+      <c r="J48" s="88">
+        <v>1</v>
+      </c>
+      <c r="K48" s="88">
+        <v>1</v>
+      </c>
+      <c r="L48" s="88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B49" s="88" t="s">
+        <v>151</v>
+      </c>
+      <c r="C49" s="88" t="s">
+        <v>46</v>
+      </c>
+      <c r="D49" s="88" t="s">
+        <v>151</v>
+      </c>
+      <c r="F49" s="88">
+        <v>1</v>
+      </c>
+      <c r="G49" s="88">
+        <v>1</v>
+      </c>
+      <c r="H49" s="88">
+        <v>1</v>
+      </c>
+      <c r="I49" s="88">
+        <v>1</v>
+      </c>
+      <c r="J49" s="88">
+        <v>1</v>
+      </c>
+      <c r="K49" s="88">
+        <v>1</v>
+      </c>
+      <c r="L49" s="88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H50" s="178"/>
       <c r="I50" s="179"/>
     </row>
-    <row r="53" spans="6:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
       <c r="G53" s="145"/>
       <c r="I53" s="145"/>
     </row>
-    <row r="54" spans="6:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
       <c r="G54" s="145"/>
     </row>
-    <row r="55" spans="6:9" s="94" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:12" s="94" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H55" s="143"/>
     </row>
-    <row r="56" spans="6:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
       <c r="F56" s="145"/>
       <c r="G56" s="145"/>
     </row>
-    <row r="58" spans="6:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
       <c r="F58" s="145"/>
     </row>
-    <row r="59" spans="6:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
       <c r="F59" s="145"/>
       <c r="H59" s="105"/>
     </row>
@@ -8401,27 +8540,27 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{148C1942-68EF-4347-B180-1E2F29F43F6F}">
   <dimension ref="B1:U59"/>
-  <sheetFormatPr defaultColWidth="25.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="25.6640625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.140625" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" customWidth="1"/>
     <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="7.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="7.5546875" customWidth="1"/>
     <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="7.5703125" customWidth="1"/>
+    <col min="14" max="14" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="7.5546875" customWidth="1"/>
     <col min="18" max="18" width="9" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="7.5703125" customWidth="1"/>
+    <col min="19" max="19" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="7.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="6" t="s">
         <v>75</v>
       </c>
@@ -8438,7 +8577,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
         <v>82</v>
       </c>
@@ -8453,14 +8592,14 @@
         <v>TH$2024</v>
       </c>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C5" s="115" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="115"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B6" s="114" t="s">
         <v>160</v>
       </c>
@@ -8486,7 +8625,7 @@
       </c>
       <c r="U6" s="1"/>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B7" s="117" t="s">
         <v>81</v>
       </c>
@@ -8536,7 +8675,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="8" spans="2:21" ht="34.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:21" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="116" t="s">
         <v>87</v>
       </c>
@@ -8570,12 +8709,12 @@
       <c r="T8" s="120"/>
       <c r="U8" s="120"/>
     </row>
-    <row r="9" spans="2:21" s="20" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:21" s="20" customFormat="1" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="175" t="s">
         <v>165</v>
       </c>
       <c r="C9" s="175" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D9" s="175" t="s">
         <v>148</v>
@@ -8611,7 +8750,7 @@
       </c>
       <c r="U9" s="9"/>
     </row>
-    <row r="10" spans="2:21" s="20" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:21" s="20" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="B10" s="175" t="s">
         <v>165</v>
       </c>
@@ -8635,7 +8774,7 @@
         <v>MANELC</v>
       </c>
       <c r="J10" s="145" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K10" s="185">
         <v>3.3566276423652626E-2</v>
@@ -8649,7 +8788,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O10" s="145" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="P10" s="185">
         <v>3.3566276423652626E-2</v>
@@ -8662,18 +8801,18 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T10" s="145" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="U10" s="185">
         <v>3.3566276423652626E-2</v>
       </c>
     </row>
-    <row r="11" spans="2:21" s="158" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:21" s="158" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="B11" s="175" t="s">
         <v>165</v>
       </c>
       <c r="C11" s="175" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D11" s="175" t="s">
         <v>148</v>
@@ -8692,7 +8831,7 @@
         <v>MANELC</v>
       </c>
       <c r="J11" s="176" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K11" s="185">
         <v>3.3302706089073604E-2</v>
@@ -8706,7 +8845,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O11" s="176" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="P11" s="185">
         <v>3.3302706089073604E-2</v>
@@ -8719,13 +8858,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T11" s="176" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="U11" s="185">
         <v>3.3302706089073604E-2</v>
       </c>
     </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B12" s="135"/>
       <c r="C12" s="135"/>
       <c r="D12" s="135"/>
@@ -8738,7 +8877,7 @@
         <v>MANELC</v>
       </c>
       <c r="J12" s="145" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K12" s="185">
         <v>3.3481814338032219E-2</v>
@@ -8752,7 +8891,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O12" s="145" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P12" s="185">
         <v>3.3481814338032219E-2</v>
@@ -8765,13 +8904,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T12" s="145" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="U12" s="185">
         <v>3.3481814338032219E-2</v>
       </c>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H13" s="1" t="s">
         <v>167</v>
       </c>
@@ -8780,7 +8919,7 @@
         <v>MANELC</v>
       </c>
       <c r="J13" s="176" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K13" s="185">
         <v>3.3611381763990082E-2</v>
@@ -8794,7 +8933,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O13" s="176" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="P13" s="185">
         <v>3.3611381763990082E-2</v>
@@ -8807,13 +8946,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T13" s="176" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="U13" s="185">
         <v>3.3611381763990082E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H14" s="1" t="s">
         <v>167</v>
       </c>
@@ -8822,7 +8961,7 @@
         <v>MANELC</v>
       </c>
       <c r="J14" s="145" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K14" s="185">
         <v>3.4004820718610197E-2</v>
@@ -8836,7 +8975,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O14" s="145" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="P14" s="185">
         <v>3.4004820718610197E-2</v>
@@ -8849,13 +8988,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T14" s="145" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="U14" s="185">
         <v>3.4004820718610197E-2</v>
       </c>
     </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H15" s="1" t="s">
         <v>167</v>
       </c>
@@ -8864,7 +9003,7 @@
         <v>MANELC</v>
       </c>
       <c r="J15" s="176" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K15" s="185">
         <v>3.4081384083392653E-2</v>
@@ -8878,7 +9017,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O15" s="176" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="P15" s="185">
         <v>3.4081384083392653E-2</v>
@@ -8891,13 +9030,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T15" s="176" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="U15" s="185">
         <v>3.4081384083392653E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H16" s="1" t="s">
         <v>167</v>
       </c>
@@ -8906,7 +9045,7 @@
         <v>MANELC</v>
       </c>
       <c r="J16" s="145" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K16" s="185">
         <v>3.3156795624830704E-2</v>
@@ -8920,7 +9059,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O16" s="145" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="P16" s="185">
         <v>3.3156795624830704E-2</v>
@@ -8933,13 +9072,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T16" s="145" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="U16" s="185">
         <v>3.3156795624830704E-2</v>
       </c>
     </row>
-    <row r="17" spans="4:21" x14ac:dyDescent="0.2">
+    <row r="17" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H17" t="s">
         <v>167</v>
       </c>
@@ -8948,7 +9087,7 @@
         <v>MANELC</v>
       </c>
       <c r="J17" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K17" s="185">
         <v>3.6518070997817571E-2</v>
@@ -8962,7 +9101,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O17" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P17" s="185">
         <v>3.6518070997817571E-2</v>
@@ -8975,13 +9114,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T17" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="U17" s="185">
         <v>3.6518070997817571E-2</v>
       </c>
     </row>
-    <row r="18" spans="4:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H18" s="1" t="s">
         <v>167</v>
       </c>
@@ -8990,7 +9129,7 @@
         <v>MANELC</v>
       </c>
       <c r="J18" s="145" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K18" s="185">
         <v>4.7257353018906531E-2</v>
@@ -9004,7 +9143,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O18" s="145" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="P18" s="185">
         <v>4.7257353018906531E-2</v>
@@ -9017,13 +9156,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T18" s="145" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="U18" s="185">
         <v>4.7257353018906531E-2</v>
       </c>
     </row>
-    <row r="19" spans="4:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H19" t="s">
         <v>167</v>
       </c>
@@ -9032,7 +9171,7 @@
         <v>MANELC</v>
       </c>
       <c r="J19" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="K19" s="185">
         <v>5.6756578785819259E-2</v>
@@ -9046,7 +9185,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O19" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P19" s="185">
         <v>5.6756578785819259E-2</v>
@@ -9059,13 +9198,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T19" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="U19" s="185">
         <v>5.6756578785819259E-2</v>
       </c>
     </row>
-    <row r="20" spans="4:21" x14ac:dyDescent="0.2">
+    <row r="20" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H20" t="s">
         <v>167</v>
       </c>
@@ -9074,7 +9213,7 @@
         <v>MANELC</v>
       </c>
       <c r="J20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K20" s="185">
         <v>5.5715023853427123E-2</v>
@@ -9088,7 +9227,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P20" s="185">
         <v>5.5715023853427123E-2</v>
@@ -9101,13 +9240,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="U20" s="185">
         <v>5.5715023853427123E-2</v>
       </c>
     </row>
-    <row r="21" spans="4:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H21" t="s">
         <v>167</v>
       </c>
@@ -9116,7 +9255,7 @@
         <v>MANELC</v>
       </c>
       <c r="J21" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K21" s="185">
         <v>5.6345483069498978E-2</v>
@@ -9130,7 +9269,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O21" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P21" s="185">
         <v>5.6345483069498978E-2</v>
@@ -9143,13 +9282,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T21" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="U21" s="185">
         <v>5.6345483069498978E-2</v>
       </c>
     </row>
-    <row r="22" spans="4:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H22" t="s">
         <v>167</v>
       </c>
@@ -9158,7 +9297,7 @@
         <v>MANELC</v>
       </c>
       <c r="J22" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K22" s="185">
         <v>4.8662133827205516E-2</v>
@@ -9172,7 +9311,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O22" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P22" s="185">
         <v>4.8662133827205516E-2</v>
@@ -9185,13 +9324,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T22" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="U22" s="185">
         <v>4.8662133827205516E-2</v>
       </c>
     </row>
-    <row r="23" spans="4:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H23" t="s">
         <v>167</v>
       </c>
@@ -9200,7 +9339,7 @@
         <v>MANELC</v>
       </c>
       <c r="J23" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K23" s="185">
         <v>5.0293526586567008E-2</v>
@@ -9214,7 +9353,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O23" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P23" s="185">
         <v>5.0293526586567008E-2</v>
@@ -9227,13 +9366,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T23" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="U23" s="185">
         <v>5.0293526586567008E-2</v>
       </c>
     </row>
-    <row r="24" spans="4:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H24" t="s">
         <v>167</v>
       </c>
@@ -9242,7 +9381,7 @@
         <v>MANELC</v>
       </c>
       <c r="J24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K24" s="185">
         <v>5.2523087098903048E-2</v>
@@ -9256,7 +9395,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="P24" s="185">
         <v>5.2523087098903048E-2</v>
@@ -9269,13 +9408,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="U24" s="185">
         <v>5.2523087098903048E-2</v>
       </c>
     </row>
-    <row r="25" spans="4:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H25" t="s">
         <v>167</v>
       </c>
@@ -9284,7 +9423,7 @@
         <v>MANELC</v>
       </c>
       <c r="J25" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K25" s="185">
         <v>5.4966761848993004E-2</v>
@@ -9298,7 +9437,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O25" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="P25" s="185">
         <v>5.4966761848993004E-2</v>
@@ -9311,13 +9450,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T25" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="U25" s="185">
         <v>5.4966761848993004E-2</v>
       </c>
     </row>
-    <row r="26" spans="4:21" x14ac:dyDescent="0.2">
+    <row r="26" spans="4:21" x14ac:dyDescent="0.25">
       <c r="D26" s="109"/>
       <c r="H26" t="s">
         <v>167</v>
@@ -9327,7 +9466,7 @@
         <v>MANELC</v>
       </c>
       <c r="J26" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K26" s="185">
         <v>5.3016988893511453E-2</v>
@@ -9341,7 +9480,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O26" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P26" s="185">
         <v>5.3016988893511453E-2</v>
@@ -9354,13 +9493,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T26" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="U26" s="185">
         <v>5.3016988893511453E-2</v>
       </c>
     </row>
-    <row r="27" spans="4:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="4:21" x14ac:dyDescent="0.25">
       <c r="D27" s="109"/>
       <c r="E27" s="5"/>
       <c r="H27" t="s">
@@ -9371,7 +9510,7 @@
         <v>MANELC</v>
       </c>
       <c r="J27" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="K27" s="185">
         <v>4.4273060594597062E-2</v>
@@ -9385,7 +9524,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O27" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P27" s="185">
         <v>4.4273060594597062E-2</v>
@@ -9398,13 +9537,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T27" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="U27" s="185">
         <v>4.4273060594597062E-2</v>
       </c>
     </row>
-    <row r="28" spans="4:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="4:21" x14ac:dyDescent="0.25">
       <c r="D28" s="109"/>
       <c r="E28" s="109"/>
       <c r="F28" s="109"/>
@@ -9416,7 +9555,7 @@
         <v>MANELC</v>
       </c>
       <c r="J28" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K28" s="185">
         <v>3.6258449498494133E-2</v>
@@ -9430,7 +9569,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O28" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="P28" s="185">
         <v>3.6258449498494133E-2</v>
@@ -9443,13 +9582,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T28" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="U28" s="185">
         <v>3.6258449498494133E-2</v>
       </c>
     </row>
-    <row r="29" spans="4:21" x14ac:dyDescent="0.2">
+    <row r="29" spans="4:21" x14ac:dyDescent="0.25">
       <c r="D29" s="109"/>
       <c r="E29" s="109"/>
       <c r="F29" s="109"/>
@@ -9461,7 +9600,7 @@
         <v>MANELC</v>
       </c>
       <c r="J29" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K29" s="185">
         <v>3.6040655779430726E-2</v>
@@ -9475,7 +9614,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O29" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P29" s="185">
         <v>3.6040655779430726E-2</v>
@@ -9488,13 +9627,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T29" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="U29" s="185">
         <v>3.6040655779430726E-2</v>
       </c>
     </row>
-    <row r="30" spans="4:21" x14ac:dyDescent="0.2">
+    <row r="30" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H30" s="1" t="s">
         <v>167</v>
       </c>
@@ -9503,7 +9642,7 @@
         <v>MANELC</v>
       </c>
       <c r="J30" s="145" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K30" s="185">
         <v>3.5097781406108856E-2</v>
@@ -9517,7 +9656,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O30" s="145" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="P30" s="185">
         <v>3.5097781406108856E-2</v>
@@ -9530,13 +9669,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T30" s="145" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="U30" s="185">
         <v>3.5097781406108856E-2</v>
       </c>
     </row>
-    <row r="31" spans="4:21" x14ac:dyDescent="0.2">
+    <row r="31" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H31" s="1" t="s">
         <v>167</v>
       </c>
@@ -9545,7 +9684,7 @@
         <v>MANELC</v>
       </c>
       <c r="J31" s="176" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="K31" s="185">
         <v>3.482493578674286E-2</v>
@@ -9559,7 +9698,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O31" s="176" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="P31" s="185">
         <v>3.482493578674286E-2</v>
@@ -9572,13 +9711,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T31" s="176" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="U31" s="185">
         <v>3.482493578674286E-2</v>
       </c>
     </row>
-    <row r="32" spans="4:21" x14ac:dyDescent="0.2">
+    <row r="32" spans="4:21" x14ac:dyDescent="0.25">
       <c r="E32" s="5"/>
       <c r="H32" s="1" t="s">
         <v>167</v>
@@ -9588,7 +9727,7 @@
         <v>MANELC</v>
       </c>
       <c r="J32" s="145" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K32" s="185">
         <v>3.2564766705734945E-2</v>
@@ -9602,7 +9741,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O32" s="145" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="P32" s="185">
         <v>3.2564766705734945E-2</v>
@@ -9615,13 +9754,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T32" s="145" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="U32" s="185">
         <v>3.2564766705734945E-2</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B33" s="1"/>
       <c r="E33" s="5"/>
       <c r="H33" s="1" t="s">
@@ -9632,7 +9771,7 @@
         <v>MANELC</v>
       </c>
       <c r="J33" s="176" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="K33" s="185">
         <v>3.3680163206659841E-2</v>
@@ -9646,7 +9785,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O33" s="176" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="P33" s="185">
         <v>3.3680163206659841E-2</v>
@@ -9659,13 +9798,13 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T33" s="176" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="U33" s="185">
         <v>3.3680163206659841E-2</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B34" s="1"/>
       <c r="H34" s="1" t="s">
         <v>167</v>
@@ -9707,7 +9846,7 @@
         <v>3.0835149280259575E-2</v>
       </c>
     </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H35" s="1" t="s">
         <v>167</v>
       </c>
@@ -9748,7 +9887,7 @@
         <v>3.1306102192535441E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B36" s="118"/>
       <c r="C36" s="1" t="s">
         <v>97</v>
@@ -9793,7 +9932,7 @@
         <v>3.0732055812390149E-2</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B37" s="47"/>
       <c r="C37" s="1" t="s">
         <v>98</v>
@@ -9838,7 +9977,7 @@
         <v>3.1026498894933252E-2</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H38" s="1" t="s">
         <v>167</v>
       </c>
@@ -9879,7 +10018,7 @@
         <v>3.1056840848101456E-2</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H39" s="1" t="s">
         <v>167</v>
       </c>
@@ -9920,7 +10059,7 @@
         <v>3.1761574865503496E-2</v>
       </c>
     </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H40" s="1" t="s">
         <v>167</v>
       </c>
@@ -9961,7 +10100,7 @@
         <v>3.2141299558210122E-2</v>
       </c>
     </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H41" s="1" t="s">
         <v>167</v>
       </c>
@@ -10002,7 +10141,7 @@
         <v>3.5213642686520726E-2</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H42" s="1" t="s">
         <v>167</v>
       </c>
@@ -10043,7 +10182,7 @@
         <v>5.1117433203485711E-2</v>
       </c>
     </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H43" s="1" t="s">
         <v>167</v>
       </c>
@@ -10084,7 +10223,7 @@
         <v>6.2773677380098022E-2</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H44" s="1" t="s">
         <v>167</v>
       </c>
@@ -10125,7 +10264,7 @@
         <v>6.1766758236552227E-2</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H45" s="1" t="s">
         <v>167</v>
       </c>
@@ -10166,7 +10305,7 @@
         <v>6.4177423190962854E-2</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H46" s="1" t="s">
         <v>167</v>
       </c>
@@ -10207,7 +10346,7 @@
         <v>5.0829723942040425E-2</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H47" s="1" t="s">
         <v>167</v>
       </c>
@@ -10248,7 +10387,7 @@
         <v>5.4268458827148723E-2</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H48" s="1" t="s">
         <v>167</v>
       </c>
@@ -10289,7 +10428,7 @@
         <v>5.9589636409466136E-2</v>
       </c>
     </row>
-    <row r="49" spans="8:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="8:21" x14ac:dyDescent="0.25">
       <c r="H49" s="1" t="s">
         <v>167</v>
       </c>
@@ -10330,7 +10469,7 @@
         <v>5.9904363990350699E-2</v>
       </c>
     </row>
-    <row r="50" spans="8:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="8:21" x14ac:dyDescent="0.25">
       <c r="H50" s="1" t="s">
         <v>167</v>
       </c>
@@ -10371,7 +10510,7 @@
         <v>5.4602121019645386E-2</v>
       </c>
     </row>
-    <row r="51" spans="8:21" x14ac:dyDescent="0.2">
+    <row r="51" spans="8:21" x14ac:dyDescent="0.25">
       <c r="H51" s="1" t="s">
         <v>167</v>
       </c>
@@ -10412,7 +10551,7 @@
         <v>4.095098396869809E-2</v>
       </c>
     </row>
-    <row r="52" spans="8:21" x14ac:dyDescent="0.2">
+    <row r="52" spans="8:21" x14ac:dyDescent="0.25">
       <c r="H52" s="1" t="s">
         <v>167</v>
       </c>
@@ -10453,7 +10592,7 @@
         <v>3.2728922255458537E-2</v>
       </c>
     </row>
-    <row r="53" spans="8:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="8:21" x14ac:dyDescent="0.25">
       <c r="H53" s="1" t="s">
         <v>167</v>
       </c>
@@ -10494,7 +10633,7 @@
         <v>3.1731181617130018E-2</v>
       </c>
     </row>
-    <row r="54" spans="8:21" x14ac:dyDescent="0.2">
+    <row r="54" spans="8:21" x14ac:dyDescent="0.25">
       <c r="H54" s="1" t="s">
         <v>167</v>
       </c>
@@ -10535,7 +10674,7 @@
         <v>3.0924439128636003E-2</v>
       </c>
     </row>
-    <row r="55" spans="8:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="8:21" x14ac:dyDescent="0.25">
       <c r="H55" s="1" t="s">
         <v>167</v>
       </c>
@@ -10576,7 +10715,7 @@
         <v>3.0529213441903326E-2</v>
       </c>
     </row>
-    <row r="56" spans="8:21" x14ac:dyDescent="0.2">
+    <row r="56" spans="8:21" x14ac:dyDescent="0.25">
       <c r="H56" s="1" t="s">
         <v>167</v>
       </c>
@@ -10617,7 +10756,7 @@
         <v>2.9792391830107463E-2</v>
       </c>
     </row>
-    <row r="57" spans="8:21" x14ac:dyDescent="0.2">
+    <row r="57" spans="8:21" x14ac:dyDescent="0.25">
       <c r="H57" s="1" t="s">
         <v>167</v>
       </c>
@@ -10658,13 +10797,13 @@
         <v>3.0240107419862172E-2</v>
       </c>
     </row>
-    <row r="58" spans="8:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="8:21" x14ac:dyDescent="0.25">
       <c r="H58" s="1"/>
       <c r="I58" s="137"/>
       <c r="J58" s="137"/>
       <c r="K58" s="181"/>
     </row>
-    <row r="59" spans="8:21" x14ac:dyDescent="0.2">
+    <row r="59" spans="8:21" x14ac:dyDescent="0.25">
       <c r="K59" s="137"/>
     </row>
   </sheetData>
@@ -10677,15 +10816,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08E959CB-7164-414F-B6F7-22B95D131062}">
   <dimension ref="B3:I25"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="122" t="s">
         <v>194</v>
       </c>
@@ -10696,7 +10835,7 @@
       <c r="G3" s="122"/>
       <c r="H3" s="122"/>
     </row>
-    <row r="4" spans="2:9" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="123"/>
       <c r="C4" s="123"/>
       <c r="D4" s="123"/>
@@ -10704,13 +10843,13 @@
       <c r="F4" s="123"/>
       <c r="G4" s="123"/>
     </row>
-    <row r="5" spans="2:9" ht="18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B5" s="124" t="s">
         <v>195</v>
       </c>
       <c r="C5" s="125"/>
     </row>
-    <row r="6" spans="2:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="126" t="s">
         <v>0</v>
       </c>
@@ -10734,7 +10873,7 @@
       <c r="H6" s="126"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="2:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="127" t="s">
         <v>87</v>
       </c>
@@ -10754,7 +10893,7 @@
       <c r="H7" s="127"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="177"/>
       <c r="C8" s="177"/>
       <c r="D8" s="177"/>
@@ -10764,7 +10903,7 @@
       <c r="H8" s="177"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" s="128" t="str">
         <f>DemTechs_INDF!Z7</f>
         <v>MANCO2</v>
@@ -10785,13 +10924,13 @@
       <c r="H9" s="129"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="118"/>
       <c r="C24" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="47"/>
       <c r="C25" s="1" t="s">
         <v>98</v>

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFE134E-9BA5-4A4B-8671-84DB74AF8E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD3293B-38F3-4184-AD11-7C0EF31032BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EBF TJ" sheetId="144" r:id="rId1"/>
@@ -1558,7 +1558,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="270">
   <si>
     <t>CommName</t>
   </si>
@@ -2491,6 +2491,15 @@
   </si>
   <si>
     <t>2024THUSD/MWh</t>
+  </si>
+  <si>
+    <t>GRIDELC</t>
+  </si>
+  <si>
+    <t>ELCAGG</t>
+  </si>
+  <si>
+    <t>Electricity aggrigator</t>
   </si>
 </sst>
 </file>
@@ -6505,7 +6514,7 @@
       </c>
       <c r="N8" s="68"/>
       <c r="O8" s="136" t="s">
-        <v>46</v>
+        <v>267</v>
       </c>
       <c r="P8" s="136" t="s">
         <v>207</v>
@@ -6936,8 +6945,8 @@
       </c>
       <c r="C26" s="68"/>
       <c r="D26" s="136" t="str">
-        <f>O$8</f>
-        <v>ELC</v>
+        <f>O8</f>
+        <v>GRIDELC</v>
       </c>
       <c r="E26" s="1">
         <v>2022</v>
@@ -7471,11 +7480,19 @@
       <c r="AF8" s="90"/>
     </row>
     <row r="9" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="X9" s="142"/>
+      <c r="X9" s="142" t="s">
+        <v>46</v>
+      </c>
       <c r="Y9" s="142"/>
-      <c r="Z9" s="142"/>
-      <c r="AA9" s="142"/>
-      <c r="AB9" s="154"/>
+      <c r="Z9" s="142" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA9" s="142" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB9" s="154" t="s">
+        <v>148</v>
+      </c>
       <c r="AC9" s="90"/>
       <c r="AD9" s="90"/>
       <c r="AE9" s="90"/>
@@ -8043,8 +8060,8 @@
         <f>Z22</f>
         <v>MANELC_TECH</v>
       </c>
-      <c r="C23" s="94" t="str">
-        <f>PRI_Sector_Fuels!O8</f>
+      <c r="C23" s="142" t="str">
+        <f>Z9</f>
         <v>ELC</v>
       </c>
       <c r="D23" s="90" t="str">
@@ -8070,8 +8087,8 @@
       <c r="O23" s="141">
         <v>50</v>
       </c>
-      <c r="R23" s="104"/>
-      <c r="S23" s="104"/>
+      <c r="R23" s="110"/>
+      <c r="S23" s="110"/>
       <c r="T23" s="104">
         <v>8.76</v>
       </c>
@@ -8079,9 +8096,24 @@
       <c r="V23" s="104">
         <v>1</v>
       </c>
-      <c r="AB23" s="88"/>
-      <c r="AC23" s="88"/>
-      <c r="AD23" s="154"/>
+      <c r="X23" s="141" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z23" s="141" t="s">
+        <v>268</v>
+      </c>
+      <c r="AA23" s="141" t="s">
+        <v>269</v>
+      </c>
+      <c r="AB23" s="88" t="s">
+        <v>148</v>
+      </c>
+      <c r="AC23" s="88" t="s">
+        <v>142</v>
+      </c>
+      <c r="AD23" s="154" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="24" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="94" t="s">
@@ -8099,8 +8131,8 @@
       <c r="J24" s="144"/>
       <c r="K24" s="144"/>
       <c r="L24" s="144"/>
-      <c r="R24" s="104"/>
-      <c r="S24" s="104"/>
+      <c r="R24" s="110"/>
+      <c r="S24" s="110"/>
       <c r="T24" s="104"/>
       <c r="U24" s="104">
         <v>0.34100000000000003</v>
@@ -8125,8 +8157,8 @@
       <c r="J25" s="144"/>
       <c r="K25" s="144"/>
       <c r="L25" s="144"/>
-      <c r="R25" s="104"/>
-      <c r="S25" s="104"/>
+      <c r="R25" s="110"/>
+      <c r="S25" s="110"/>
       <c r="T25" s="104"/>
       <c r="U25" s="104">
         <v>0.25900000000000001</v>
@@ -8136,9 +8168,18 @@
       <c r="AC25" s="94"/>
     </row>
     <row r="26" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="94"/>
-      <c r="C26" s="142"/>
-      <c r="D26" s="154"/>
+      <c r="B26" s="94" t="str">
+        <f>Z23</f>
+        <v>ELCAGG</v>
+      </c>
+      <c r="C26" s="142" t="str">
+        <f>PRI_Sector_Fuels!D26</f>
+        <v>GRIDELC</v>
+      </c>
+      <c r="D26" s="154" t="str">
+        <f>Z9</f>
+        <v>ELC</v>
+      </c>
       <c r="E26" s="143"/>
       <c r="F26" s="144"/>
       <c r="G26" s="144"/>
@@ -8147,9 +8188,27 @@
       <c r="J26" s="144"/>
       <c r="K26" s="144"/>
       <c r="L26" s="144"/>
-      <c r="R26" s="110"/>
-      <c r="S26" s="110"/>
-      <c r="T26" s="110"/>
+      <c r="M26" s="141">
+        <v>1</v>
+      </c>
+      <c r="N26" s="141">
+        <v>1</v>
+      </c>
+      <c r="O26" s="141">
+        <v>50</v>
+      </c>
+      <c r="Q26" s="141">
+        <v>0</v>
+      </c>
+      <c r="R26" s="110">
+        <v>0</v>
+      </c>
+      <c r="S26" s="110">
+        <v>0</v>
+      </c>
+      <c r="T26" s="110">
+        <v>8.76</v>
+      </c>
       <c r="U26" s="110"/>
       <c r="AB26" s="94"/>
       <c r="AC26" s="94"/>
@@ -10867,7 +10926,7 @@
       </c>
       <c r="F6" s="126" t="str">
         <f>PRI_Sector_Fuels!O8</f>
-        <v>ELC</v>
+        <v>GRIDELC</v>
       </c>
       <c r="G6" s="126"/>
       <c r="H6" s="126"/>

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD3293B-38F3-4184-AD11-7C0EF31032BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F05F217-14D4-4B8B-B467-3F66523363A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6941,7 +6941,7 @@
     <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B26" s="64" t="str">
         <f>O26</f>
-        <v>ELCGRID</v>
+        <v>GRID</v>
       </c>
       <c r="C26" s="68"/>
       <c r="D26" s="136" t="str">
@@ -6965,8 +6965,8 @@
       </c>
       <c r="N26" s="138"/>
       <c r="O26" s="68" t="str">
-        <f>$M$26&amp;$C$4</f>
-        <v>ELCGRID</v>
+        <f>$C$4</f>
+        <v>GRID</v>
       </c>
       <c r="P26" s="140" t="s">
         <v>200</v>

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F05F217-14D4-4B8B-B467-3F66523363A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC63FEAA-1CF5-41B3-AE3C-BE7B85BE63AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1558,7 +1558,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="269">
   <si>
     <t>CommName</t>
   </si>
@@ -2155,9 +2155,6 @@
   </si>
   <si>
     <t>Manufacturing  Electricity for machine drive and other services</t>
-  </si>
-  <si>
-    <t>GRID</t>
   </si>
   <si>
     <t>Grid electricity</t>
@@ -2229,9 +2226,6 @@
     <t>ktoe</t>
   </si>
   <si>
-    <t>Aggrigate electricity demand of manufacturing sector</t>
-  </si>
-  <si>
     <t>%</t>
   </si>
   <si>
@@ -2500,6 +2494,9 @@
   </si>
   <si>
     <t>Electricity aggrigator</t>
+  </si>
+  <si>
+    <t>Electricity from Grid</t>
   </si>
 </sst>
 </file>
@@ -5135,13 +5132,13 @@
       </c>
       <c r="K2" s="20"/>
       <c r="O2" s="24" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="P2" s="7" t="s">
         <v>148</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
@@ -6156,7 +6153,7 @@
         <v>121</v>
       </c>
       <c r="C46" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D46" s="109">
         <f>D18/(D18+E18)</f>
@@ -6177,7 +6174,7 @@
         <v>121</v>
       </c>
       <c r="C47" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E47" s="109">
         <f>E18/(D18+E18)</f>
@@ -6198,7 +6195,7 @@
         <v>121</v>
       </c>
       <c r="C48" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J48" s="109">
         <v>1</v>
@@ -6385,7 +6382,7 @@
     </row>
     <row r="4" spans="2:21" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C4" s="137" t="s">
-        <v>199</v>
+        <v>265</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>197</v>
@@ -6430,13 +6427,13 @@
       <c r="D5" s="138"/>
       <c r="E5" s="77"/>
       <c r="F5" s="138"/>
-      <c r="G5" s="7"/>
+      <c r="G5" s="77"/>
       <c r="M5" s="64" t="s">
         <v>74</v>
       </c>
       <c r="N5" s="68"/>
       <c r="O5" s="136" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P5" s="64" t="s">
         <v>152</v>
@@ -6446,7 +6443,7 @@
       </c>
       <c r="R5" s="64"/>
       <c r="S5" s="137" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T5" s="64"/>
       <c r="U5" s="64"/>
@@ -6456,13 +6453,13 @@
       <c r="D6" s="138"/>
       <c r="E6" s="77"/>
       <c r="F6" s="138"/>
-      <c r="G6" s="7"/>
+      <c r="G6" s="77"/>
       <c r="M6" s="64" t="s">
         <v>74</v>
       </c>
       <c r="N6" s="68"/>
       <c r="O6" s="136" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="P6" s="64" t="s">
         <v>153</v>
@@ -6472,7 +6469,7 @@
       </c>
       <c r="R6" s="64"/>
       <c r="S6" s="137" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T6" s="64"/>
       <c r="U6" s="64"/>
@@ -6482,13 +6479,13 @@
       <c r="D7" s="138"/>
       <c r="E7" s="77"/>
       <c r="F7" s="138"/>
-      <c r="G7" s="7"/>
+      <c r="G7" s="77"/>
       <c r="M7" s="64" t="s">
         <v>74</v>
       </c>
       <c r="N7" s="68"/>
       <c r="O7" s="136" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P7" s="64" t="s">
         <v>154</v>
@@ -6498,7 +6495,7 @@
       </c>
       <c r="R7" s="64"/>
       <c r="S7" s="137" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T7" s="64"/>
       <c r="U7" s="64"/>
@@ -6508,23 +6505,23 @@
       <c r="D8" s="138"/>
       <c r="E8" s="77"/>
       <c r="F8" s="138"/>
-      <c r="G8" s="7"/>
+      <c r="G8" s="77"/>
       <c r="M8" s="136" t="s">
         <v>46</v>
       </c>
       <c r="N8" s="68"/>
       <c r="O8" s="136" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="P8" s="136" t="s">
-        <v>207</v>
+        <v>268</v>
       </c>
       <c r="Q8" s="64" t="s">
         <v>148</v>
       </c>
       <c r="R8" s="64"/>
       <c r="S8" s="137" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T8" s="64"/>
       <c r="U8" s="64"/>
@@ -6534,7 +6531,7 @@
       <c r="D9" s="138"/>
       <c r="E9" s="77"/>
       <c r="F9" s="138"/>
-      <c r="G9" s="7"/>
+      <c r="G9" s="77"/>
       <c r="M9" s="139"/>
       <c r="N9" s="139"/>
       <c r="O9" s="139"/>
@@ -6783,7 +6780,7 @@
         <v>GWh</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I22" s="8" t="str">
         <f>$E$2</f>
@@ -6846,7 +6843,7 @@
       </c>
       <c r="R23" s="68"/>
       <c r="S23" s="137" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T23" s="68"/>
       <c r="U23" s="68"/>
@@ -6892,7 +6889,7 @@
       </c>
       <c r="R24" s="68"/>
       <c r="S24" s="137" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T24" s="68"/>
       <c r="U24" s="68"/>
@@ -6935,13 +6932,13 @@
         <v>148</v>
       </c>
       <c r="S25" s="137" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B26" s="64" t="str">
         <f>O26</f>
-        <v>GRID</v>
+        <v>GRIDELC</v>
       </c>
       <c r="C26" s="68"/>
       <c r="D26" s="136" t="str">
@@ -6966,16 +6963,16 @@
       <c r="N26" s="138"/>
       <c r="O26" s="68" t="str">
         <f>$C$4</f>
-        <v>GRID</v>
+        <v>GRIDELC</v>
       </c>
       <c r="P26" s="140" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q26" t="s">
         <v>148</v>
       </c>
       <c r="S26" s="137" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.25">
@@ -7394,10 +7391,10 @@
       </c>
       <c r="Y5" s="142"/>
       <c r="Z5" s="142" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AA5" s="142" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AB5" s="90" t="s">
         <v>148</v>
@@ -7428,7 +7425,7 @@
         <v>151</v>
       </c>
       <c r="AA6" s="90" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AB6" s="90" t="s">
         <v>148</v>
@@ -7466,10 +7463,10 @@
       </c>
       <c r="Y8" s="142"/>
       <c r="Z8" s="142" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AA8" s="142" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AB8" s="154" t="s">
         <v>148</v>
@@ -7598,28 +7595,28 @@
         <v>6</v>
       </c>
       <c r="E17" s="95" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F17" s="96" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G17" s="96" t="s">
+        <v>241</v>
+      </c>
+      <c r="H17" s="96" t="s">
+        <v>242</v>
+      </c>
+      <c r="I17" s="96" t="s">
         <v>243</v>
       </c>
-      <c r="H17" s="96" t="s">
+      <c r="J17" s="96" t="s">
         <v>244</v>
       </c>
-      <c r="I17" s="96" t="s">
+      <c r="K17" s="96" t="s">
         <v>245</v>
       </c>
-      <c r="J17" s="96" t="s">
-        <v>246</v>
-      </c>
-      <c r="K17" s="96" t="s">
-        <v>247</v>
-      </c>
       <c r="L17" s="96" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M17" s="95" t="s">
         <v>102</v>
@@ -7631,7 +7628,7 @@
         <v>104</v>
       </c>
       <c r="P17" s="95" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Q17" s="95" t="s">
         <v>156</v>
@@ -7640,16 +7637,16 @@
         <v>157</v>
       </c>
       <c r="S17" s="95" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="T17" s="95" t="s">
         <v>149</v>
       </c>
       <c r="U17" s="95" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="V17" s="95" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="W17" s="155"/>
       <c r="X17" s="91" t="s">
@@ -7724,7 +7721,7 @@
         <v>113</v>
       </c>
       <c r="P18" s="97" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Q18" s="97" t="s">
         <v>158</v>
@@ -7733,16 +7730,16 @@
         <v>159</v>
       </c>
       <c r="S18" s="98" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="T18" s="97" t="s">
         <v>150</v>
       </c>
       <c r="U18" s="97" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="V18" s="97" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="W18" s="156"/>
       <c r="X18" s="93" t="s">
@@ -7783,25 +7780,25 @@
         <v>192</v>
       </c>
       <c r="F19" s="100" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G19" s="100" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H19" s="100" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I19" s="100" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J19" s="100" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K19" s="100" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L19" s="100" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M19" s="100"/>
       <c r="N19" s="101"/>
@@ -7810,17 +7807,17 @@
       </c>
       <c r="P19" s="100"/>
       <c r="Q19" s="100" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="R19" s="100" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="S19" s="100" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="T19" s="100"/>
       <c r="U19" s="100" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="V19" s="100"/>
       <c r="W19" s="157"/>
@@ -7901,7 +7898,7 @@
         <v>142</v>
       </c>
       <c r="AD20" s="154" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AE20" s="154"/>
       <c r="AF20" s="90"/>
@@ -7983,7 +7980,7 @@
         <v>142</v>
       </c>
       <c r="AD21" s="154" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AE21" s="154"/>
       <c r="AF21" s="90"/>
@@ -8040,7 +8037,7 @@
         <v>109</v>
       </c>
       <c r="Z22" s="145" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AA22" s="88" t="s">
         <v>198</v>
@@ -8052,7 +8049,7 @@
         <v>142</v>
       </c>
       <c r="AD22" s="154" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
@@ -8100,10 +8097,10 @@
         <v>46</v>
       </c>
       <c r="Z23" s="141" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AA23" s="141" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AB23" s="88" t="s">
         <v>148</v>
@@ -8112,7 +8109,7 @@
         <v>142</v>
       </c>
       <c r="AD23" s="154" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
@@ -8121,7 +8118,7 @@
       </c>
       <c r="C24" s="142"/>
       <c r="D24" s="154" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E24" s="143"/>
       <c r="F24" s="144"/>
@@ -8147,7 +8144,7 @@
       </c>
       <c r="C25" s="142"/>
       <c r="D25" s="154" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E25" s="143"/>
       <c r="F25" s="144"/>
@@ -8408,25 +8405,25 @@
         <v>192</v>
       </c>
       <c r="F45" s="144" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G45" s="144" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H45" s="144" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I45" s="144" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J45" s="144" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K45" s="144" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L45" s="144" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M45" s="141"/>
       <c r="N45" s="141"/>
@@ -8442,10 +8439,10 @@
         <v>141</v>
       </c>
       <c r="C46" s="142" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D46" s="90" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E46" s="143"/>
       <c r="F46" s="144">
@@ -8471,10 +8468,10 @@
         <v>141</v>
       </c>
       <c r="C47" s="88" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D47" s="88" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F47" s="88">
         <v>0.41136476969163144</v>
@@ -8503,10 +8500,10 @@
         <v>143</v>
       </c>
       <c r="C48" s="88" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D48" s="88" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F48" s="88">
         <v>1</v>
@@ -8773,7 +8770,7 @@
         <v>165</v>
       </c>
       <c r="C9" s="175" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D9" s="175" t="s">
         <v>148</v>
@@ -8833,7 +8830,7 @@
         <v>MANELC</v>
       </c>
       <c r="J10" s="145" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K10" s="185">
         <v>3.3566276423652626E-2</v>
@@ -8847,7 +8844,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O10" s="145" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="P10" s="185">
         <v>3.3566276423652626E-2</v>
@@ -8860,7 +8857,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T10" s="145" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="U10" s="185">
         <v>3.3566276423652626E-2</v>
@@ -8871,7 +8868,7 @@
         <v>165</v>
       </c>
       <c r="C11" s="175" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D11" s="175" t="s">
         <v>148</v>
@@ -8890,7 +8887,7 @@
         <v>MANELC</v>
       </c>
       <c r="J11" s="176" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K11" s="185">
         <v>3.3302706089073604E-2</v>
@@ -8904,7 +8901,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O11" s="176" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="P11" s="185">
         <v>3.3302706089073604E-2</v>
@@ -8917,7 +8914,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T11" s="176" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="U11" s="185">
         <v>3.3302706089073604E-2</v>
@@ -8936,7 +8933,7 @@
         <v>MANELC</v>
       </c>
       <c r="J12" s="145" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K12" s="185">
         <v>3.3481814338032219E-2</v>
@@ -8950,7 +8947,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O12" s="145" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="P12" s="185">
         <v>3.3481814338032219E-2</v>
@@ -8963,7 +8960,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T12" s="145" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="U12" s="185">
         <v>3.3481814338032219E-2</v>
@@ -8978,7 +8975,7 @@
         <v>MANELC</v>
       </c>
       <c r="J13" s="176" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K13" s="185">
         <v>3.3611381763990082E-2</v>
@@ -8992,7 +8989,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O13" s="176" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="P13" s="185">
         <v>3.3611381763990082E-2</v>
@@ -9005,7 +9002,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T13" s="176" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="U13" s="185">
         <v>3.3611381763990082E-2</v>
@@ -9020,7 +9017,7 @@
         <v>MANELC</v>
       </c>
       <c r="J14" s="145" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K14" s="185">
         <v>3.4004820718610197E-2</v>
@@ -9034,7 +9031,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O14" s="145" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P14" s="185">
         <v>3.4004820718610197E-2</v>
@@ -9047,7 +9044,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T14" s="145" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="U14" s="185">
         <v>3.4004820718610197E-2</v>
@@ -9062,7 +9059,7 @@
         <v>MANELC</v>
       </c>
       <c r="J15" s="176" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K15" s="185">
         <v>3.4081384083392653E-2</v>
@@ -9076,7 +9073,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O15" s="176" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="P15" s="185">
         <v>3.4081384083392653E-2</v>
@@ -9089,7 +9086,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T15" s="176" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="U15" s="185">
         <v>3.4081384083392653E-2</v>
@@ -9104,7 +9101,7 @@
         <v>MANELC</v>
       </c>
       <c r="J16" s="145" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K16" s="185">
         <v>3.3156795624830704E-2</v>
@@ -9118,7 +9115,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O16" s="145" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="P16" s="185">
         <v>3.3156795624830704E-2</v>
@@ -9131,7 +9128,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T16" s="145" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="U16" s="185">
         <v>3.3156795624830704E-2</v>
@@ -9146,7 +9143,7 @@
         <v>MANELC</v>
       </c>
       <c r="J17" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K17" s="185">
         <v>3.6518070997817571E-2</v>
@@ -9160,7 +9157,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O17" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="P17" s="185">
         <v>3.6518070997817571E-2</v>
@@ -9173,7 +9170,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T17" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="U17" s="185">
         <v>3.6518070997817571E-2</v>
@@ -9188,7 +9185,7 @@
         <v>MANELC</v>
       </c>
       <c r="J18" s="145" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K18" s="185">
         <v>4.7257353018906531E-2</v>
@@ -9202,7 +9199,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O18" s="145" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="P18" s="185">
         <v>4.7257353018906531E-2</v>
@@ -9215,7 +9212,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T18" s="145" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="U18" s="185">
         <v>4.7257353018906531E-2</v>
@@ -9230,7 +9227,7 @@
         <v>MANELC</v>
       </c>
       <c r="J19" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K19" s="185">
         <v>5.6756578785819259E-2</v>
@@ -9244,7 +9241,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O19" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P19" s="185">
         <v>5.6756578785819259E-2</v>
@@ -9257,7 +9254,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T19" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="U19" s="185">
         <v>5.6756578785819259E-2</v>
@@ -9272,7 +9269,7 @@
         <v>MANELC</v>
       </c>
       <c r="J20" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K20" s="185">
         <v>5.5715023853427123E-2</v>
@@ -9286,7 +9283,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O20" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="P20" s="185">
         <v>5.5715023853427123E-2</v>
@@ -9299,7 +9296,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T20" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="U20" s="185">
         <v>5.5715023853427123E-2</v>
@@ -9314,7 +9311,7 @@
         <v>MANELC</v>
       </c>
       <c r="J21" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="K21" s="185">
         <v>5.6345483069498978E-2</v>
@@ -9328,7 +9325,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O21" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P21" s="185">
         <v>5.6345483069498978E-2</v>
@@ -9341,7 +9338,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T21" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="U21" s="185">
         <v>5.6345483069498978E-2</v>
@@ -9356,7 +9353,7 @@
         <v>MANELC</v>
       </c>
       <c r="J22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K22" s="185">
         <v>4.8662133827205516E-2</v>
@@ -9370,7 +9367,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P22" s="185">
         <v>4.8662133827205516E-2</v>
@@ -9383,7 +9380,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="U22" s="185">
         <v>4.8662133827205516E-2</v>
@@ -9398,7 +9395,7 @@
         <v>MANELC</v>
       </c>
       <c r="J23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K23" s="185">
         <v>5.0293526586567008E-2</v>
@@ -9412,7 +9409,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P23" s="185">
         <v>5.0293526586567008E-2</v>
@@ -9425,7 +9422,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="U23" s="185">
         <v>5.0293526586567008E-2</v>
@@ -9440,7 +9437,7 @@
         <v>MANELC</v>
       </c>
       <c r="J24" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K24" s="185">
         <v>5.2523087098903048E-2</v>
@@ -9454,7 +9451,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O24" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P24" s="185">
         <v>5.2523087098903048E-2</v>
@@ -9467,7 +9464,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T24" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="U24" s="185">
         <v>5.2523087098903048E-2</v>
@@ -9482,7 +9479,7 @@
         <v>MANELC</v>
       </c>
       <c r="J25" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K25" s="185">
         <v>5.4966761848993004E-2</v>
@@ -9496,7 +9493,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O25" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P25" s="185">
         <v>5.4966761848993004E-2</v>
@@ -9509,7 +9506,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T25" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="U25" s="185">
         <v>5.4966761848993004E-2</v>
@@ -9525,7 +9522,7 @@
         <v>MANELC</v>
       </c>
       <c r="J26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K26" s="185">
         <v>5.3016988893511453E-2</v>
@@ -9539,7 +9536,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="P26" s="185">
         <v>5.3016988893511453E-2</v>
@@ -9552,7 +9549,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="U26" s="185">
         <v>5.3016988893511453E-2</v>
@@ -9569,7 +9566,7 @@
         <v>MANELC</v>
       </c>
       <c r="J27" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K27" s="185">
         <v>4.4273060594597062E-2</v>
@@ -9583,7 +9580,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O27" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="P27" s="185">
         <v>4.4273060594597062E-2</v>
@@ -9596,7 +9593,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T27" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="U27" s="185">
         <v>4.4273060594597062E-2</v>
@@ -9614,7 +9611,7 @@
         <v>MANELC</v>
       </c>
       <c r="J28" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K28" s="185">
         <v>3.6258449498494133E-2</v>
@@ -9628,7 +9625,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O28" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P28" s="185">
         <v>3.6258449498494133E-2</v>
@@ -9641,7 +9638,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T28" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="U28" s="185">
         <v>3.6258449498494133E-2</v>
@@ -9659,7 +9656,7 @@
         <v>MANELC</v>
       </c>
       <c r="J29" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="K29" s="185">
         <v>3.6040655779430726E-2</v>
@@ -9673,7 +9670,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O29" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P29" s="185">
         <v>3.6040655779430726E-2</v>
@@ -9686,7 +9683,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T29" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="U29" s="185">
         <v>3.6040655779430726E-2</v>
@@ -9701,7 +9698,7 @@
         <v>MANELC</v>
       </c>
       <c r="J30" s="145" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K30" s="185">
         <v>3.5097781406108856E-2</v>
@@ -9715,7 +9712,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O30" s="145" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="P30" s="185">
         <v>3.5097781406108856E-2</v>
@@ -9728,7 +9725,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T30" s="145" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="U30" s="185">
         <v>3.5097781406108856E-2</v>
@@ -9743,7 +9740,7 @@
         <v>MANELC</v>
       </c>
       <c r="J31" s="176" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K31" s="185">
         <v>3.482493578674286E-2</v>
@@ -9757,7 +9754,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O31" s="176" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P31" s="185">
         <v>3.482493578674286E-2</v>
@@ -9770,7 +9767,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T31" s="176" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="U31" s="185">
         <v>3.482493578674286E-2</v>
@@ -9786,7 +9783,7 @@
         <v>MANELC</v>
       </c>
       <c r="J32" s="145" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K32" s="185">
         <v>3.2564766705734945E-2</v>
@@ -9800,7 +9797,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O32" s="145" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="P32" s="185">
         <v>3.2564766705734945E-2</v>
@@ -9813,7 +9810,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T32" s="145" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="U32" s="185">
         <v>3.2564766705734945E-2</v>
@@ -9830,7 +9827,7 @@
         <v>MANELC</v>
       </c>
       <c r="J33" s="176" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="K33" s="185">
         <v>3.3680163206659841E-2</v>
@@ -9844,7 +9841,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O33" s="176" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="P33" s="185">
         <v>3.3680163206659841E-2</v>
@@ -9857,7 +9854,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T33" s="176" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="U33" s="185">
         <v>3.3680163206659841E-2</v>

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC63FEAA-1CF5-41B3-AE3C-BE7B85BE63AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A26077-FC90-4FE8-9ED7-1CF2D4424F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1558,7 +1558,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="270">
   <si>
     <t>CommName</t>
   </si>
@@ -2497,6 +2497,9 @@
   </si>
   <si>
     <t>Electricity from Grid</t>
+  </si>
+  <si>
+    <t>ELCGRID</t>
   </si>
 </sst>
 </file>
@@ -6938,7 +6941,7 @@
     <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B26" s="64" t="str">
         <f>O26</f>
-        <v>GRIDELC</v>
+        <v>ELCGRID</v>
       </c>
       <c r="C26" s="68"/>
       <c r="D26" s="136" t="str">
@@ -6961,9 +6964,8 @@
         <v>46</v>
       </c>
       <c r="N26" s="138"/>
-      <c r="O26" s="68" t="str">
-        <f>$C$4</f>
-        <v>GRIDELC</v>
+      <c r="O26" s="68" t="s">
+        <v>269</v>
       </c>
       <c r="P26" s="140" t="s">
         <v>199</v>

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A26077-FC90-4FE8-9ED7-1CF2D4424F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023DEEF6-5B9A-4505-B079-1BED34294FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1558,7 +1558,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="268">
   <si>
     <t>CommName</t>
   </si>
@@ -2488,12 +2488,6 @@
   </si>
   <si>
     <t>GRIDELC</t>
-  </si>
-  <si>
-    <t>ELCAGG</t>
-  </si>
-  <si>
-    <t>Electricity aggrigator</t>
   </si>
   <si>
     <t>Electricity from Grid</t>
@@ -6514,10 +6508,10 @@
       </c>
       <c r="N8" s="68"/>
       <c r="O8" s="136" t="s">
-        <v>265</v>
+        <v>46</v>
       </c>
       <c r="P8" s="136" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="Q8" s="64" t="s">
         <v>148</v>
@@ -6946,7 +6940,7 @@
       <c r="C26" s="68"/>
       <c r="D26" s="136" t="str">
         <f>O8</f>
-        <v>GRIDELC</v>
+        <v>ELC</v>
       </c>
       <c r="E26" s="1">
         <v>2022</v>
@@ -6965,7 +6959,7 @@
       </c>
       <c r="N26" s="138"/>
       <c r="O26" s="68" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="P26" s="140" t="s">
         <v>199</v>
@@ -7479,19 +7473,11 @@
       <c r="AF8" s="90"/>
     </row>
     <row r="9" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="X9" s="142" t="s">
-        <v>46</v>
-      </c>
+      <c r="X9" s="142"/>
       <c r="Y9" s="142"/>
-      <c r="Z9" s="142" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA9" s="142" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB9" s="154" t="s">
-        <v>148</v>
-      </c>
+      <c r="Z9" s="142"/>
+      <c r="AA9" s="142"/>
+      <c r="AB9" s="154"/>
       <c r="AC9" s="90"/>
       <c r="AD9" s="90"/>
       <c r="AE9" s="90"/>
@@ -8060,7 +8046,7 @@
         <v>MANELC_TECH</v>
       </c>
       <c r="C23" s="142" t="str">
-        <f>Z9</f>
+        <f>PRI_Sector_Fuels!O8</f>
         <v>ELC</v>
       </c>
       <c r="D23" s="90" t="str">
@@ -8095,24 +8081,9 @@
       <c r="V23" s="104">
         <v>1</v>
       </c>
-      <c r="X23" s="141" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z23" s="141" t="s">
-        <v>266</v>
-      </c>
-      <c r="AA23" s="141" t="s">
-        <v>267</v>
-      </c>
-      <c r="AB23" s="88" t="s">
-        <v>148</v>
-      </c>
-      <c r="AC23" s="88" t="s">
-        <v>142</v>
-      </c>
-      <c r="AD23" s="154" t="s">
-        <v>201</v>
-      </c>
+      <c r="AB23" s="88"/>
+      <c r="AC23" s="88"/>
+      <c r="AD23" s="154"/>
     </row>
     <row r="24" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="94" t="s">
@@ -8167,18 +8138,9 @@
       <c r="AC25" s="94"/>
     </row>
     <row r="26" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="94" t="str">
-        <f>Z23</f>
-        <v>ELCAGG</v>
-      </c>
-      <c r="C26" s="142" t="str">
-        <f>PRI_Sector_Fuels!D26</f>
-        <v>GRIDELC</v>
-      </c>
-      <c r="D26" s="154" t="str">
-        <f>Z9</f>
-        <v>ELC</v>
-      </c>
+      <c r="B26" s="94"/>
+      <c r="C26" s="142"/>
+      <c r="D26" s="154"/>
       <c r="E26" s="143"/>
       <c r="F26" s="144"/>
       <c r="G26" s="144"/>
@@ -8187,27 +8149,9 @@
       <c r="J26" s="144"/>
       <c r="K26" s="144"/>
       <c r="L26" s="144"/>
-      <c r="M26" s="141">
-        <v>1</v>
-      </c>
-      <c r="N26" s="141">
-        <v>1</v>
-      </c>
-      <c r="O26" s="141">
-        <v>50</v>
-      </c>
-      <c r="Q26" s="141">
-        <v>0</v>
-      </c>
-      <c r="R26" s="110">
-        <v>0</v>
-      </c>
-      <c r="S26" s="110">
-        <v>0</v>
-      </c>
-      <c r="T26" s="110">
-        <v>8.76</v>
-      </c>
+      <c r="R26" s="110"/>
+      <c r="S26" s="110"/>
+      <c r="T26" s="110"/>
       <c r="U26" s="110"/>
       <c r="AB26" s="94"/>
       <c r="AC26" s="94"/>
@@ -10925,7 +10869,7 @@
       </c>
       <c r="F6" s="126" t="str">
         <f>PRI_Sector_Fuels!O8</f>
-        <v>GRIDELC</v>
+        <v>ELC</v>
       </c>
       <c r="G6" s="126"/>
       <c r="H6" s="126"/>

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023DEEF6-5B9A-4505-B079-1BED34294FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E57EEBC5-A6DC-46E2-BB58-056DE7578C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EBF TJ" sheetId="144" r:id="rId1"/>
@@ -1558,7 +1558,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="267">
   <si>
     <t>CommName</t>
   </si>
@@ -2223,9 +2223,6 @@
     </r>
   </si>
   <si>
-    <t>ktoe</t>
-  </si>
-  <si>
     <t>%</t>
   </si>
   <si>
@@ -2487,13 +2484,13 @@
     <t>2024THUSD/MWh</t>
   </si>
   <si>
-    <t>GRIDELC</t>
-  </si>
-  <si>
-    <t>Electricity from Grid</t>
-  </si>
-  <si>
-    <t>ELCGRID</t>
+    <t>GRID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aggrigate electricity demand </t>
+  </si>
+  <si>
+    <t>kte</t>
   </si>
 </sst>
 </file>
@@ -5129,13 +5126,13 @@
       </c>
       <c r="K2" s="20"/>
       <c r="O2" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P2" s="7" t="s">
         <v>148</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>205</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
@@ -6150,7 +6147,7 @@
         <v>121</v>
       </c>
       <c r="C46" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D46" s="109">
         <f>D18/(D18+E18)</f>
@@ -6171,7 +6168,7 @@
         <v>121</v>
       </c>
       <c r="C47" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E47" s="109">
         <f>E18/(D18+E18)</f>
@@ -6192,7 +6189,7 @@
         <v>121</v>
       </c>
       <c r="C48" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J48" s="109">
         <v>1</v>
@@ -6379,7 +6376,7 @@
     </row>
     <row r="4" spans="2:21" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C4" s="137" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>197</v>
@@ -6511,7 +6508,7 @@
         <v>46</v>
       </c>
       <c r="P8" s="136" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q8" s="64" t="s">
         <v>148</v>
@@ -6777,7 +6774,7 @@
         <v>GWh</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I22" s="8" t="str">
         <f>$E$2</f>
@@ -6958,8 +6955,9 @@
         <v>46</v>
       </c>
       <c r="N26" s="138"/>
-      <c r="O26" s="68" t="s">
-        <v>267</v>
+      <c r="O26" s="68" t="str">
+        <f>$M$26&amp;$C$4</f>
+        <v>ELCGRID</v>
       </c>
       <c r="P26" s="140" t="s">
         <v>199</v>
@@ -7387,10 +7385,10 @@
       </c>
       <c r="Y5" s="142"/>
       <c r="Z5" s="142" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AA5" s="142" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AB5" s="90" t="s">
         <v>148</v>
@@ -7446,7 +7444,7 @@
       </c>
       <c r="AB7" s="90" t="str">
         <f>EBF!Q2</f>
-        <v>ktoe</v>
+        <v>kte</v>
       </c>
       <c r="AC7" s="90"/>
       <c r="AD7" s="90"/>
@@ -7459,10 +7457,10 @@
       </c>
       <c r="Y8" s="142"/>
       <c r="Z8" s="142" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AA8" s="142" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB8" s="154" t="s">
         <v>148</v>
@@ -7583,28 +7581,28 @@
         <v>6</v>
       </c>
       <c r="E17" s="95" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F17" s="96" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G17" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="H17" s="96" t="s">
         <v>241</v>
       </c>
-      <c r="H17" s="96" t="s">
+      <c r="I17" s="96" t="s">
         <v>242</v>
       </c>
-      <c r="I17" s="96" t="s">
+      <c r="J17" s="96" t="s">
         <v>243</v>
       </c>
-      <c r="J17" s="96" t="s">
+      <c r="K17" s="96" t="s">
         <v>244</v>
       </c>
-      <c r="K17" s="96" t="s">
-        <v>245</v>
-      </c>
       <c r="L17" s="96" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="M17" s="95" t="s">
         <v>102</v>
@@ -7616,7 +7614,7 @@
         <v>104</v>
       </c>
       <c r="P17" s="95" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q17" s="95" t="s">
         <v>156</v>
@@ -7625,16 +7623,16 @@
         <v>157</v>
       </c>
       <c r="S17" s="95" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="T17" s="95" t="s">
         <v>149</v>
       </c>
       <c r="U17" s="95" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="V17" s="95" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="W17" s="155"/>
       <c r="X17" s="91" t="s">
@@ -7709,7 +7707,7 @@
         <v>113</v>
       </c>
       <c r="P18" s="97" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q18" s="97" t="s">
         <v>158</v>
@@ -7718,16 +7716,16 @@
         <v>159</v>
       </c>
       <c r="S18" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T18" s="97" t="s">
         <v>150</v>
       </c>
       <c r="U18" s="97" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="V18" s="97" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="W18" s="156"/>
       <c r="X18" s="93" t="s">
@@ -7768,25 +7766,25 @@
         <v>192</v>
       </c>
       <c r="F19" s="100" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G19" s="100" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H19" s="100" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I19" s="100" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J19" s="100" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K19" s="100" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L19" s="100" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M19" s="100"/>
       <c r="N19" s="101"/>
@@ -7795,17 +7793,17 @@
       </c>
       <c r="P19" s="100"/>
       <c r="Q19" s="100" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="R19" s="100" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="S19" s="100" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="T19" s="100"/>
       <c r="U19" s="100" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="V19" s="100"/>
       <c r="W19" s="157"/>
@@ -8025,7 +8023,7 @@
         <v>109</v>
       </c>
       <c r="Z22" s="145" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AA22" s="88" t="s">
         <v>198</v>
@@ -8091,7 +8089,7 @@
       </c>
       <c r="C24" s="142"/>
       <c r="D24" s="154" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E24" s="143"/>
       <c r="F24" s="144"/>
@@ -8117,7 +8115,7 @@
       </c>
       <c r="C25" s="142"/>
       <c r="D25" s="154" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E25" s="143"/>
       <c r="F25" s="144"/>
@@ -8351,25 +8349,25 @@
         <v>192</v>
       </c>
       <c r="F45" s="144" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G45" s="144" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H45" s="144" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I45" s="144" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J45" s="144" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K45" s="144" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L45" s="144" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M45" s="141"/>
       <c r="N45" s="141"/>
@@ -8385,10 +8383,10 @@
         <v>141</v>
       </c>
       <c r="C46" s="142" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D46" s="90" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E46" s="143"/>
       <c r="F46" s="144">
@@ -8414,10 +8412,10 @@
         <v>141</v>
       </c>
       <c r="C47" s="88" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D47" s="88" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F47" s="88">
         <v>0.41136476969163144</v>
@@ -8446,10 +8444,10 @@
         <v>143</v>
       </c>
       <c r="C48" s="88" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D48" s="88" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F48" s="88">
         <v>1</v>
@@ -8716,7 +8714,7 @@
         <v>165</v>
       </c>
       <c r="C9" s="175" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" s="175" t="s">
         <v>148</v>
@@ -8776,7 +8774,7 @@
         <v>MANELC</v>
       </c>
       <c r="J10" s="145" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K10" s="185">
         <v>3.3566276423652626E-2</v>
@@ -8790,7 +8788,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O10" s="145" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P10" s="185">
         <v>3.3566276423652626E-2</v>
@@ -8803,7 +8801,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T10" s="145" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="U10" s="185">
         <v>3.3566276423652626E-2</v>
@@ -8814,7 +8812,7 @@
         <v>165</v>
       </c>
       <c r="C11" s="175" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D11" s="175" t="s">
         <v>148</v>
@@ -8833,7 +8831,7 @@
         <v>MANELC</v>
       </c>
       <c r="J11" s="176" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K11" s="185">
         <v>3.3302706089073604E-2</v>
@@ -8847,7 +8845,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O11" s="176" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P11" s="185">
         <v>3.3302706089073604E-2</v>
@@ -8860,7 +8858,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T11" s="176" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="U11" s="185">
         <v>3.3302706089073604E-2</v>
@@ -8879,7 +8877,7 @@
         <v>MANELC</v>
       </c>
       <c r="J12" s="145" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K12" s="185">
         <v>3.3481814338032219E-2</v>
@@ -8893,7 +8891,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O12" s="145" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P12" s="185">
         <v>3.3481814338032219E-2</v>
@@ -8906,7 +8904,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T12" s="145" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="U12" s="185">
         <v>3.3481814338032219E-2</v>
@@ -8921,7 +8919,7 @@
         <v>MANELC</v>
       </c>
       <c r="J13" s="176" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K13" s="185">
         <v>3.3611381763990082E-2</v>
@@ -8935,7 +8933,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O13" s="176" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P13" s="185">
         <v>3.3611381763990082E-2</v>
@@ -8948,7 +8946,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T13" s="176" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="U13" s="185">
         <v>3.3611381763990082E-2</v>
@@ -8963,7 +8961,7 @@
         <v>MANELC</v>
       </c>
       <c r="J14" s="145" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K14" s="185">
         <v>3.4004820718610197E-2</v>
@@ -8977,7 +8975,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O14" s="145" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P14" s="185">
         <v>3.4004820718610197E-2</v>
@@ -8990,7 +8988,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T14" s="145" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="U14" s="185">
         <v>3.4004820718610197E-2</v>
@@ -9005,7 +9003,7 @@
         <v>MANELC</v>
       </c>
       <c r="J15" s="176" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K15" s="185">
         <v>3.4081384083392653E-2</v>
@@ -9019,7 +9017,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O15" s="176" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P15" s="185">
         <v>3.4081384083392653E-2</v>
@@ -9032,7 +9030,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T15" s="176" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="U15" s="185">
         <v>3.4081384083392653E-2</v>
@@ -9047,7 +9045,7 @@
         <v>MANELC</v>
       </c>
       <c r="J16" s="145" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K16" s="185">
         <v>3.3156795624830704E-2</v>
@@ -9061,7 +9059,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O16" s="145" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P16" s="185">
         <v>3.3156795624830704E-2</v>
@@ -9074,7 +9072,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T16" s="145" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="U16" s="185">
         <v>3.3156795624830704E-2</v>
@@ -9089,7 +9087,7 @@
         <v>MANELC</v>
       </c>
       <c r="J17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K17" s="185">
         <v>3.6518070997817571E-2</v>
@@ -9103,7 +9101,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P17" s="185">
         <v>3.6518070997817571E-2</v>
@@ -9116,7 +9114,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="U17" s="185">
         <v>3.6518070997817571E-2</v>
@@ -9131,7 +9129,7 @@
         <v>MANELC</v>
       </c>
       <c r="J18" s="145" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K18" s="185">
         <v>4.7257353018906531E-2</v>
@@ -9145,7 +9143,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O18" s="145" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P18" s="185">
         <v>4.7257353018906531E-2</v>
@@ -9158,7 +9156,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T18" s="145" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="U18" s="185">
         <v>4.7257353018906531E-2</v>
@@ -9173,7 +9171,7 @@
         <v>MANELC</v>
       </c>
       <c r="J19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K19" s="185">
         <v>5.6756578785819259E-2</v>
@@ -9187,7 +9185,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P19" s="185">
         <v>5.6756578785819259E-2</v>
@@ -9200,7 +9198,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U19" s="185">
         <v>5.6756578785819259E-2</v>
@@ -9215,7 +9213,7 @@
         <v>MANELC</v>
       </c>
       <c r="J20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K20" s="185">
         <v>5.5715023853427123E-2</v>
@@ -9229,7 +9227,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P20" s="185">
         <v>5.5715023853427123E-2</v>
@@ -9242,7 +9240,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="U20" s="185">
         <v>5.5715023853427123E-2</v>
@@ -9257,7 +9255,7 @@
         <v>MANELC</v>
       </c>
       <c r="J21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K21" s="185">
         <v>5.6345483069498978E-2</v>
@@ -9271,7 +9269,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P21" s="185">
         <v>5.6345483069498978E-2</v>
@@ -9284,7 +9282,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="U21" s="185">
         <v>5.6345483069498978E-2</v>
@@ -9299,7 +9297,7 @@
         <v>MANELC</v>
       </c>
       <c r="J22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K22" s="185">
         <v>4.8662133827205516E-2</v>
@@ -9313,7 +9311,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P22" s="185">
         <v>4.8662133827205516E-2</v>
@@ -9326,7 +9324,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="U22" s="185">
         <v>4.8662133827205516E-2</v>
@@ -9341,7 +9339,7 @@
         <v>MANELC</v>
       </c>
       <c r="J23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K23" s="185">
         <v>5.0293526586567008E-2</v>
@@ -9355,7 +9353,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P23" s="185">
         <v>5.0293526586567008E-2</v>
@@ -9368,7 +9366,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="U23" s="185">
         <v>5.0293526586567008E-2</v>
@@ -9383,7 +9381,7 @@
         <v>MANELC</v>
       </c>
       <c r="J24" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K24" s="185">
         <v>5.2523087098903048E-2</v>
@@ -9397,7 +9395,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O24" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P24" s="185">
         <v>5.2523087098903048E-2</v>
@@ -9410,7 +9408,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T24" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U24" s="185">
         <v>5.2523087098903048E-2</v>
@@ -9425,7 +9423,7 @@
         <v>MANELC</v>
       </c>
       <c r="J25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K25" s="185">
         <v>5.4966761848993004E-2</v>
@@ -9439,7 +9437,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P25" s="185">
         <v>5.4966761848993004E-2</v>
@@ -9452,7 +9450,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="U25" s="185">
         <v>5.4966761848993004E-2</v>
@@ -9468,7 +9466,7 @@
         <v>MANELC</v>
       </c>
       <c r="J26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K26" s="185">
         <v>5.3016988893511453E-2</v>
@@ -9482,7 +9480,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P26" s="185">
         <v>5.3016988893511453E-2</v>
@@ -9495,7 +9493,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="U26" s="185">
         <v>5.3016988893511453E-2</v>
@@ -9512,7 +9510,7 @@
         <v>MANELC</v>
       </c>
       <c r="J27" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K27" s="185">
         <v>4.4273060594597062E-2</v>
@@ -9526,7 +9524,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O27" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P27" s="185">
         <v>4.4273060594597062E-2</v>
@@ -9539,7 +9537,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T27" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U27" s="185">
         <v>4.4273060594597062E-2</v>
@@ -9557,7 +9555,7 @@
         <v>MANELC</v>
       </c>
       <c r="J28" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K28" s="185">
         <v>3.6258449498494133E-2</v>
@@ -9571,7 +9569,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O28" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P28" s="185">
         <v>3.6258449498494133E-2</v>
@@ -9584,7 +9582,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T28" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U28" s="185">
         <v>3.6258449498494133E-2</v>
@@ -9602,7 +9600,7 @@
         <v>MANELC</v>
       </c>
       <c r="J29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K29" s="185">
         <v>3.6040655779430726E-2</v>
@@ -9616,7 +9614,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P29" s="185">
         <v>3.6040655779430726E-2</v>
@@ -9629,7 +9627,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="U29" s="185">
         <v>3.6040655779430726E-2</v>
@@ -9644,7 +9642,7 @@
         <v>MANELC</v>
       </c>
       <c r="J30" s="145" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K30" s="185">
         <v>3.5097781406108856E-2</v>
@@ -9658,7 +9656,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O30" s="145" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P30" s="185">
         <v>3.5097781406108856E-2</v>
@@ -9671,7 +9669,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T30" s="145" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="U30" s="185">
         <v>3.5097781406108856E-2</v>
@@ -9686,7 +9684,7 @@
         <v>MANELC</v>
       </c>
       <c r="J31" s="176" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K31" s="185">
         <v>3.482493578674286E-2</v>
@@ -9700,7 +9698,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O31" s="176" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P31" s="185">
         <v>3.482493578674286E-2</v>
@@ -9713,7 +9711,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T31" s="176" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="U31" s="185">
         <v>3.482493578674286E-2</v>
@@ -9729,7 +9727,7 @@
         <v>MANELC</v>
       </c>
       <c r="J32" s="145" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K32" s="185">
         <v>3.2564766705734945E-2</v>
@@ -9743,7 +9741,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O32" s="145" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P32" s="185">
         <v>3.2564766705734945E-2</v>
@@ -9756,7 +9754,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T32" s="145" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="U32" s="185">
         <v>3.2564766705734945E-2</v>
@@ -9773,7 +9771,7 @@
         <v>MANELC</v>
       </c>
       <c r="J33" s="176" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K33" s="185">
         <v>3.3680163206659841E-2</v>
@@ -9787,7 +9785,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O33" s="176" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P33" s="185">
         <v>3.3680163206659841E-2</v>
@@ -9800,7 +9798,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T33" s="176" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="U33" s="185">
         <v>3.3680163206659841E-2</v>

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E57EEBC5-A6DC-46E2-BB58-056DE7578C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C858FB53-CDF6-4A4D-B83E-A21E5476E3E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EBF TJ" sheetId="144" r:id="rId1"/>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="C26" s="68"/>
       <c r="D26" s="136" t="str">
-        <f>O8</f>
+        <f>O$8</f>
         <v>ELC</v>
       </c>
       <c r="E26" s="1">

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFE134E-9BA5-4A4B-8671-84DB74AF8E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C858FB53-CDF6-4A4D-B83E-A21E5476E3E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EBF TJ" sheetId="144" r:id="rId1"/>
@@ -2157,9 +2157,6 @@
     <t>Manufacturing  Electricity for machine drive and other services</t>
   </si>
   <si>
-    <t>GRID</t>
-  </si>
-  <si>
     <t>Grid electricity</t>
   </si>
   <si>
@@ -2226,12 +2223,6 @@
     </r>
   </si>
   <si>
-    <t>ktoe</t>
-  </si>
-  <si>
-    <t>Aggrigate electricity demand of manufacturing sector</t>
-  </si>
-  <si>
     <t>%</t>
   </si>
   <si>
@@ -2491,6 +2482,15 @@
   </si>
   <si>
     <t>2024THUSD/MWh</t>
+  </si>
+  <si>
+    <t>GRID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aggrigate electricity demand </t>
+  </si>
+  <si>
+    <t>kte</t>
   </si>
 </sst>
 </file>
@@ -5126,13 +5126,13 @@
       </c>
       <c r="K2" s="20"/>
       <c r="O2" s="24" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="P2" s="7" t="s">
         <v>148</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>206</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
@@ -6147,7 +6147,7 @@
         <v>121</v>
       </c>
       <c r="C46" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D46" s="109">
         <f>D18/(D18+E18)</f>
@@ -6168,7 +6168,7 @@
         <v>121</v>
       </c>
       <c r="C47" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E47" s="109">
         <f>E18/(D18+E18)</f>
@@ -6189,7 +6189,7 @@
         <v>121</v>
       </c>
       <c r="C48" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J48" s="109">
         <v>1</v>
@@ -6376,7 +6376,7 @@
     </row>
     <row r="4" spans="2:21" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C4" s="137" t="s">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>197</v>
@@ -6421,13 +6421,13 @@
       <c r="D5" s="138"/>
       <c r="E5" s="77"/>
       <c r="F5" s="138"/>
-      <c r="G5" s="7"/>
+      <c r="G5" s="77"/>
       <c r="M5" s="64" t="s">
         <v>74</v>
       </c>
       <c r="N5" s="68"/>
       <c r="O5" s="136" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P5" s="64" t="s">
         <v>152</v>
@@ -6437,7 +6437,7 @@
       </c>
       <c r="R5" s="64"/>
       <c r="S5" s="137" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T5" s="64"/>
       <c r="U5" s="64"/>
@@ -6447,13 +6447,13 @@
       <c r="D6" s="138"/>
       <c r="E6" s="77"/>
       <c r="F6" s="138"/>
-      <c r="G6" s="7"/>
+      <c r="G6" s="77"/>
       <c r="M6" s="64" t="s">
         <v>74</v>
       </c>
       <c r="N6" s="68"/>
       <c r="O6" s="136" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="P6" s="64" t="s">
         <v>153</v>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="R6" s="64"/>
       <c r="S6" s="137" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T6" s="64"/>
       <c r="U6" s="64"/>
@@ -6473,13 +6473,13 @@
       <c r="D7" s="138"/>
       <c r="E7" s="77"/>
       <c r="F7" s="138"/>
-      <c r="G7" s="7"/>
+      <c r="G7" s="77"/>
       <c r="M7" s="64" t="s">
         <v>74</v>
       </c>
       <c r="N7" s="68"/>
       <c r="O7" s="136" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P7" s="64" t="s">
         <v>154</v>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="R7" s="64"/>
       <c r="S7" s="137" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T7" s="64"/>
       <c r="U7" s="64"/>
@@ -6499,7 +6499,7 @@
       <c r="D8" s="138"/>
       <c r="E8" s="77"/>
       <c r="F8" s="138"/>
-      <c r="G8" s="7"/>
+      <c r="G8" s="77"/>
       <c r="M8" s="136" t="s">
         <v>46</v>
       </c>
@@ -6508,14 +6508,14 @@
         <v>46</v>
       </c>
       <c r="P8" s="136" t="s">
-        <v>207</v>
+        <v>265</v>
       </c>
       <c r="Q8" s="64" t="s">
         <v>148</v>
       </c>
       <c r="R8" s="64"/>
       <c r="S8" s="137" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T8" s="64"/>
       <c r="U8" s="64"/>
@@ -6525,7 +6525,7 @@
       <c r="D9" s="138"/>
       <c r="E9" s="77"/>
       <c r="F9" s="138"/>
-      <c r="G9" s="7"/>
+      <c r="G9" s="77"/>
       <c r="M9" s="139"/>
       <c r="N9" s="139"/>
       <c r="O9" s="139"/>
@@ -6774,7 +6774,7 @@
         <v>GWh</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I22" s="8" t="str">
         <f>$E$2</f>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="R23" s="68"/>
       <c r="S23" s="137" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T23" s="68"/>
       <c r="U23" s="68"/>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="R24" s="68"/>
       <c r="S24" s="137" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T24" s="68"/>
       <c r="U24" s="68"/>
@@ -6926,7 +6926,7 @@
         <v>148</v>
       </c>
       <c r="S25" s="137" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26" spans="2:21" x14ac:dyDescent="0.25">
@@ -6960,13 +6960,13 @@
         <v>ELCGRID</v>
       </c>
       <c r="P26" s="140" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q26" t="s">
         <v>148</v>
       </c>
       <c r="S26" s="137" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.25">
@@ -7385,10 +7385,10 @@
       </c>
       <c r="Y5" s="142"/>
       <c r="Z5" s="142" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AA5" s="142" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AB5" s="90" t="s">
         <v>148</v>
@@ -7419,7 +7419,7 @@
         <v>151</v>
       </c>
       <c r="AA6" s="90" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AB6" s="90" t="s">
         <v>148</v>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="AB7" s="90" t="str">
         <f>EBF!Q2</f>
-        <v>ktoe</v>
+        <v>kte</v>
       </c>
       <c r="AC7" s="90"/>
       <c r="AD7" s="90"/>
@@ -7457,10 +7457,10 @@
       </c>
       <c r="Y8" s="142"/>
       <c r="Z8" s="142" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AA8" s="142" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="AB8" s="154" t="s">
         <v>148</v>
@@ -7581,28 +7581,28 @@
         <v>6</v>
       </c>
       <c r="E17" s="95" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F17" s="96" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="G17" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="H17" s="96" t="s">
+        <v>241</v>
+      </c>
+      <c r="I17" s="96" t="s">
+        <v>242</v>
+      </c>
+      <c r="J17" s="96" t="s">
         <v>243</v>
       </c>
-      <c r="H17" s="96" t="s">
+      <c r="K17" s="96" t="s">
         <v>244</v>
       </c>
-      <c r="I17" s="96" t="s">
-        <v>245</v>
-      </c>
-      <c r="J17" s="96" t="s">
-        <v>246</v>
-      </c>
-      <c r="K17" s="96" t="s">
-        <v>247</v>
-      </c>
       <c r="L17" s="96" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M17" s="95" t="s">
         <v>102</v>
@@ -7614,7 +7614,7 @@
         <v>104</v>
       </c>
       <c r="P17" s="95" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Q17" s="95" t="s">
         <v>156</v>
@@ -7623,16 +7623,16 @@
         <v>157</v>
       </c>
       <c r="S17" s="95" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="T17" s="95" t="s">
         <v>149</v>
       </c>
       <c r="U17" s="95" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="V17" s="95" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="W17" s="155"/>
       <c r="X17" s="91" t="s">
@@ -7707,7 +7707,7 @@
         <v>113</v>
       </c>
       <c r="P18" s="97" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="Q18" s="97" t="s">
         <v>158</v>
@@ -7716,16 +7716,16 @@
         <v>159</v>
       </c>
       <c r="S18" s="98" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="T18" s="97" t="s">
         <v>150</v>
       </c>
       <c r="U18" s="97" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="V18" s="97" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="W18" s="156"/>
       <c r="X18" s="93" t="s">
@@ -7766,25 +7766,25 @@
         <v>192</v>
       </c>
       <c r="F19" s="100" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G19" s="100" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="H19" s="100" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I19" s="100" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="J19" s="100" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K19" s="100" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L19" s="100" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="M19" s="100"/>
       <c r="N19" s="101"/>
@@ -7793,17 +7793,17 @@
       </c>
       <c r="P19" s="100"/>
       <c r="Q19" s="100" t="s">
+        <v>251</v>
+      </c>
+      <c r="R19" s="100" t="s">
         <v>254</v>
       </c>
-      <c r="R19" s="100" t="s">
-        <v>257</v>
-      </c>
       <c r="S19" s="100" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="T19" s="100"/>
       <c r="U19" s="100" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="V19" s="100"/>
       <c r="W19" s="157"/>
@@ -7884,7 +7884,7 @@
         <v>142</v>
       </c>
       <c r="AD20" s="154" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AE20" s="154"/>
       <c r="AF20" s="90"/>
@@ -7966,7 +7966,7 @@
         <v>142</v>
       </c>
       <c r="AD21" s="154" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AE21" s="154"/>
       <c r="AF21" s="90"/>
@@ -8023,7 +8023,7 @@
         <v>109</v>
       </c>
       <c r="Z22" s="145" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AA22" s="88" t="s">
         <v>198</v>
@@ -8035,7 +8035,7 @@
         <v>142</v>
       </c>
       <c r="AD22" s="154" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
@@ -8043,7 +8043,7 @@
         <f>Z22</f>
         <v>MANELC_TECH</v>
       </c>
-      <c r="C23" s="94" t="str">
+      <c r="C23" s="142" t="str">
         <f>PRI_Sector_Fuels!O8</f>
         <v>ELC</v>
       </c>
@@ -8070,8 +8070,8 @@
       <c r="O23" s="141">
         <v>50</v>
       </c>
-      <c r="R23" s="104"/>
-      <c r="S23" s="104"/>
+      <c r="R23" s="110"/>
+      <c r="S23" s="110"/>
       <c r="T23" s="104">
         <v>8.76</v>
       </c>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="C24" s="142"/>
       <c r="D24" s="154" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E24" s="143"/>
       <c r="F24" s="144"/>
@@ -8099,8 +8099,8 @@
       <c r="J24" s="144"/>
       <c r="K24" s="144"/>
       <c r="L24" s="144"/>
-      <c r="R24" s="104"/>
-      <c r="S24" s="104"/>
+      <c r="R24" s="110"/>
+      <c r="S24" s="110"/>
       <c r="T24" s="104"/>
       <c r="U24" s="104">
         <v>0.34100000000000003</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C25" s="142"/>
       <c r="D25" s="154" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E25" s="143"/>
       <c r="F25" s="144"/>
@@ -8125,8 +8125,8 @@
       <c r="J25" s="144"/>
       <c r="K25" s="144"/>
       <c r="L25" s="144"/>
-      <c r="R25" s="104"/>
-      <c r="S25" s="104"/>
+      <c r="R25" s="110"/>
+      <c r="S25" s="110"/>
       <c r="T25" s="104"/>
       <c r="U25" s="104">
         <v>0.25900000000000001</v>
@@ -8349,25 +8349,25 @@
         <v>192</v>
       </c>
       <c r="F45" s="144" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G45" s="144" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="H45" s="144" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I45" s="144" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="J45" s="144" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K45" s="144" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L45" s="144" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="M45" s="141"/>
       <c r="N45" s="141"/>
@@ -8383,10 +8383,10 @@
         <v>141</v>
       </c>
       <c r="C46" s="142" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D46" s="90" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E46" s="143"/>
       <c r="F46" s="144">
@@ -8412,10 +8412,10 @@
         <v>141</v>
       </c>
       <c r="C47" s="88" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D47" s="88" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F47" s="88">
         <v>0.41136476969163144</v>
@@ -8444,10 +8444,10 @@
         <v>143</v>
       </c>
       <c r="C48" s="88" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D48" s="88" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F48" s="88">
         <v>1</v>
@@ -8714,7 +8714,7 @@
         <v>165</v>
       </c>
       <c r="C9" s="175" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D9" s="175" t="s">
         <v>148</v>
@@ -8774,7 +8774,7 @@
         <v>MANELC</v>
       </c>
       <c r="J10" s="145" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K10" s="185">
         <v>3.3566276423652626E-2</v>
@@ -8788,7 +8788,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O10" s="145" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P10" s="185">
         <v>3.3566276423652626E-2</v>
@@ -8801,7 +8801,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T10" s="145" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U10" s="185">
         <v>3.3566276423652626E-2</v>
@@ -8812,7 +8812,7 @@
         <v>165</v>
       </c>
       <c r="C11" s="175" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D11" s="175" t="s">
         <v>148</v>
@@ -8831,7 +8831,7 @@
         <v>MANELC</v>
       </c>
       <c r="J11" s="176" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="K11" s="185">
         <v>3.3302706089073604E-2</v>
@@ -8845,7 +8845,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O11" s="176" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P11" s="185">
         <v>3.3302706089073604E-2</v>
@@ -8858,7 +8858,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T11" s="176" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="U11" s="185">
         <v>3.3302706089073604E-2</v>
@@ -8877,7 +8877,7 @@
         <v>MANELC</v>
       </c>
       <c r="J12" s="145" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K12" s="185">
         <v>3.3481814338032219E-2</v>
@@ -8891,7 +8891,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O12" s="145" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P12" s="185">
         <v>3.3481814338032219E-2</v>
@@ -8904,7 +8904,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T12" s="145" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="U12" s="185">
         <v>3.3481814338032219E-2</v>
@@ -8919,7 +8919,7 @@
         <v>MANELC</v>
       </c>
       <c r="J13" s="176" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K13" s="185">
         <v>3.3611381763990082E-2</v>
@@ -8933,7 +8933,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O13" s="176" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P13" s="185">
         <v>3.3611381763990082E-2</v>
@@ -8946,7 +8946,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T13" s="176" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="U13" s="185">
         <v>3.3611381763990082E-2</v>
@@ -8961,7 +8961,7 @@
         <v>MANELC</v>
       </c>
       <c r="J14" s="145" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K14" s="185">
         <v>3.4004820718610197E-2</v>
@@ -8975,7 +8975,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O14" s="145" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="P14" s="185">
         <v>3.4004820718610197E-2</v>
@@ -8988,7 +8988,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T14" s="145" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="U14" s="185">
         <v>3.4004820718610197E-2</v>
@@ -9003,7 +9003,7 @@
         <v>MANELC</v>
       </c>
       <c r="J15" s="176" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="K15" s="185">
         <v>3.4081384083392653E-2</v>
@@ -9017,7 +9017,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O15" s="176" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="P15" s="185">
         <v>3.4081384083392653E-2</v>
@@ -9030,7 +9030,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T15" s="176" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="U15" s="185">
         <v>3.4081384083392653E-2</v>
@@ -9045,7 +9045,7 @@
         <v>MANELC</v>
       </c>
       <c r="J16" s="145" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="K16" s="185">
         <v>3.3156795624830704E-2</v>
@@ -9059,7 +9059,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O16" s="145" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="P16" s="185">
         <v>3.3156795624830704E-2</v>
@@ -9072,7 +9072,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T16" s="145" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="U16" s="185">
         <v>3.3156795624830704E-2</v>
@@ -9087,7 +9087,7 @@
         <v>MANELC</v>
       </c>
       <c r="J17" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="K17" s="185">
         <v>3.6518070997817571E-2</v>
@@ -9101,7 +9101,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O17" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P17" s="185">
         <v>3.6518070997817571E-2</v>
@@ -9114,7 +9114,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T17" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="U17" s="185">
         <v>3.6518070997817571E-2</v>
@@ -9129,7 +9129,7 @@
         <v>MANELC</v>
       </c>
       <c r="J18" s="145" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K18" s="185">
         <v>4.7257353018906531E-2</v>
@@ -9143,7 +9143,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O18" s="145" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P18" s="185">
         <v>4.7257353018906531E-2</v>
@@ -9156,7 +9156,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T18" s="145" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="U18" s="185">
         <v>4.7257353018906531E-2</v>
@@ -9171,7 +9171,7 @@
         <v>MANELC</v>
       </c>
       <c r="J19" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="K19" s="185">
         <v>5.6756578785819259E-2</v>
@@ -9185,7 +9185,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O19" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="P19" s="185">
         <v>5.6756578785819259E-2</v>
@@ -9198,7 +9198,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T19" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="U19" s="185">
         <v>5.6756578785819259E-2</v>
@@ -9213,7 +9213,7 @@
         <v>MANELC</v>
       </c>
       <c r="J20" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="K20" s="185">
         <v>5.5715023853427123E-2</v>
@@ -9227,7 +9227,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O20" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="P20" s="185">
         <v>5.5715023853427123E-2</v>
@@ -9240,7 +9240,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T20" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="U20" s="185">
         <v>5.5715023853427123E-2</v>
@@ -9255,7 +9255,7 @@
         <v>MANELC</v>
       </c>
       <c r="J21" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="K21" s="185">
         <v>5.6345483069498978E-2</v>
@@ -9269,7 +9269,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O21" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="P21" s="185">
         <v>5.6345483069498978E-2</v>
@@ -9282,7 +9282,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T21" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="U21" s="185">
         <v>5.6345483069498978E-2</v>
@@ -9297,7 +9297,7 @@
         <v>MANELC</v>
       </c>
       <c r="J22" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K22" s="185">
         <v>4.8662133827205516E-2</v>
@@ -9311,7 +9311,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O22" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="P22" s="185">
         <v>4.8662133827205516E-2</v>
@@ -9324,7 +9324,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T22" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="U22" s="185">
         <v>4.8662133827205516E-2</v>
@@ -9339,7 +9339,7 @@
         <v>MANELC</v>
       </c>
       <c r="J23" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K23" s="185">
         <v>5.0293526586567008E-2</v>
@@ -9353,7 +9353,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O23" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="P23" s="185">
         <v>5.0293526586567008E-2</v>
@@ -9366,7 +9366,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T23" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="U23" s="185">
         <v>5.0293526586567008E-2</v>
@@ -9381,7 +9381,7 @@
         <v>MANELC</v>
       </c>
       <c r="J24" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="K24" s="185">
         <v>5.2523087098903048E-2</v>
@@ -9395,7 +9395,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O24" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P24" s="185">
         <v>5.2523087098903048E-2</v>
@@ -9408,7 +9408,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T24" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="U24" s="185">
         <v>5.2523087098903048E-2</v>
@@ -9423,7 +9423,7 @@
         <v>MANELC</v>
       </c>
       <c r="J25" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K25" s="185">
         <v>5.4966761848993004E-2</v>
@@ -9437,7 +9437,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O25" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="P25" s="185">
         <v>5.4966761848993004E-2</v>
@@ -9450,7 +9450,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T25" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="U25" s="185">
         <v>5.4966761848993004E-2</v>
@@ -9466,7 +9466,7 @@
         <v>MANELC</v>
       </c>
       <c r="J26" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="K26" s="185">
         <v>5.3016988893511453E-2</v>
@@ -9480,7 +9480,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O26" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P26" s="185">
         <v>5.3016988893511453E-2</v>
@@ -9493,7 +9493,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T26" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="U26" s="185">
         <v>5.3016988893511453E-2</v>
@@ -9510,7 +9510,7 @@
         <v>MANELC</v>
       </c>
       <c r="J27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K27" s="185">
         <v>4.4273060594597062E-2</v>
@@ -9524,7 +9524,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="P27" s="185">
         <v>4.4273060594597062E-2</v>
@@ -9537,7 +9537,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="U27" s="185">
         <v>4.4273060594597062E-2</v>
@@ -9555,7 +9555,7 @@
         <v>MANELC</v>
       </c>
       <c r="J28" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="K28" s="185">
         <v>3.6258449498494133E-2</v>
@@ -9569,7 +9569,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O28" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P28" s="185">
         <v>3.6258449498494133E-2</v>
@@ -9582,7 +9582,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T28" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="U28" s="185">
         <v>3.6258449498494133E-2</v>
@@ -9600,7 +9600,7 @@
         <v>MANELC</v>
       </c>
       <c r="J29" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K29" s="185">
         <v>3.6040655779430726E-2</v>
@@ -9614,7 +9614,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O29" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="P29" s="185">
         <v>3.6040655779430726E-2</v>
@@ -9627,7 +9627,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T29" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="U29" s="185">
         <v>3.6040655779430726E-2</v>
@@ -9642,7 +9642,7 @@
         <v>MANELC</v>
       </c>
       <c r="J30" s="145" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="K30" s="185">
         <v>3.5097781406108856E-2</v>
@@ -9656,7 +9656,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O30" s="145" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="P30" s="185">
         <v>3.5097781406108856E-2</v>
@@ -9669,7 +9669,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T30" s="145" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="U30" s="185">
         <v>3.5097781406108856E-2</v>
@@ -9684,7 +9684,7 @@
         <v>MANELC</v>
       </c>
       <c r="J31" s="176" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="K31" s="185">
         <v>3.482493578674286E-2</v>
@@ -9698,7 +9698,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O31" s="176" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="P31" s="185">
         <v>3.482493578674286E-2</v>
@@ -9711,7 +9711,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T31" s="176" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="U31" s="185">
         <v>3.482493578674286E-2</v>
@@ -9727,7 +9727,7 @@
         <v>MANELC</v>
       </c>
       <c r="J32" s="145" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="K32" s="185">
         <v>3.2564766705734945E-2</v>
@@ -9741,7 +9741,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O32" s="145" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="P32" s="185">
         <v>3.2564766705734945E-2</v>
@@ -9754,7 +9754,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T32" s="145" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="U32" s="185">
         <v>3.2564766705734945E-2</v>
@@ -9771,7 +9771,7 @@
         <v>MANELC</v>
       </c>
       <c r="J33" s="176" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="K33" s="185">
         <v>3.3680163206659841E-2</v>
@@ -9785,7 +9785,7 @@
         <v>MANHEAT</v>
       </c>
       <c r="O33" s="176" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P33" s="185">
         <v>3.3680163206659841E-2</v>
@@ -9798,7 +9798,7 @@
         <v>CEMENTHEAT</v>
       </c>
       <c r="T33" s="176" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="U33" s="185">
         <v>3.3680163206659841E-2</v>

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C858FB53-CDF6-4A4D-B83E-A21E5476E3E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{173AB996-058D-4CD2-98E0-360E614A324F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EBF TJ" sheetId="144" r:id="rId1"/>
@@ -1558,7 +1558,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="266">
   <si>
     <t>CommName</t>
   </si>
@@ -2314,9 +2314,6 @@
   </si>
   <si>
     <t>W_24</t>
-  </si>
-  <si>
-    <t>MANCO2</t>
   </si>
   <si>
     <t>ENV_ACT</t>
@@ -5126,13 +5123,13 @@
       </c>
       <c r="K2" s="20"/>
       <c r="O2" s="24" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P2" s="7" t="s">
         <v>148</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
@@ -6147,7 +6144,7 @@
         <v>121</v>
       </c>
       <c r="C46" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D46" s="109">
         <f>D18/(D18+E18)</f>
@@ -6168,7 +6165,7 @@
         <v>121</v>
       </c>
       <c r="C47" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E47" s="109">
         <f>E18/(D18+E18)</f>
@@ -6189,7 +6186,7 @@
         <v>121</v>
       </c>
       <c r="C48" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J48" s="109">
         <v>1</v>
@@ -6376,7 +6373,7 @@
     </row>
     <row r="4" spans="2:21" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C4" s="137" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>197</v>
@@ -6508,7 +6505,7 @@
         <v>46</v>
       </c>
       <c r="P8" s="136" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q8" s="64" t="s">
         <v>148</v>
@@ -6774,7 +6771,7 @@
         <v>GWh</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I22" s="8" t="str">
         <f>$E$2</f>
@@ -6951,7 +6948,7 @@
         <v>8.76</v>
       </c>
       <c r="K26" s="162"/>
-      <c r="M26" s="138" t="s">
+      <c r="M26" t="s">
         <v>46</v>
       </c>
       <c r="N26" s="138"/>
@@ -7457,7 +7454,7 @@
       </c>
       <c r="Y8" s="142"/>
       <c r="Z8" s="142" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AA8" s="142" t="s">
         <v>209</v>
@@ -7584,25 +7581,25 @@
         <v>211</v>
       </c>
       <c r="F17" s="96" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G17" s="96" t="s">
+        <v>239</v>
+      </c>
+      <c r="H17" s="96" t="s">
         <v>240</v>
       </c>
-      <c r="H17" s="96" t="s">
+      <c r="I17" s="96" t="s">
         <v>241</v>
       </c>
-      <c r="I17" s="96" t="s">
+      <c r="J17" s="96" t="s">
         <v>242</v>
       </c>
-      <c r="J17" s="96" t="s">
+      <c r="K17" s="96" t="s">
         <v>243</v>
       </c>
-      <c r="K17" s="96" t="s">
-        <v>244</v>
-      </c>
       <c r="L17" s="96" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M17" s="95" t="s">
         <v>102</v>
@@ -7623,16 +7620,16 @@
         <v>157</v>
       </c>
       <c r="S17" s="95" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="T17" s="95" t="s">
         <v>149</v>
       </c>
       <c r="U17" s="95" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="V17" s="95" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="W17" s="155"/>
       <c r="X17" s="91" t="s">
@@ -7716,16 +7713,16 @@
         <v>159</v>
       </c>
       <c r="S18" s="98" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="T18" s="97" t="s">
         <v>150</v>
       </c>
       <c r="U18" s="97" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="V18" s="97" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="W18" s="156"/>
       <c r="X18" s="93" t="s">
@@ -7793,17 +7790,17 @@
       </c>
       <c r="P19" s="100"/>
       <c r="Q19" s="100" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="R19" s="100" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="S19" s="100" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T19" s="100"/>
       <c r="U19" s="100" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="V19" s="100"/>
       <c r="W19" s="157"/>
@@ -7973,57 +7970,31 @@
     </row>
     <row r="22" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B22" s="88" t="str">
-        <f>Z$21</f>
-        <v>Boiler</v>
-      </c>
-      <c r="C22" s="88" t="str">
-        <f>PRI_Sector_Fuels!O7</f>
-        <v>MANOILIMP</v>
+        <f>Z$20</f>
+        <v>Kiln</v>
       </c>
       <c r="D22" s="90" t="str">
-        <f>Z$5</f>
-        <v>MANHEAT</v>
+        <f>Z$7</f>
+        <v>MANCO2</v>
       </c>
       <c r="E22" s="105"/>
-      <c r="F22" s="102">
-        <v>1</v>
-      </c>
+      <c r="F22" s="102"/>
       <c r="G22" s="102"/>
       <c r="H22" s="102"/>
       <c r="I22" s="102"/>
       <c r="J22" s="102"/>
       <c r="K22" s="102"/>
       <c r="L22" s="102"/>
-      <c r="M22" s="103">
-        <v>0.8</v>
-      </c>
-      <c r="N22" s="105">
-        <v>1</v>
-      </c>
-      <c r="O22" s="104">
-        <v>25</v>
-      </c>
-      <c r="P22" s="121"/>
-      <c r="Q22" s="188">
-        <v>62.9</v>
-      </c>
-      <c r="R22" s="189">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="S22" s="189">
-        <v>1.82</v>
-      </c>
-      <c r="T22" s="104">
-        <v>8.76</v>
-      </c>
-      <c r="U22" s="104"/>
+      <c r="U22" s="104">
+        <v>0.34100000000000003</v>
+      </c>
       <c r="V22" s="104"/>
       <c r="W22" s="110"/>
       <c r="X22" s="88" t="s">
         <v>109</v>
       </c>
       <c r="Z22" s="145" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AA22" s="88" t="s">
         <v>198</v>
@@ -8040,16 +8011,16 @@
     </row>
     <row r="23" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="94" t="str">
-        <f>Z22</f>
-        <v>MANELC_TECH</v>
+        <f>Z21</f>
+        <v>Boiler</v>
       </c>
       <c r="C23" s="142" t="str">
-        <f>PRI_Sector_Fuels!O8</f>
-        <v>ELC</v>
+        <f>PRI_Sector_Fuels!O7</f>
+        <v>MANOILIMP</v>
       </c>
       <c r="D23" s="90" t="str">
-        <f>Z6</f>
-        <v>MANELC</v>
+        <f>Z5</f>
+        <v>MANHEAT</v>
       </c>
       <c r="E23" s="105"/>
       <c r="F23" s="144">
@@ -8061,35 +8032,42 @@
       <c r="J23" s="144"/>
       <c r="K23" s="144"/>
       <c r="L23" s="144"/>
-      <c r="M23" s="141">
+      <c r="M23" s="103">
+        <v>0.8</v>
+      </c>
+      <c r="N23" s="105">
         <v>1</v>
       </c>
-      <c r="N23" s="141">
-        <v>1</v>
-      </c>
-      <c r="O23" s="141">
-        <v>50</v>
-      </c>
-      <c r="R23" s="110"/>
-      <c r="S23" s="110"/>
+      <c r="O23" s="104">
+        <v>25</v>
+      </c>
+      <c r="P23" s="121"/>
+      <c r="Q23" s="188">
+        <v>62.9</v>
+      </c>
+      <c r="R23" s="189">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="S23" s="189">
+        <v>1.82</v>
+      </c>
       <c r="T23" s="104">
         <v>8.76</v>
       </c>
-      <c r="U23" s="104"/>
-      <c r="V23" s="104">
-        <v>1</v>
-      </c>
+      <c r="V23" s="104"/>
       <c r="AB23" s="88"/>
       <c r="AC23" s="88"/>
       <c r="AD23" s="154"/>
     </row>
     <row r="24" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="94" t="s">
-        <v>141</v>
+      <c r="B24" s="94" t="str">
+        <f>Z21</f>
+        <v>Boiler</v>
       </c>
       <c r="C24" s="142"/>
-      <c r="D24" s="154" t="s">
-        <v>236</v>
+      <c r="D24" s="154" t="str">
+        <f>Z7</f>
+        <v>MANCO2</v>
       </c>
       <c r="E24" s="143"/>
       <c r="F24" s="144"/>
@@ -8103,35 +8081,53 @@
       <c r="S24" s="110"/>
       <c r="T24" s="104"/>
       <c r="U24" s="104">
-        <v>0.34100000000000003</v>
+        <v>0.25900000000000001</v>
       </c>
       <c r="V24" s="104"/>
       <c r="AB24" s="94"/>
       <c r="AC24" s="94"/>
     </row>
     <row r="25" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="94" t="s">
-        <v>143</v>
-      </c>
-      <c r="C25" s="142"/>
-      <c r="D25" s="154" t="s">
-        <v>236</v>
+      <c r="B25" s="94" t="str">
+        <f>Z22</f>
+        <v>MANELC_TECH</v>
+      </c>
+      <c r="C25" s="142" t="str">
+        <f>PRI_Sector_Fuels!O8</f>
+        <v>ELC</v>
+      </c>
+      <c r="D25" s="154" t="str">
+        <f>Z6</f>
+        <v>MANELC</v>
       </c>
       <c r="E25" s="143"/>
-      <c r="F25" s="144"/>
+      <c r="F25" s="144">
+        <v>1</v>
+      </c>
       <c r="G25" s="144"/>
       <c r="H25" s="144"/>
       <c r="I25" s="144"/>
       <c r="J25" s="144"/>
       <c r="K25" s="144"/>
       <c r="L25" s="144"/>
+      <c r="M25" s="141">
+        <v>1</v>
+      </c>
+      <c r="N25" s="141">
+        <v>1</v>
+      </c>
+      <c r="O25" s="141">
+        <v>50</v>
+      </c>
       <c r="R25" s="110"/>
       <c r="S25" s="110"/>
-      <c r="T25" s="104"/>
-      <c r="U25" s="104">
-        <v>0.25900000000000001</v>
-      </c>
-      <c r="V25" s="104"/>
+      <c r="T25" s="104">
+        <v>8.76</v>
+      </c>
+      <c r="U25" s="104"/>
+      <c r="V25" s="104">
+        <v>1</v>
+      </c>
       <c r="AB25" s="94"/>
       <c r="AC25" s="94"/>
     </row>
@@ -8383,10 +8379,10 @@
         <v>141</v>
       </c>
       <c r="C46" s="142" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D46" s="90" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E46" s="143"/>
       <c r="F46" s="144">
@@ -8412,10 +8408,10 @@
         <v>141</v>
       </c>
       <c r="C47" s="88" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D47" s="88" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F47" s="88">
         <v>0.41136476969163144</v>
@@ -8444,7 +8440,7 @@
         <v>143</v>
       </c>
       <c r="C48" s="88" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D48" s="88" t="s">
         <v>210</v>
@@ -8812,7 +8808,7 @@
         <v>165</v>
       </c>
       <c r="C11" s="175" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D11" s="175" t="s">
         <v>148</v>

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{173AB996-058D-4CD2-98E0-360E614A324F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A82F354-61C7-4CB9-950D-54B0CAE6AA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EBF TJ" sheetId="144" r:id="rId1"/>
@@ -1558,7 +1558,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="270">
   <si>
     <t>CommName</t>
   </si>
@@ -2016,15 +2016,6 @@
     <t>MANELC</t>
   </si>
   <si>
-    <t>Manufacturing coal-domestic</t>
-  </si>
-  <si>
-    <t>Manufacturing coal-imported</t>
-  </si>
-  <si>
-    <t>Manufacturing oil-imported</t>
-  </si>
-  <si>
     <t>Coal</t>
   </si>
   <si>
@@ -2155,9 +2146,6 @@
   </si>
   <si>
     <t>Manufacturing  Electricity for machine drive and other services</t>
-  </si>
-  <si>
-    <t>Grid electricity</t>
   </si>
   <si>
     <t>Manufacturing ElectricitySupply-ELC</t>
@@ -2484,10 +2472,34 @@
     <t>GRID</t>
   </si>
   <si>
-    <t xml:space="preserve">Aggrigate electricity demand </t>
-  </si>
-  <si>
     <t>kte</t>
+  </si>
+  <si>
+    <t>GRIDELC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electricity from Grid </t>
+  </si>
+  <si>
+    <t>Aggrigate Electricity</t>
+  </si>
+  <si>
+    <t>Manufacturing Coal-Domestic</t>
+  </si>
+  <si>
+    <t>Manufacturing Coal-Imported</t>
+  </si>
+  <si>
+    <t>Manufacturing Oil-Imported</t>
+  </si>
+  <si>
+    <t>GRIDAGG</t>
+  </si>
+  <si>
+    <t>Grid Electricity to ELC Aggrigator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid Electricity </t>
   </si>
 </sst>
 </file>
@@ -4392,7 +4404,7 @@
     <row r="3" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C3" s="4"/>
       <c r="D3" s="28" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E3" s="28" t="s">
         <v>115</v>
@@ -5123,19 +5135,19 @@
       </c>
       <c r="K2" s="20"/>
       <c r="O2" s="24" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="P2" s="7" t="s">
         <v>148</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
       <c r="C3" s="4"/>
       <c r="D3" s="28" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E3" s="28" t="s">
         <v>115</v>
@@ -6144,7 +6156,7 @@
         <v>121</v>
       </c>
       <c r="C46" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D46" s="109">
         <f>D18/(D18+E18)</f>
@@ -6165,7 +6177,7 @@
         <v>121</v>
       </c>
       <c r="C47" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="E47" s="109">
         <f>E18/(D18+E18)</f>
@@ -6186,7 +6198,7 @@
         <v>121</v>
       </c>
       <c r="C48" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J48" s="109">
         <v>1</v>
@@ -6373,10 +6385,10 @@
     </row>
     <row r="4" spans="2:21" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C4" s="137" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E4" s="77" t="s">
         <v>148</v>
@@ -6424,17 +6436,17 @@
       </c>
       <c r="N5" s="68"/>
       <c r="O5" s="136" t="s">
-        <v>202</v>
-      </c>
-      <c r="P5" s="64" t="s">
-        <v>152</v>
+        <v>198</v>
+      </c>
+      <c r="P5" s="136" t="s">
+        <v>264</v>
       </c>
       <c r="Q5" s="64" t="s">
         <v>148</v>
       </c>
       <c r="R5" s="64"/>
       <c r="S5" s="137" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="T5" s="64"/>
       <c r="U5" s="64"/>
@@ -6450,17 +6462,17 @@
       </c>
       <c r="N6" s="68"/>
       <c r="O6" s="136" t="s">
-        <v>203</v>
-      </c>
-      <c r="P6" s="64" t="s">
-        <v>153</v>
+        <v>199</v>
+      </c>
+      <c r="P6" s="136" t="s">
+        <v>265</v>
       </c>
       <c r="Q6" s="64" t="s">
         <v>148</v>
       </c>
       <c r="R6" s="64"/>
       <c r="S6" s="137" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="T6" s="64"/>
       <c r="U6" s="64"/>
@@ -6476,17 +6488,17 @@
       </c>
       <c r="N7" s="68"/>
       <c r="O7" s="136" t="s">
-        <v>204</v>
-      </c>
-      <c r="P7" s="64" t="s">
-        <v>154</v>
+        <v>200</v>
+      </c>
+      <c r="P7" s="136" t="s">
+        <v>266</v>
       </c>
       <c r="Q7" s="64" t="s">
         <v>148</v>
       </c>
       <c r="R7" s="64"/>
       <c r="S7" s="137" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="T7" s="64"/>
       <c r="U7" s="64"/>
@@ -6502,17 +6514,17 @@
       </c>
       <c r="N8" s="68"/>
       <c r="O8" s="136" t="s">
-        <v>46</v>
+        <v>261</v>
       </c>
       <c r="P8" s="136" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Q8" s="64" t="s">
         <v>148</v>
       </c>
       <c r="R8" s="64"/>
       <c r="S8" s="137" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="T8" s="64"/>
       <c r="U8" s="64"/>
@@ -6523,13 +6535,23 @@
       <c r="E9" s="77"/>
       <c r="F9" s="138"/>
       <c r="G9" s="77"/>
-      <c r="M9" s="139"/>
+      <c r="M9" s="139" t="s">
+        <v>46</v>
+      </c>
       <c r="N9" s="139"/>
-      <c r="O9" s="139"/>
-      <c r="P9" s="139"/>
-      <c r="Q9" s="139"/>
+      <c r="O9" s="139" t="s">
+        <v>46</v>
+      </c>
+      <c r="P9" s="139" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q9" s="64" t="s">
+        <v>148</v>
+      </c>
       <c r="R9" s="64"/>
-      <c r="S9" s="64"/>
+      <c r="S9" s="137" t="s">
+        <v>197</v>
+      </c>
       <c r="T9" s="64"/>
       <c r="U9" s="64"/>
     </row>
@@ -6771,7 +6793,7 @@
         <v>GWh</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="I22" s="8" t="str">
         <f>$E$2</f>
@@ -6834,7 +6856,7 @@
       </c>
       <c r="R23" s="68"/>
       <c r="S23" s="137" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="T23" s="68"/>
       <c r="U23" s="68"/>
@@ -6880,7 +6902,7 @@
       </c>
       <c r="R24" s="68"/>
       <c r="S24" s="137" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="T24" s="68"/>
       <c r="U24" s="68"/>
@@ -6923,7 +6945,7 @@
         <v>148</v>
       </c>
       <c r="S25" s="137" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="26" spans="2:21" x14ac:dyDescent="0.25">
@@ -6934,7 +6956,7 @@
       <c r="C26" s="68"/>
       <c r="D26" s="136" t="str">
         <f>O$8</f>
-        <v>ELC</v>
+        <v>GRIDELC</v>
       </c>
       <c r="E26" s="1">
         <v>2022</v>
@@ -6957,31 +6979,57 @@
         <v>ELCGRID</v>
       </c>
       <c r="P26" s="140" t="s">
-        <v>199</v>
+        <v>269</v>
       </c>
       <c r="Q26" t="s">
         <v>148</v>
       </c>
       <c r="S26" s="137" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B27" s="147"/>
-      <c r="C27" s="147"/>
-      <c r="D27" s="136"/>
-      <c r="E27" s="146"/>
+      <c r="B27" s="64" t="str">
+        <f>O27</f>
+        <v>GRIDAGG</v>
+      </c>
+      <c r="C27" s="147" t="str">
+        <f>O8</f>
+        <v>GRIDELC</v>
+      </c>
+      <c r="D27" s="136" t="str">
+        <f>O9</f>
+        <v>ELC</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2022</v>
+      </c>
       <c r="F27" s="138"/>
       <c r="G27" s="138"/>
-      <c r="H27" s="163"/>
+      <c r="H27" s="163">
+        <v>0</v>
+      </c>
       <c r="I27" s="166"/>
-      <c r="J27" s="163"/>
+      <c r="J27" s="113">
+        <v>8.76</v>
+      </c>
       <c r="K27" s="163"/>
-      <c r="M27" s="138"/>
+      <c r="M27" s="138" t="s">
+        <v>46</v>
+      </c>
       <c r="N27" s="138"/>
-      <c r="O27" s="139"/>
-      <c r="P27" s="140"/>
-      <c r="Q27" s="138"/>
+      <c r="O27" s="139" t="s">
+        <v>267</v>
+      </c>
+      <c r="P27" s="140" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>148</v>
+      </c>
+      <c r="S27" s="137" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B28" s="147"/>
@@ -7382,10 +7430,10 @@
       </c>
       <c r="Y5" s="142"/>
       <c r="Z5" s="142" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="AA5" s="142" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AB5" s="90" t="s">
         <v>148</v>
@@ -7416,7 +7464,7 @@
         <v>151</v>
       </c>
       <c r="AA6" s="90" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AB6" s="90" t="s">
         <v>148</v>
@@ -7454,10 +7502,10 @@
       </c>
       <c r="Y8" s="142"/>
       <c r="Z8" s="142" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="AA8" s="142" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AB8" s="154" t="s">
         <v>148</v>
@@ -7578,28 +7626,28 @@
         <v>6</v>
       </c>
       <c r="E17" s="95" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F17" s="96" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="G17" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="H17" s="96" t="s">
+        <v>236</v>
+      </c>
+      <c r="I17" s="96" t="s">
+        <v>237</v>
+      </c>
+      <c r="J17" s="96" t="s">
+        <v>238</v>
+      </c>
+      <c r="K17" s="96" t="s">
         <v>239</v>
       </c>
-      <c r="H17" s="96" t="s">
-        <v>240</v>
-      </c>
-      <c r="I17" s="96" t="s">
-        <v>241</v>
-      </c>
-      <c r="J17" s="96" t="s">
-        <v>242</v>
-      </c>
-      <c r="K17" s="96" t="s">
-        <v>243</v>
-      </c>
       <c r="L17" s="96" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="M17" s="95" t="s">
         <v>102</v>
@@ -7611,25 +7659,25 @@
         <v>104</v>
       </c>
       <c r="P17" s="95" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="Q17" s="95" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="R17" s="95" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="S17" s="95" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="T17" s="95" t="s">
         <v>149</v>
       </c>
       <c r="U17" s="95" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="V17" s="95" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="W17" s="155"/>
       <c r="X17" s="91" t="s">
@@ -7704,25 +7752,25 @@
         <v>113</v>
       </c>
       <c r="P18" s="97" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="Q18" s="97" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="R18" s="98" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="S18" s="98" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="T18" s="97" t="s">
         <v>150</v>
       </c>
       <c r="U18" s="97" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="V18" s="97" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="W18" s="156"/>
       <c r="X18" s="93" t="s">
@@ -7760,28 +7808,28 @@
       <c r="C19" s="99"/>
       <c r="D19" s="99"/>
       <c r="E19" s="100" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F19" s="100" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G19" s="100" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H19" s="100" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I19" s="100" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="J19" s="100" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="K19" s="100" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="L19" s="100" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="M19" s="100"/>
       <c r="N19" s="101"/>
@@ -7790,17 +7838,17 @@
       </c>
       <c r="P19" s="100"/>
       <c r="Q19" s="100" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="R19" s="100" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="S19" s="100" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="T19" s="100"/>
       <c r="U19" s="100" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="V19" s="100"/>
       <c r="W19" s="157"/>
@@ -7871,7 +7919,7 @@
         <v>141</v>
       </c>
       <c r="AA20" s="88" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AB20" s="90" t="str">
         <f>$E$2</f>
@@ -7881,7 +7929,7 @@
         <v>142</v>
       </c>
       <c r="AD20" s="154" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AE20" s="154"/>
       <c r="AF20" s="90"/>
@@ -7963,7 +8011,7 @@
         <v>142</v>
       </c>
       <c r="AD21" s="154" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AE21" s="154"/>
       <c r="AF21" s="90"/>
@@ -7994,10 +8042,10 @@
         <v>109</v>
       </c>
       <c r="Z22" s="145" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="AA22" s="88" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AB22" s="88" t="s">
         <v>148</v>
@@ -8006,7 +8054,7 @@
         <v>142</v>
       </c>
       <c r="AD22" s="154" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
@@ -8093,7 +8141,7 @@
         <v>MANELC_TECH</v>
       </c>
       <c r="C25" s="142" t="str">
-        <f>PRI_Sector_Fuels!O8</f>
+        <f>PRI_Sector_Fuels!O9</f>
         <v>ELC</v>
       </c>
       <c r="D25" s="154" t="str">
@@ -8342,28 +8390,28 @@
       <c r="C45" s="142"/>
       <c r="D45" s="90"/>
       <c r="E45" s="143" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F45" s="144" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G45" s="144" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H45" s="144" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I45" s="144" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="J45" s="144" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="K45" s="144" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="L45" s="144" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="M45" s="141"/>
       <c r="N45" s="141"/>
@@ -8379,10 +8427,10 @@
         <v>141</v>
       </c>
       <c r="C46" s="142" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D46" s="90" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E46" s="143"/>
       <c r="F46" s="144">
@@ -8408,10 +8456,10 @@
         <v>141</v>
       </c>
       <c r="C47" s="88" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D47" s="88" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F47" s="88">
         <v>0.41136476969163144</v>
@@ -8440,10 +8488,10 @@
         <v>143</v>
       </c>
       <c r="C48" s="88" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D48" s="88" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F48" s="88">
         <v>1</v>
@@ -8597,13 +8645,13 @@
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B6" s="114" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C6" s="114" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="114" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E6" s="114">
         <v>2022</v>
@@ -8626,46 +8674,46 @@
         <v>81</v>
       </c>
       <c r="C7" s="117" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D7" s="117" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E7" s="117" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H7" s="114" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I7" s="114" t="s">
         <v>0</v>
       </c>
       <c r="J7" s="114" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="K7" s="114">
         <v>2022</v>
       </c>
       <c r="M7" s="114" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="N7" s="114" t="s">
         <v>0</v>
       </c>
       <c r="O7" s="114" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P7" s="114">
         <v>2022</v>
       </c>
       <c r="R7" s="114" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="S7" s="114" t="s">
         <v>0</v>
       </c>
       <c r="T7" s="114" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="U7" s="114">
         <v>2022</v>
@@ -8684,7 +8732,7 @@
         <v>81</v>
       </c>
       <c r="I8" s="120" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J8" s="120"/>
       <c r="K8" s="120"/>
@@ -8692,7 +8740,7 @@
         <v>81</v>
       </c>
       <c r="N8" s="120" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="O8" s="120"/>
       <c r="P8" s="120"/>
@@ -8700,17 +8748,17 @@
         <v>81</v>
       </c>
       <c r="S8" s="120" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="T8" s="120"/>
       <c r="U8" s="120"/>
     </row>
     <row r="9" spans="2:21" s="20" customFormat="1" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="175" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C9" s="175" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D9" s="175" t="s">
         <v>148</v>
@@ -8726,7 +8774,7 @@
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="K9" s="9"/>
       <c r="M9" s="9" t="s">
@@ -8734,7 +8782,7 @@
       </c>
       <c r="N9" s="9"/>
       <c r="O9" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P9" s="9"/>
       <c r="R9" s="9" t="s">
@@ -8742,13 +8790,13 @@
       </c>
       <c r="S9" s="9"/>
       <c r="T9" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="U9" s="9"/>
     </row>
     <row r="10" spans="2:21" s="20" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="B10" s="175" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C10" s="175" t="s">
         <v>151</v>
@@ -8763,41 +8811,41 @@
       <c r="F10"/>
       <c r="G10"/>
       <c r="H10" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I10" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J10" s="145" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K10" s="185">
         <v>3.3566276423652626E-2</v>
       </c>
       <c r="L10" s="186"/>
       <c r="M10" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N10" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O10" s="145" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="P10" s="185">
         <v>3.3566276423652626E-2</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S10" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T10" s="145" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="U10" s="185">
         <v>3.3566276423652626E-2</v>
@@ -8805,10 +8853,10 @@
     </row>
     <row r="11" spans="2:21" s="158" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="B11" s="175" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C11" s="175" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D11" s="175" t="s">
         <v>148</v>
@@ -8820,41 +8868,41 @@
       <c r="F11"/>
       <c r="G11"/>
       <c r="H11" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I11" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J11" s="176" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="K11" s="185">
         <v>3.3302706089073604E-2</v>
       </c>
       <c r="L11" s="187"/>
       <c r="M11" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N11" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O11" s="176" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="P11" s="185">
         <v>3.3302706089073604E-2</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S11" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T11" s="176" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="U11" s="185">
         <v>3.3302706089073604E-2</v>
@@ -8866,41 +8914,41 @@
       <c r="D12" s="135"/>
       <c r="E12" s="135"/>
       <c r="H12" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I12" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J12" s="145" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="K12" s="185">
         <v>3.3481814338032219E-2</v>
       </c>
       <c r="L12" s="184"/>
       <c r="M12" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N12" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O12" s="145" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="P12" s="185">
         <v>3.3481814338032219E-2</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S12" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T12" s="145" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="U12" s="185">
         <v>3.3481814338032219E-2</v>
@@ -8908,41 +8956,41 @@
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H13" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I13" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J13" s="176" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="K13" s="185">
         <v>3.3611381763990082E-2</v>
       </c>
       <c r="L13" s="184"/>
       <c r="M13" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N13" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O13" s="176" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="P13" s="185">
         <v>3.3611381763990082E-2</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S13" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T13" s="176" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="U13" s="185">
         <v>3.3611381763990082E-2</v>
@@ -8950,41 +8998,41 @@
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H14" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I14" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J14" s="145" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="K14" s="185">
         <v>3.4004820718610197E-2</v>
       </c>
       <c r="L14" s="184"/>
       <c r="M14" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N14" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O14" s="145" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="P14" s="185">
         <v>3.4004820718610197E-2</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S14" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T14" s="145" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="U14" s="185">
         <v>3.4004820718610197E-2</v>
@@ -8992,41 +9040,41 @@
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H15" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I15" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J15" s="176" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="K15" s="185">
         <v>3.4081384083392653E-2</v>
       </c>
       <c r="L15" s="184"/>
       <c r="M15" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N15" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O15" s="176" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="P15" s="185">
         <v>3.4081384083392653E-2</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S15" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T15" s="176" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="U15" s="185">
         <v>3.4081384083392653E-2</v>
@@ -9034,41 +9082,41 @@
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H16" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I16" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J16" s="145" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="K16" s="185">
         <v>3.3156795624830704E-2</v>
       </c>
       <c r="L16" s="184"/>
       <c r="M16" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N16" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O16" s="145" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="P16" s="185">
         <v>3.3156795624830704E-2</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S16" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T16" s="145" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="U16" s="185">
         <v>3.3156795624830704E-2</v>
@@ -9076,41 +9124,41 @@
     </row>
     <row r="17" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H17" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I17" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J17" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="K17" s="185">
         <v>3.6518070997817571E-2</v>
       </c>
       <c r="L17" s="184"/>
       <c r="M17" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N17" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O17" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="P17" s="185">
         <v>3.6518070997817571E-2</v>
       </c>
       <c r="R17" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S17" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T17" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="U17" s="185">
         <v>3.6518070997817571E-2</v>
@@ -9118,41 +9166,41 @@
     </row>
     <row r="18" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H18" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I18" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J18" s="145" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="K18" s="185">
         <v>4.7257353018906531E-2</v>
       </c>
       <c r="L18" s="184"/>
       <c r="M18" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N18" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O18" s="145" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="P18" s="185">
         <v>4.7257353018906531E-2</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S18" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T18" s="145" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="U18" s="185">
         <v>4.7257353018906531E-2</v>
@@ -9160,41 +9208,41 @@
     </row>
     <row r="19" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H19" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I19" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J19" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="K19" s="185">
         <v>5.6756578785819259E-2</v>
       </c>
       <c r="L19" s="184"/>
       <c r="M19" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N19" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O19" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="P19" s="185">
         <v>5.6756578785819259E-2</v>
       </c>
       <c r="R19" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S19" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T19" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="U19" s="185">
         <v>5.6756578785819259E-2</v>
@@ -9202,41 +9250,41 @@
     </row>
     <row r="20" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H20" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I20" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J20" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="K20" s="185">
         <v>5.5715023853427123E-2</v>
       </c>
       <c r="L20" s="184"/>
       <c r="M20" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N20" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O20" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="P20" s="185">
         <v>5.5715023853427123E-2</v>
       </c>
       <c r="R20" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S20" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T20" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="U20" s="185">
         <v>5.5715023853427123E-2</v>
@@ -9244,41 +9292,41 @@
     </row>
     <row r="21" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H21" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I21" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J21" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="K21" s="185">
         <v>5.6345483069498978E-2</v>
       </c>
       <c r="L21" s="184"/>
       <c r="M21" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N21" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O21" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="P21" s="185">
         <v>5.6345483069498978E-2</v>
       </c>
       <c r="R21" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S21" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T21" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="U21" s="185">
         <v>5.6345483069498978E-2</v>
@@ -9286,41 +9334,41 @@
     </row>
     <row r="22" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H22" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I22" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J22" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="K22" s="185">
         <v>4.8662133827205516E-2</v>
       </c>
       <c r="L22" s="184"/>
       <c r="M22" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N22" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O22" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="P22" s="185">
         <v>4.8662133827205516E-2</v>
       </c>
       <c r="R22" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S22" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T22" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="U22" s="185">
         <v>4.8662133827205516E-2</v>
@@ -9328,41 +9376,41 @@
     </row>
     <row r="23" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H23" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I23" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J23" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="K23" s="185">
         <v>5.0293526586567008E-2</v>
       </c>
       <c r="L23" s="184"/>
       <c r="M23" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N23" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O23" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="P23" s="185">
         <v>5.0293526586567008E-2</v>
       </c>
       <c r="R23" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S23" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T23" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="U23" s="185">
         <v>5.0293526586567008E-2</v>
@@ -9370,41 +9418,41 @@
     </row>
     <row r="24" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H24" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I24" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J24" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="K24" s="185">
         <v>5.2523087098903048E-2</v>
       </c>
       <c r="L24" s="184"/>
       <c r="M24" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N24" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O24" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="P24" s="185">
         <v>5.2523087098903048E-2</v>
       </c>
       <c r="R24" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S24" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T24" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="U24" s="185">
         <v>5.2523087098903048E-2</v>
@@ -9412,41 +9460,41 @@
     </row>
     <row r="25" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H25" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I25" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J25" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="K25" s="185">
         <v>5.4966761848993004E-2</v>
       </c>
       <c r="L25" s="184"/>
       <c r="M25" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N25" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O25" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="P25" s="185">
         <v>5.4966761848993004E-2</v>
       </c>
       <c r="R25" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S25" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T25" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="U25" s="185">
         <v>5.4966761848993004E-2</v>
@@ -9455,41 +9503,41 @@
     <row r="26" spans="4:21" x14ac:dyDescent="0.25">
       <c r="D26" s="109"/>
       <c r="H26" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I26" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J26" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="K26" s="185">
         <v>5.3016988893511453E-2</v>
       </c>
       <c r="L26" s="184"/>
       <c r="M26" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N26" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O26" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="P26" s="185">
         <v>5.3016988893511453E-2</v>
       </c>
       <c r="R26" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S26" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T26" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="U26" s="185">
         <v>5.3016988893511453E-2</v>
@@ -9499,41 +9547,41 @@
       <c r="D27" s="109"/>
       <c r="E27" s="5"/>
       <c r="H27" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I27" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J27" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="K27" s="185">
         <v>4.4273060594597062E-2</v>
       </c>
       <c r="L27" s="184"/>
       <c r="M27" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N27" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O27" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="P27" s="185">
         <v>4.4273060594597062E-2</v>
       </c>
       <c r="R27" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S27" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T27" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="U27" s="185">
         <v>4.4273060594597062E-2</v>
@@ -9544,41 +9592,41 @@
       <c r="E28" s="109"/>
       <c r="F28" s="109"/>
       <c r="H28" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I28" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J28" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K28" s="185">
         <v>3.6258449498494133E-2</v>
       </c>
       <c r="L28" s="184"/>
       <c r="M28" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N28" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O28" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="P28" s="185">
         <v>3.6258449498494133E-2</v>
       </c>
       <c r="R28" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S28" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T28" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="U28" s="185">
         <v>3.6258449498494133E-2</v>
@@ -9589,41 +9637,41 @@
       <c r="E29" s="109"/>
       <c r="F29" s="109"/>
       <c r="H29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I29" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J29" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="K29" s="185">
         <v>3.6040655779430726E-2</v>
       </c>
       <c r="L29" s="184"/>
       <c r="M29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N29" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O29" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="P29" s="185">
         <v>3.6040655779430726E-2</v>
       </c>
       <c r="R29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S29" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T29" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="U29" s="185">
         <v>3.6040655779430726E-2</v>
@@ -9631,41 +9679,41 @@
     </row>
     <row r="30" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H30" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I30" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J30" s="145" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="K30" s="185">
         <v>3.5097781406108856E-2</v>
       </c>
       <c r="L30" s="184"/>
       <c r="M30" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N30" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O30" s="145" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="P30" s="185">
         <v>3.5097781406108856E-2</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S30" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T30" s="145" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="U30" s="185">
         <v>3.5097781406108856E-2</v>
@@ -9673,41 +9721,41 @@
     </row>
     <row r="31" spans="4:21" x14ac:dyDescent="0.25">
       <c r="H31" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I31" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J31" s="176" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="K31" s="185">
         <v>3.482493578674286E-2</v>
       </c>
       <c r="L31" s="184"/>
       <c r="M31" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N31" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O31" s="176" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="P31" s="185">
         <v>3.482493578674286E-2</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S31" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T31" s="176" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="U31" s="185">
         <v>3.482493578674286E-2</v>
@@ -9716,41 +9764,41 @@
     <row r="32" spans="4:21" x14ac:dyDescent="0.25">
       <c r="E32" s="5"/>
       <c r="H32" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I32" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J32" s="145" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="K32" s="185">
         <v>3.2564766705734945E-2</v>
       </c>
       <c r="L32" s="184"/>
       <c r="M32" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N32" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O32" s="145" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="P32" s="185">
         <v>3.2564766705734945E-2</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S32" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T32" s="145" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="U32" s="185">
         <v>3.2564766705734945E-2</v>
@@ -9760,41 +9808,41 @@
       <c r="B33" s="1"/>
       <c r="E33" s="5"/>
       <c r="H33" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I33" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J33" s="176" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="K33" s="185">
         <v>3.3680163206659841E-2</v>
       </c>
       <c r="L33" s="184"/>
       <c r="M33" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N33" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O33" s="176" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="P33" s="185">
         <v>3.3680163206659841E-2</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S33" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T33" s="176" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="U33" s="185">
         <v>3.3680163206659841E-2</v>
@@ -9803,40 +9851,40 @@
     <row r="34" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B34" s="1"/>
       <c r="H34" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I34" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J34" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K34" s="185">
         <v>3.0835149280259575E-2</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N34" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O34" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="P34" s="185">
         <v>3.0835149280259575E-2</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S34" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T34" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="U34" s="185">
         <v>3.0835149280259575E-2</v>
@@ -9844,40 +9892,40 @@
     </row>
     <row r="35" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H35" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I35" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J35" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="K35" s="185">
         <v>3.1306102192535441E-2</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N35" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O35" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="P35" s="185">
         <v>3.1306102192535441E-2</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S35" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T35" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="U35" s="185">
         <v>3.1306102192535441E-2</v>
@@ -9889,40 +9937,40 @@
         <v>97</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I36" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J36" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="K36" s="185">
         <v>3.0732055812390149E-2</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N36" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O36" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="P36" s="185">
         <v>3.0732055812390149E-2</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S36" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T36" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="U36" s="185">
         <v>3.0732055812390149E-2</v>
@@ -9934,40 +9982,40 @@
         <v>98</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I37" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J37" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="K37" s="185">
         <v>3.1026498894933252E-2</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N37" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O37" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="P37" s="185">
         <v>3.1026498894933252E-2</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S37" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T37" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="U37" s="185">
         <v>3.1026498894933252E-2</v>
@@ -9975,40 +10023,40 @@
     </row>
     <row r="38" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H38" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I38" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J38" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K38" s="185">
         <v>3.1056840848101456E-2</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N38" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O38" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="P38" s="185">
         <v>3.1056840848101456E-2</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S38" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T38" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="U38" s="185">
         <v>3.1056840848101456E-2</v>
@@ -10016,40 +10064,40 @@
     </row>
     <row r="39" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H39" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I39" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J39" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="K39" s="185">
         <v>3.1761574865503496E-2</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N39" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O39" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="P39" s="185">
         <v>3.1761574865503496E-2</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S39" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T39" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="U39" s="185">
         <v>3.1761574865503496E-2</v>
@@ -10057,40 +10105,40 @@
     </row>
     <row r="40" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H40" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I40" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J40" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="K40" s="185">
         <v>3.2141299558210122E-2</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N40" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O40" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P40" s="185">
         <v>3.2141299558210122E-2</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S40" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T40" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="U40" s="185">
         <v>3.2141299558210122E-2</v>
@@ -10098,40 +10146,40 @@
     </row>
     <row r="41" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H41" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I41" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J41" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="K41" s="185">
         <v>3.5213642686520726E-2</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N41" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O41" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="P41" s="185">
         <v>3.5213642686520726E-2</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S41" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T41" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="U41" s="185">
         <v>3.5213642686520726E-2</v>
@@ -10139,40 +10187,40 @@
     </row>
     <row r="42" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H42" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I42" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J42" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="K42" s="185">
         <v>5.1117433203485711E-2</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N42" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O42" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P42" s="185">
         <v>5.1117433203485711E-2</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S42" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T42" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="U42" s="185">
         <v>5.1117433203485711E-2</v>
@@ -10180,40 +10228,40 @@
     </row>
     <row r="43" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H43" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I43" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J43" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K43" s="185">
         <v>6.2773677380098022E-2</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N43" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O43" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="P43" s="185">
         <v>6.2773677380098022E-2</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S43" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T43" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="U43" s="185">
         <v>6.2773677380098022E-2</v>
@@ -10221,40 +10269,40 @@
     </row>
     <row r="44" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H44" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I44" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J44" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K44" s="185">
         <v>6.1766758236552227E-2</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N44" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O44" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P44" s="185">
         <v>6.1766758236552227E-2</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S44" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T44" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="U44" s="185">
         <v>6.1766758236552227E-2</v>
@@ -10262,40 +10310,40 @@
     </row>
     <row r="45" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H45" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I45" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J45" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="K45" s="185">
         <v>6.4177423190962854E-2</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N45" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O45" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="P45" s="185">
         <v>6.4177423190962854E-2</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S45" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T45" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="U45" s="185">
         <v>6.4177423190962854E-2</v>
@@ -10303,40 +10351,40 @@
     </row>
     <row r="46" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H46" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I46" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J46" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="K46" s="185">
         <v>5.0829723942040425E-2</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N46" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O46" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="P46" s="185">
         <v>5.0829723942040425E-2</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S46" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T46" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="U46" s="185">
         <v>5.0829723942040425E-2</v>
@@ -10344,40 +10392,40 @@
     </row>
     <row r="47" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H47" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I47" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J47" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="K47" s="185">
         <v>5.4268458827148723E-2</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N47" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O47" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="P47" s="185">
         <v>5.4268458827148723E-2</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S47" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T47" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="U47" s="185">
         <v>5.4268458827148723E-2</v>
@@ -10385,40 +10433,40 @@
     </row>
     <row r="48" spans="2:21" x14ac:dyDescent="0.25">
       <c r="H48" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I48" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J48" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="K48" s="185">
         <v>5.9589636409466136E-2</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N48" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O48" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="P48" s="185">
         <v>5.9589636409466136E-2</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S48" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T48" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="U48" s="185">
         <v>5.9589636409466136E-2</v>
@@ -10426,40 +10474,40 @@
     </row>
     <row r="49" spans="8:21" x14ac:dyDescent="0.25">
       <c r="H49" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I49" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J49" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K49" s="185">
         <v>5.9904363990350699E-2</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N49" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O49" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P49" s="185">
         <v>5.9904363990350699E-2</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S49" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T49" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="U49" s="185">
         <v>5.9904363990350699E-2</v>
@@ -10467,40 +10515,40 @@
     </row>
     <row r="50" spans="8:21" x14ac:dyDescent="0.25">
       <c r="H50" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I50" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J50" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K50" s="185">
         <v>5.4602121019645386E-2</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N50" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O50" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="P50" s="185">
         <v>5.4602121019645386E-2</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S50" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T50" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="U50" s="185">
         <v>5.4602121019645386E-2</v>
@@ -10508,40 +10556,40 @@
     </row>
     <row r="51" spans="8:21" x14ac:dyDescent="0.25">
       <c r="H51" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I51" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J51" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K51" s="185">
         <v>4.095098396869809E-2</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N51" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O51" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="P51" s="185">
         <v>4.095098396869809E-2</v>
       </c>
       <c r="R51" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S51" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T51" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="U51" s="185">
         <v>4.095098396869809E-2</v>
@@ -10549,40 +10597,40 @@
     </row>
     <row r="52" spans="8:21" x14ac:dyDescent="0.25">
       <c r="H52" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I52" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J52" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="K52" s="185">
         <v>3.2728922255458537E-2</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N52" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O52" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="P52" s="185">
         <v>3.2728922255458537E-2</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S52" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T52" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="U52" s="185">
         <v>3.2728922255458537E-2</v>
@@ -10590,40 +10638,40 @@
     </row>
     <row r="53" spans="8:21" x14ac:dyDescent="0.25">
       <c r="H53" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I53" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J53" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K53" s="185">
         <v>3.1731181617130018E-2</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N53" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O53" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="P53" s="185">
         <v>3.1731181617130018E-2</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S53" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T53" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="U53" s="185">
         <v>3.1731181617130018E-2</v>
@@ -10631,40 +10679,40 @@
     </row>
     <row r="54" spans="8:21" x14ac:dyDescent="0.25">
       <c r="H54" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I54" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J54" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K54" s="185">
         <v>3.0924439128636003E-2</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N54" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O54" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P54" s="185">
         <v>3.0924439128636003E-2</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S54" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T54" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="U54" s="185">
         <v>3.0924439128636003E-2</v>
@@ -10672,40 +10720,40 @@
     </row>
     <row r="55" spans="8:21" x14ac:dyDescent="0.25">
       <c r="H55" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I55" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J55" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="K55" s="185">
         <v>3.0529213441903326E-2</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N55" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O55" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P55" s="185">
         <v>3.0529213441903326E-2</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S55" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T55" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="U55" s="185">
         <v>3.0529213441903326E-2</v>
@@ -10713,40 +10761,40 @@
     </row>
     <row r="56" spans="8:21" x14ac:dyDescent="0.25">
       <c r="H56" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I56" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J56" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="K56" s="185">
         <v>2.9792391830107463E-2</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N56" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O56" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="P56" s="185">
         <v>2.9792391830107463E-2</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S56" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T56" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="U56" s="185">
         <v>2.9792391830107463E-2</v>
@@ -10754,40 +10802,40 @@
     </row>
     <row r="57" spans="8:21" x14ac:dyDescent="0.25">
       <c r="H57" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I57" s="1" t="str">
         <f>DemTechs_INDF!Z$6</f>
         <v>MANELC</v>
       </c>
       <c r="J57" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="K57" s="185">
         <v>3.0240107419862172E-2</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N57" s="1" t="str">
         <f>DemTechs_INDF!Z$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O57" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P57" s="185">
         <v>3.0240107419862172E-2</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S57" s="1" t="str">
         <f>DemTechs_INDF!Z$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T57" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="U57" s="185">
         <v>3.0240107419862172E-2</v>
@@ -10822,7 +10870,7 @@
   <sheetData>
     <row r="3" spans="2:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="122" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C3" s="122"/>
       <c r="D3" s="122"/>
@@ -10841,7 +10889,7 @@
     </row>
     <row r="5" spans="2:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B5" s="124" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C5" s="125"/>
     </row>
@@ -10863,7 +10911,7 @@
       </c>
       <c r="F6" s="126" t="str">
         <f>PRI_Sector_Fuels!O8</f>
-        <v>ELC</v>
+        <v>GRIDELC</v>
       </c>
       <c r="G6" s="126"/>
       <c r="H6" s="126"/>
@@ -10874,16 +10922,16 @@
         <v>87</v>
       </c>
       <c r="C7" s="127" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D7" s="127" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E7" s="127" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F7" s="127" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G7" s="127"/>
       <c r="H7" s="127"/>

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A82F354-61C7-4CB9-950D-54B0CAE6AA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0029A0FA-CC64-4EA4-9F3E-7CAF5801D9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EBF TJ" sheetId="144" r:id="rId1"/>
@@ -1558,7 +1558,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="268">
   <si>
     <t>CommName</t>
   </si>
@@ -2491,12 +2491,6 @@
   </si>
   <si>
     <t>Manufacturing Oil-Imported</t>
-  </si>
-  <si>
-    <t>GRIDAGG</t>
-  </si>
-  <si>
-    <t>Grid Electricity to ELC Aggrigator</t>
   </si>
   <si>
     <t xml:space="preserve">Grid Electricity </t>
@@ -6955,8 +6949,8 @@
       </c>
       <c r="C26" s="68"/>
       <c r="D26" s="136" t="str">
-        <f>O$8</f>
-        <v>GRIDELC</v>
+        <f>O9</f>
+        <v>ELC</v>
       </c>
       <c r="E26" s="1">
         <v>2022</v>
@@ -6979,7 +6973,7 @@
         <v>ELCGRID</v>
       </c>
       <c r="P26" s="140" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="Q26" t="s">
         <v>148</v>
@@ -6989,47 +6983,21 @@
       </c>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B27" s="64" t="str">
-        <f>O27</f>
-        <v>GRIDAGG</v>
-      </c>
-      <c r="C27" s="147" t="str">
-        <f>O8</f>
-        <v>GRIDELC</v>
-      </c>
-      <c r="D27" s="136" t="str">
-        <f>O9</f>
-        <v>ELC</v>
-      </c>
-      <c r="E27" s="1">
-        <v>2022</v>
-      </c>
+      <c r="B27" s="64"/>
+      <c r="C27" s="147"/>
+      <c r="D27" s="136"/>
+      <c r="E27" s="1"/>
       <c r="F27" s="138"/>
       <c r="G27" s="138"/>
-      <c r="H27" s="163">
-        <v>0</v>
-      </c>
+      <c r="H27" s="163"/>
       <c r="I27" s="166"/>
-      <c r="J27" s="113">
-        <v>8.76</v>
-      </c>
+      <c r="J27" s="113"/>
       <c r="K27" s="163"/>
-      <c r="M27" s="138" t="s">
-        <v>46</v>
-      </c>
+      <c r="M27" s="138"/>
       <c r="N27" s="138"/>
-      <c r="O27" s="139" t="s">
-        <v>267</v>
-      </c>
-      <c r="P27" s="140" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>148</v>
-      </c>
-      <c r="S27" s="137" t="s">
-        <v>197</v>
-      </c>
+      <c r="O27" s="139"/>
+      <c r="P27" s="140"/>
+      <c r="S27" s="137"/>
     </row>
     <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B28" s="147"/>

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0029A0FA-CC64-4EA4-9F3E-7CAF5801D9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE543AE-9BAE-46B0-92E3-3BB9B23F8145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EBF TJ" sheetId="144" r:id="rId1"/>
@@ -8732,8 +8732,8 @@
         <v>148</v>
       </c>
       <c r="E9" s="47">
-        <f>EBF!E18</f>
-        <v>2605.1202084096003</v>
+        <f>EBF!E18*0.8</f>
+        <v>2084.0961667276802</v>
       </c>
       <c r="F9"/>
       <c r="G9"/>
@@ -8830,8 +8830,8 @@
         <v>148</v>
       </c>
       <c r="E11" s="47">
-        <f>EBF!D18</f>
-        <v>7676.2275585426005</v>
+        <f>EBF!D18*0.56</f>
+        <v>4298.6874327838568</v>
       </c>
       <c r="F11"/>
       <c r="G11"/>

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE543AE-9BAE-46B0-92E3-3BB9B23F8145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BA464A-F1C6-4B2C-83B8-839681BF6F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EBF TJ" sheetId="144" r:id="rId1"/>
@@ -1558,7 +1558,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="270">
   <si>
     <t>CommName</t>
   </si>
@@ -2495,6 +2495,12 @@
   <si>
     <t xml:space="preserve">Grid Electricity </t>
   </si>
+  <si>
+    <t>ELC_AGG</t>
+  </si>
+  <si>
+    <t>Electricity aggrigator</t>
+  </si>
 </sst>
 </file>
 
@@ -2507,7 +2513,7 @@
     <numFmt numFmtId="167" formatCode="0.000000000"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="37" x14ac:knownFonts="1">
+  <fonts count="38" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2738,6 +2744,12 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="7"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="19">
@@ -3115,7 +3127,7 @@
     <xf numFmtId="0" fontId="31" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3472,6 +3484,8 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="16" borderId="0" xfId="9" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="9" applyFont="1"/>
   </cellXfs>
   <cellStyles count="37">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
@@ -3713,13 +3727,13 @@
     <xdr:from>
       <xdr:col>22</xdr:col>
       <xdr:colOff>516548</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>65943</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>3771674</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>142143</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6529,23 +6543,6 @@
       <c r="E9" s="77"/>
       <c r="F9" s="138"/>
       <c r="G9" s="77"/>
-      <c r="M9" s="139" t="s">
-        <v>46</v>
-      </c>
-      <c r="N9" s="139"/>
-      <c r="O9" s="139" t="s">
-        <v>46</v>
-      </c>
-      <c r="P9" s="139" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q9" s="64" t="s">
-        <v>148</v>
-      </c>
-      <c r="R9" s="64"/>
-      <c r="S9" s="137" t="s">
-        <v>197</v>
-      </c>
       <c r="T9" s="64"/>
       <c r="U9" s="64"/>
     </row>
@@ -6949,8 +6946,8 @@
       </c>
       <c r="C26" s="68"/>
       <c r="D26" s="136" t="str">
-        <f>O9</f>
-        <v>ELC</v>
+        <f>O8</f>
+        <v>GRIDELC</v>
       </c>
       <c r="E26" s="1">
         <v>2022</v>
@@ -6993,11 +6990,13 @@
       <c r="I27" s="166"/>
       <c r="J27" s="113"/>
       <c r="K27" s="163"/>
-      <c r="M27" s="138"/>
-      <c r="N27" s="138"/>
-      <c r="O27" s="139"/>
-      <c r="P27" s="140"/>
-      <c r="S27" s="137"/>
+      <c r="M27" s="190"/>
+      <c r="N27" s="190"/>
+      <c r="O27" s="190"/>
+      <c r="P27" s="190"/>
+      <c r="Q27" s="191"/>
+      <c r="R27" s="191"/>
+      <c r="S27" s="190"/>
     </row>
     <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B28" s="147"/>
@@ -7211,7 +7210,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCAE1E4F-5A92-46AB-9A10-74ADD64337C0}">
-  <dimension ref="B1:AF59"/>
+  <dimension ref="B1:AF60"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="88" customWidth="1"/>
@@ -7407,7 +7406,9 @@
         <v>148</v>
       </c>
       <c r="AC5" s="90"/>
-      <c r="AD5" s="90"/>
+      <c r="AD5" s="154" t="s">
+        <v>197</v>
+      </c>
       <c r="AE5" s="90"/>
       <c r="AF5" s="90"/>
     </row>
@@ -7438,7 +7439,9 @@
         <v>148</v>
       </c>
       <c r="AC6" s="90"/>
-      <c r="AD6" s="90"/>
+      <c r="AD6" s="154" t="s">
+        <v>197</v>
+      </c>
       <c r="AE6" s="90"/>
       <c r="AF6" s="90"/>
     </row>
@@ -7479,18 +7482,30 @@
         <v>148</v>
       </c>
       <c r="AC8" s="90"/>
-      <c r="AD8" s="90"/>
+      <c r="AD8" s="154" t="s">
+        <v>197</v>
+      </c>
       <c r="AE8" s="90"/>
       <c r="AF8" s="90"/>
     </row>
     <row r="9" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="X9" s="142"/>
-      <c r="Y9" s="142"/>
-      <c r="Z9" s="142"/>
-      <c r="AA9" s="142"/>
-      <c r="AB9" s="154"/>
-      <c r="AC9" s="90"/>
-      <c r="AD9" s="90"/>
+      <c r="X9" s="139" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y9" s="139"/>
+      <c r="Z9" s="139" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA9" s="139" t="s">
+        <v>263</v>
+      </c>
+      <c r="AB9" s="64" t="s">
+        <v>148</v>
+      </c>
+      <c r="AC9" s="64"/>
+      <c r="AD9" s="137" t="s">
+        <v>197</v>
+      </c>
       <c r="AE9" s="90"/>
       <c r="AF9" s="90"/>
     </row>
@@ -8071,9 +8086,25 @@
         <v>8.76</v>
       </c>
       <c r="V23" s="104"/>
-      <c r="AB23" s="88"/>
-      <c r="AC23" s="88"/>
-      <c r="AD23" s="154"/>
+      <c r="X23" s="190" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y23" s="190"/>
+      <c r="Z23" s="190" t="s">
+        <v>268</v>
+      </c>
+      <c r="AA23" s="190" t="s">
+        <v>269</v>
+      </c>
+      <c r="AB23" s="191" t="s">
+        <v>148</v>
+      </c>
+      <c r="AC23" s="191" t="s">
+        <v>142</v>
+      </c>
+      <c r="AD23" s="190" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="24" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="94" t="str">
@@ -8105,21 +8136,19 @@
     </row>
     <row r="25" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="94" t="str">
-        <f>Z22</f>
-        <v>MANELC_TECH</v>
+        <f>Z23</f>
+        <v>ELC_AGG</v>
       </c>
       <c r="C25" s="142" t="str">
-        <f>PRI_Sector_Fuels!O9</f>
+        <f>PRI_Sector_Fuels!O26</f>
+        <v>ELCGRID</v>
+      </c>
+      <c r="D25" s="154" t="str">
+        <f>Z9</f>
         <v>ELC</v>
       </c>
-      <c r="D25" s="154" t="str">
-        <f>Z6</f>
-        <v>MANELC</v>
-      </c>
       <c r="E25" s="143"/>
-      <c r="F25" s="144">
-        <v>1</v>
-      </c>
+      <c r="F25" s="144"/>
       <c r="G25" s="144"/>
       <c r="H25" s="144"/>
       <c r="I25" s="144"/>
@@ -8141,28 +8170,49 @@
         <v>8.76</v>
       </c>
       <c r="U25" s="104"/>
-      <c r="V25" s="104">
-        <v>1</v>
-      </c>
+      <c r="V25" s="104"/>
       <c r="AB25" s="94"/>
       <c r="AC25" s="94"/>
     </row>
     <row r="26" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="94"/>
-      <c r="C26" s="142"/>
-      <c r="D26" s="154"/>
+      <c r="B26" s="94" t="str">
+        <f>Z22</f>
+        <v>MANELC_TECH</v>
+      </c>
+      <c r="C26" s="142" t="str">
+        <f>DemTechs_INDF!Z9</f>
+        <v>ELC</v>
+      </c>
+      <c r="D26" s="154" t="str">
+        <f>Z6</f>
+        <v>MANELC</v>
+      </c>
       <c r="E26" s="143"/>
-      <c r="F26" s="144"/>
+      <c r="F26" s="144">
+        <v>1</v>
+      </c>
       <c r="G26" s="144"/>
       <c r="H26" s="144"/>
       <c r="I26" s="144"/>
       <c r="J26" s="144"/>
       <c r="K26" s="144"/>
       <c r="L26" s="144"/>
+      <c r="M26" s="141">
+        <v>1</v>
+      </c>
+      <c r="N26" s="141">
+        <v>1</v>
+      </c>
+      <c r="O26" s="141">
+        <v>50</v>
+      </c>
       <c r="R26" s="110"/>
       <c r="S26" s="110"/>
-      <c r="T26" s="110"/>
-      <c r="U26" s="110"/>
+      <c r="T26" s="104">
+        <v>8.76</v>
+      </c>
+      <c r="U26" s="104"/>
+      <c r="V26" s="104"/>
       <c r="AB26" s="94"/>
       <c r="AC26" s="94"/>
     </row>
@@ -8186,32 +8236,33 @@
       <c r="AC27" s="94"/>
     </row>
     <row r="28" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="94"/>
+      <c r="C28" s="142"/>
+      <c r="D28" s="154"/>
+      <c r="E28" s="143"/>
+      <c r="F28" s="144"/>
+      <c r="G28" s="144"/>
+      <c r="H28" s="144"/>
+      <c r="I28" s="144"/>
+      <c r="J28" s="144"/>
+      <c r="K28" s="144"/>
+      <c r="L28" s="144"/>
+      <c r="R28" s="110"/>
+      <c r="S28" s="110"/>
+      <c r="T28" s="110"/>
+      <c r="U28" s="110"/>
       <c r="AB28" s="94"/>
       <c r="AC28" s="94"/>
-      <c r="AD28" s="152"/>
     </row>
     <row r="29" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB29" s="94"/>
       <c r="AC29" s="94"/>
-    </row>
-    <row r="30" spans="2:32" s="110" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="145"/>
-      <c r="C30" s="90"/>
-      <c r="D30" s="90"/>
-      <c r="E30" s="143"/>
-      <c r="F30" s="144"/>
-      <c r="G30" s="144"/>
-      <c r="H30" s="144"/>
-      <c r="I30" s="144"/>
-      <c r="J30" s="144"/>
-      <c r="K30" s="144"/>
-      <c r="L30" s="144"/>
-      <c r="M30" s="141"/>
-      <c r="N30" s="141"/>
-      <c r="O30" s="141"/>
-      <c r="P30" s="141"/>
-      <c r="Q30" s="141"/>
-    </row>
-    <row r="31" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="AD29" s="152"/>
+    </row>
+    <row r="30" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC30" s="94"/>
+    </row>
+    <row r="31" spans="2:32" s="110" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="145"/>
       <c r="C31" s="90"/>
       <c r="D31" s="90"/>
@@ -8232,7 +8283,7 @@
     <row r="32" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B32" s="145"/>
       <c r="C32" s="90"/>
-      <c r="D32" s="142"/>
+      <c r="D32" s="90"/>
       <c r="E32" s="143"/>
       <c r="F32" s="144"/>
       <c r="G32" s="144"/>
@@ -8248,19 +8299,22 @@
       <c r="Q32" s="141"/>
     </row>
     <row r="33" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="E33" s="145"/>
-      <c r="F33" s="106"/>
-      <c r="G33" s="106"/>
-      <c r="H33" s="106"/>
-      <c r="I33" s="106"/>
-      <c r="J33" s="106"/>
-      <c r="K33" s="106"/>
-      <c r="L33" s="106"/>
-      <c r="N33" s="164"/>
-      <c r="Q33" s="164"/>
-      <c r="AB33" s="90"/>
-      <c r="AC33" s="90"/>
-      <c r="AD33" s="151"/>
+      <c r="B33" s="145"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="142"/>
+      <c r="E33" s="143"/>
+      <c r="F33" s="144"/>
+      <c r="G33" s="144"/>
+      <c r="H33" s="144"/>
+      <c r="I33" s="144"/>
+      <c r="J33" s="144"/>
+      <c r="K33" s="144"/>
+      <c r="L33" s="144"/>
+      <c r="M33" s="141"/>
+      <c r="N33" s="141"/>
+      <c r="O33" s="141"/>
+      <c r="P33" s="141"/>
+      <c r="Q33" s="141"/>
     </row>
     <row r="34" spans="2:30" x14ac:dyDescent="0.25">
       <c r="E34" s="145"/>
@@ -8273,10 +8327,9 @@
       <c r="L34" s="106"/>
       <c r="N34" s="164"/>
       <c r="Q34" s="164"/>
-      <c r="Y34" s="110"/>
-      <c r="AA34" s="110"/>
-      <c r="AB34" s="111"/>
-      <c r="AC34" s="111"/>
+      <c r="AB34" s="90"/>
+      <c r="AC34" s="90"/>
+      <c r="AD34" s="151"/>
     </row>
     <row r="35" spans="2:30" x14ac:dyDescent="0.25">
       <c r="E35" s="145"/>
@@ -8287,129 +8340,116 @@
       <c r="J35" s="106"/>
       <c r="K35" s="106"/>
       <c r="L35" s="106"/>
-      <c r="N35" s="107"/>
+      <c r="N35" s="164"/>
       <c r="Q35" s="164"/>
+      <c r="Y35" s="110"/>
+      <c r="AA35" s="110"/>
+      <c r="AB35" s="111"/>
+      <c r="AC35" s="111"/>
     </row>
     <row r="36" spans="2:30" x14ac:dyDescent="0.25">
       <c r="E36" s="145"/>
+      <c r="F36" s="106"/>
+      <c r="G36" s="106"/>
+      <c r="H36" s="106"/>
+      <c r="I36" s="106"/>
+      <c r="J36" s="106"/>
+      <c r="K36" s="106"/>
+      <c r="L36" s="106"/>
       <c r="N36" s="107"/>
-      <c r="O36" s="106"/>
       <c r="Q36" s="164"/>
     </row>
     <row r="37" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B37" s="104"/>
-      <c r="C37" s="88" t="s">
+      <c r="E37" s="145"/>
+      <c r="N37" s="107"/>
+      <c r="O37" s="106"/>
+      <c r="Q37" s="164"/>
+    </row>
+    <row r="38" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B38" s="104"/>
+      <c r="C38" s="88" t="s">
         <v>97</v>
       </c>
-      <c r="N37" s="107"/>
-    </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B38" s="108"/>
-      <c r="C38" s="88" t="s">
+      <c r="N38" s="107"/>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B39" s="108"/>
+      <c r="C39" s="88" t="s">
         <v>98</v>
       </c>
-      <c r="N38" s="107"/>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.25">
       <c r="N39" s="107"/>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="E42" s="21"/>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B44" s="88" t="s">
+    <row r="40" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="N40" s="107"/>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="E43" s="21"/>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B45" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="88" t="s">
+      <c r="C45" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="D44" s="88" t="s">
+      <c r="D45" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="E44" s="88" t="s">
+      <c r="E45" s="88" t="s">
         <v>105</v>
       </c>
-      <c r="F44" s="88" t="s">
+      <c r="F45" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="G44" s="88" t="s">
+      <c r="G45" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="H44" s="88" t="s">
+      <c r="H45" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="I44" s="88" t="s">
+      <c r="I45" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="J44" s="88" t="s">
+      <c r="J45" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="K44" s="88" t="s">
+      <c r="K45" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="L44" s="88" t="s">
+      <c r="L45" s="88" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B45" s="94" t="s">
-        <v>87</v>
-      </c>
-      <c r="C45" s="142"/>
-      <c r="D45" s="90"/>
-      <c r="E45" s="143" t="s">
-        <v>189</v>
-      </c>
-      <c r="F45" s="144" t="s">
-        <v>201</v>
-      </c>
-      <c r="G45" s="144" t="s">
-        <v>201</v>
-      </c>
-      <c r="H45" s="144" t="s">
-        <v>201</v>
-      </c>
-      <c r="I45" s="144" t="s">
-        <v>201</v>
-      </c>
-      <c r="J45" s="144" t="s">
-        <v>201</v>
-      </c>
-      <c r="K45" s="144" t="s">
-        <v>201</v>
-      </c>
-      <c r="L45" s="144" t="s">
-        <v>201</v>
-      </c>
-      <c r="M45" s="141"/>
-      <c r="N45" s="141"/>
-      <c r="O45" s="141"/>
-      <c r="P45" s="141"/>
-      <c r="Q45" s="141"/>
-      <c r="R45" s="141"/>
-      <c r="S45" s="141"/>
-      <c r="T45" s="141"/>
     </row>
     <row r="46" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B46" s="94" t="s">
-        <v>141</v>
-      </c>
-      <c r="C46" s="142" t="s">
-        <v>252</v>
-      </c>
-      <c r="D46" s="90" t="s">
-        <v>240</v>
-      </c>
-      <c r="E46" s="143"/>
-      <c r="F46" s="144">
-        <v>0.59</v>
-      </c>
-      <c r="G46" s="144"/>
-      <c r="H46" s="144"/>
-      <c r="I46" s="144"/>
-      <c r="J46" s="144"/>
-      <c r="K46" s="144"/>
-      <c r="L46" s="144"/>
+        <v>87</v>
+      </c>
+      <c r="C46" s="142"/>
+      <c r="D46" s="90"/>
+      <c r="E46" s="143" t="s">
+        <v>189</v>
+      </c>
+      <c r="F46" s="144" t="s">
+        <v>201</v>
+      </c>
+      <c r="G46" s="144" t="s">
+        <v>201</v>
+      </c>
+      <c r="H46" s="144" t="s">
+        <v>201</v>
+      </c>
+      <c r="I46" s="144" t="s">
+        <v>201</v>
+      </c>
+      <c r="J46" s="144" t="s">
+        <v>201</v>
+      </c>
+      <c r="K46" s="144" t="s">
+        <v>201</v>
+      </c>
+      <c r="L46" s="144" t="s">
+        <v>201</v>
+      </c>
       <c r="M46" s="141"/>
       <c r="N46" s="141"/>
       <c r="O46" s="141"/>
@@ -8420,78 +8460,75 @@
       <c r="T46" s="141"/>
     </row>
     <row r="47" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B47" s="88" t="s">
+      <c r="B47" s="94" t="s">
         <v>141</v>
       </c>
-      <c r="C47" s="88" t="s">
-        <v>253</v>
-      </c>
-      <c r="D47" s="88" t="s">
+      <c r="C47" s="142" t="s">
+        <v>252</v>
+      </c>
+      <c r="D47" s="90" t="s">
         <v>240</v>
       </c>
-      <c r="F47" s="88">
-        <v>0.41136476969163144</v>
-      </c>
-      <c r="G47" s="88">
-        <v>0.23585310113354352</v>
-      </c>
-      <c r="H47" s="88">
-        <v>7.3264515611810618E-2</v>
-      </c>
-      <c r="I47" s="88">
-        <v>1.9847450096360672E-2</v>
-      </c>
-      <c r="J47" s="88">
-        <v>5.1598550415568115E-3</v>
-      </c>
-      <c r="K47" s="88">
-        <v>1.3267245984926927E-3</v>
-      </c>
-      <c r="L47" s="88">
-        <v>3.4015961616990566E-4</v>
-      </c>
+      <c r="E47" s="143"/>
+      <c r="F47" s="144">
+        <v>0.59</v>
+      </c>
+      <c r="G47" s="144"/>
+      <c r="H47" s="144"/>
+      <c r="I47" s="144"/>
+      <c r="J47" s="144"/>
+      <c r="K47" s="144"/>
+      <c r="L47" s="144"/>
+      <c r="M47" s="141"/>
+      <c r="N47" s="141"/>
+      <c r="O47" s="141"/>
+      <c r="P47" s="141"/>
+      <c r="Q47" s="141"/>
+      <c r="R47" s="141"/>
+      <c r="S47" s="141"/>
+      <c r="T47" s="141"/>
     </row>
     <row r="48" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B48" s="88" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C48" s="88" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D48" s="88" t="s">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="F48" s="88">
-        <v>1</v>
+        <v>0.41136476969163144</v>
       </c>
       <c r="G48" s="88">
-        <v>1</v>
+        <v>0.23585310113354352</v>
       </c>
       <c r="H48" s="88">
-        <v>1</v>
+        <v>7.3264515611810618E-2</v>
       </c>
       <c r="I48" s="88">
-        <v>1</v>
+        <v>1.9847450096360672E-2</v>
       </c>
       <c r="J48" s="88">
-        <v>1</v>
+        <v>5.1598550415568115E-3</v>
       </c>
       <c r="K48" s="88">
-        <v>1</v>
+        <v>1.3267245984926927E-3</v>
       </c>
       <c r="L48" s="88">
-        <v>1</v>
+        <v>3.4015961616990566E-4</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B49" s="88" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C49" s="88" t="s">
-        <v>46</v>
+        <v>254</v>
       </c>
       <c r="D49" s="88" t="s">
-        <v>151</v>
+        <v>206</v>
       </c>
       <c r="F49" s="88">
         <v>1</v>
@@ -8516,34 +8553,69 @@
       </c>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="H50" s="178"/>
-      <c r="I50" s="179"/>
-    </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="G53" s="145"/>
-      <c r="I53" s="145"/>
+      <c r="B50" s="88" t="s">
+        <v>151</v>
+      </c>
+      <c r="C50" s="88" t="s">
+        <v>46</v>
+      </c>
+      <c r="D50" s="88" t="s">
+        <v>151</v>
+      </c>
+      <c r="F50" s="88">
+        <v>1</v>
+      </c>
+      <c r="G50" s="88">
+        <v>1</v>
+      </c>
+      <c r="H50" s="88">
+        <v>1</v>
+      </c>
+      <c r="I50" s="88">
+        <v>1</v>
+      </c>
+      <c r="J50" s="88">
+        <v>1</v>
+      </c>
+      <c r="K50" s="88">
+        <v>1</v>
+      </c>
+      <c r="L50" s="88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="H51" s="178"/>
+      <c r="I51" s="179"/>
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.25">
       <c r="G54" s="145"/>
-    </row>
-    <row r="55" spans="2:12" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="H55" s="143"/>
-    </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F56" s="145"/>
-      <c r="G56" s="145"/>
-    </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F58" s="145"/>
+      <c r="I54" s="145"/>
+    </row>
+    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="G55" s="145"/>
+    </row>
+    <row r="56" spans="2:12" s="94" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H56" s="143"/>
+    </row>
+    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="F57" s="145"/>
+      <c r="G57" s="145"/>
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.25">
       <c r="F59" s="145"/>
-      <c r="H59" s="105"/>
+    </row>
+    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="F60" s="145"/>
+      <c r="H60" s="105"/>
     </row>
   </sheetData>
   <phoneticPr fontId="34" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="B24" formula="1"/>
+  </ignoredErrors>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BA464A-F1C6-4B2C-83B8-839681BF6F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE42ACF-D726-4B4A-BA8F-DEE429B9D60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8140,8 +8140,8 @@
         <v>ELC_AGG</v>
       </c>
       <c r="C25" s="142" t="str">
-        <f>PRI_Sector_Fuels!O26</f>
-        <v>ELCGRID</v>
+        <f>PRI_Sector_Fuels!O8</f>
+        <v>GRIDELC</v>
       </c>
       <c r="D25" s="154" t="str">
         <f>Z9</f>

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE42ACF-D726-4B4A-BA8F-DEE429B9D60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600AE320-7C42-4F77-AE12-E71F95FC476A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EBF TJ" sheetId="144" r:id="rId1"/>
@@ -8845,7 +8845,7 @@
         <v>148</v>
       </c>
       <c r="E10" s="47">
-        <f>EBF!J18</f>
+        <f>EBF!J18*1</f>
         <v>2861.5612011470998</v>
       </c>
       <c r="F10"/>

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600AE320-7C42-4F77-AE12-E71F95FC476A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE4AE2F-324B-4925-B4F1-A90FB99D79E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EBF TJ" sheetId="144" r:id="rId1"/>
@@ -1558,7 +1558,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="271">
   <si>
     <t>CommName</t>
   </si>
@@ -2500,6 +2500,9 @@
   </si>
   <si>
     <t>Electricity aggrigator</t>
+  </si>
+  <si>
+    <t>ELE</t>
   </si>
 </sst>
 </file>
@@ -6942,7 +6945,7 @@
     <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B26" s="64" t="str">
         <f>O26</f>
-        <v>ELCGRID</v>
+        <v>ELEGRID</v>
       </c>
       <c r="C26" s="68"/>
       <c r="D26" s="136" t="str">
@@ -6961,13 +6964,13 @@
         <v>8.76</v>
       </c>
       <c r="K26" s="162"/>
-      <c r="M26" t="s">
-        <v>46</v>
+      <c r="M26" s="137" t="s">
+        <v>270</v>
       </c>
       <c r="N26" s="138"/>
       <c r="O26" s="68" t="str">
         <f>$M$26&amp;$C$4</f>
-        <v>ELCGRID</v>
+        <v>ELEGRID</v>
       </c>
       <c r="P26" s="140" t="s">
         <v>267</v>

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE4AE2F-324B-4925-B4F1-A90FB99D79E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C27837-3BEC-429A-80B8-0A862CEB50AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1558,7 +1558,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="267">
   <si>
     <t>CommName</t>
   </si>
@@ -2475,15 +2475,9 @@
     <t>kte</t>
   </si>
   <si>
-    <t>GRIDELC</t>
-  </si>
-  <si>
     <t xml:space="preserve">Electricity from Grid </t>
   </si>
   <si>
-    <t>Aggrigate Electricity</t>
-  </si>
-  <si>
     <t>Manufacturing Coal-Domestic</t>
   </si>
   <si>
@@ -2494,12 +2488,6 @@
   </si>
   <si>
     <t xml:space="preserve">Grid Electricity </t>
-  </si>
-  <si>
-    <t>ELC_AGG</t>
-  </si>
-  <si>
-    <t>Electricity aggrigator</t>
   </si>
   <si>
     <t>ELE</t>
@@ -3730,13 +3718,13 @@
     <xdr:from>
       <xdr:col>22</xdr:col>
       <xdr:colOff>516548</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>65943</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>3771674</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>142143</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6450,7 +6438,7 @@
         <v>198</v>
       </c>
       <c r="P5" s="136" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Q5" s="64" t="s">
         <v>148</v>
@@ -6476,7 +6464,7 @@
         <v>199</v>
       </c>
       <c r="P6" s="136" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q6" s="64" t="s">
         <v>148</v>
@@ -6502,7 +6490,7 @@
         <v>200</v>
       </c>
       <c r="P7" s="136" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="Q7" s="64" t="s">
         <v>148</v>
@@ -6525,10 +6513,10 @@
       </c>
       <c r="N8" s="68"/>
       <c r="O8" s="136" t="s">
+        <v>46</v>
+      </c>
+      <c r="P8" s="136" t="s">
         <v>261</v>
-      </c>
-      <c r="P8" s="136" t="s">
-        <v>262</v>
       </c>
       <c r="Q8" s="64" t="s">
         <v>148</v>
@@ -6950,7 +6938,7 @@
       <c r="C26" s="68"/>
       <c r="D26" s="136" t="str">
         <f>O8</f>
-        <v>GRIDELC</v>
+        <v>ELC</v>
       </c>
       <c r="E26" s="1">
         <v>2022</v>
@@ -6965,7 +6953,7 @@
       </c>
       <c r="K26" s="162"/>
       <c r="M26" s="137" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="N26" s="138"/>
       <c r="O26" s="68" t="str">
@@ -6973,7 +6961,7 @@
         <v>ELEGRID</v>
       </c>
       <c r="P26" s="140" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Q26" t="s">
         <v>148</v>
@@ -7213,7 +7201,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCAE1E4F-5A92-46AB-9A10-74ADD64337C0}">
-  <dimension ref="B1:AF60"/>
+  <dimension ref="B1:AG59"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="88" customWidth="1"/>
@@ -7492,23 +7480,13 @@
       <c r="AF8" s="90"/>
     </row>
     <row r="9" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="X9" s="139" t="s">
-        <v>46</v>
-      </c>
+      <c r="X9" s="139"/>
       <c r="Y9" s="139"/>
-      <c r="Z9" s="139" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA9" s="139" t="s">
-        <v>263</v>
-      </c>
-      <c r="AB9" s="64" t="s">
-        <v>148</v>
-      </c>
+      <c r="Z9" s="139"/>
+      <c r="AA9" s="139"/>
+      <c r="AB9" s="64"/>
       <c r="AC9" s="64"/>
-      <c r="AD9" s="137" t="s">
-        <v>197</v>
-      </c>
+      <c r="AD9" s="137"/>
       <c r="AE9" s="90"/>
       <c r="AF9" s="90"/>
     </row>
@@ -7601,7 +7579,7 @@
       <c r="AE16" s="90"/>
       <c r="AF16" s="90"/>
     </row>
-    <row r="17" spans="2:32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="52" t="s">
         <v>1</v>
       </c>
@@ -7694,7 +7672,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="2:32" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:33" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="97" t="s">
         <v>39</v>
       </c>
@@ -7787,7 +7765,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="2:32" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:33" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="99" t="s">
         <v>87</v>
       </c>
@@ -7850,7 +7828,7 @@
       <c r="AE19" s="93"/>
       <c r="AF19" s="93"/>
     </row>
-    <row r="20" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B20" s="88" t="str">
         <f>Z$20</f>
         <v>Kiln</v>
@@ -7920,7 +7898,7 @@
       <c r="AE20" s="154"/>
       <c r="AF20" s="90"/>
     </row>
-    <row r="21" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B21" s="88" t="str">
         <f>Z$20</f>
         <v>Kiln</v>
@@ -8002,7 +7980,7 @@
       <c r="AE21" s="154"/>
       <c r="AF21" s="90"/>
     </row>
-    <row r="22" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B22" s="88" t="str">
         <f>Z$20</f>
         <v>Kiln</v>
@@ -8043,7 +8021,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="23" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:33" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="94" t="str">
         <f>Z21</f>
         <v>Boiler</v>
@@ -8089,27 +8067,15 @@
         <v>8.76</v>
       </c>
       <c r="V23" s="104"/>
-      <c r="X23" s="190" t="s">
-        <v>46</v>
-      </c>
+      <c r="X23" s="190"/>
       <c r="Y23" s="190"/>
-      <c r="Z23" s="190" t="s">
-        <v>268</v>
-      </c>
-      <c r="AA23" s="190" t="s">
-        <v>269</v>
-      </c>
-      <c r="AB23" s="191" t="s">
-        <v>148</v>
-      </c>
-      <c r="AC23" s="191" t="s">
-        <v>142</v>
-      </c>
-      <c r="AD23" s="190" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="24" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z23" s="190"/>
+      <c r="AA23" s="190"/>
+      <c r="AB23" s="191"/>
+      <c r="AC23" s="191"/>
+      <c r="AD23" s="190"/>
+    </row>
+    <row r="24" spans="2:33" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="94" t="str">
         <f>Z21</f>
         <v>Boiler</v>
@@ -8137,21 +8103,23 @@
       <c r="AB24" s="94"/>
       <c r="AC24" s="94"/>
     </row>
-    <row r="25" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:33" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="94" t="str">
-        <f>Z23</f>
-        <v>ELC_AGG</v>
+        <f>Z22</f>
+        <v>MANELC_TECH</v>
       </c>
       <c r="C25" s="142" t="str">
         <f>PRI_Sector_Fuels!O8</f>
-        <v>GRIDELC</v>
+        <v>ELC</v>
       </c>
       <c r="D25" s="154" t="str">
-        <f>Z9</f>
-        <v>ELC</v>
+        <f>Z6</f>
+        <v>MANELC</v>
       </c>
       <c r="E25" s="143"/>
-      <c r="F25" s="144"/>
+      <c r="F25" s="144">
+        <v>1</v>
+      </c>
       <c r="G25" s="144"/>
       <c r="H25" s="144"/>
       <c r="I25" s="144"/>
@@ -8177,49 +8145,26 @@
       <c r="AB25" s="94"/>
       <c r="AC25" s="94"/>
     </row>
-    <row r="26" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="94" t="str">
-        <f>Z22</f>
-        <v>MANELC_TECH</v>
-      </c>
-      <c r="C26" s="142" t="str">
-        <f>DemTechs_INDF!Z9</f>
-        <v>ELC</v>
-      </c>
-      <c r="D26" s="154" t="str">
-        <f>Z6</f>
-        <v>MANELC</v>
-      </c>
+    <row r="26" spans="2:33" s="141" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="94"/>
+      <c r="C26" s="142"/>
+      <c r="D26" s="154"/>
       <c r="E26" s="143"/>
-      <c r="F26" s="144">
-        <v>1</v>
-      </c>
+      <c r="F26" s="144"/>
       <c r="G26" s="144"/>
       <c r="H26" s="144"/>
       <c r="I26" s="144"/>
       <c r="J26" s="144"/>
       <c r="K26" s="144"/>
       <c r="L26" s="144"/>
-      <c r="M26" s="141">
-        <v>1</v>
-      </c>
-      <c r="N26" s="141">
-        <v>1</v>
-      </c>
-      <c r="O26" s="141">
-        <v>50</v>
-      </c>
       <c r="R26" s="110"/>
       <c r="S26" s="110"/>
-      <c r="T26" s="104">
-        <v>8.76</v>
-      </c>
-      <c r="U26" s="104"/>
-      <c r="V26" s="104"/>
+      <c r="T26" s="110"/>
+      <c r="U26" s="110"/>
       <c r="AB26" s="94"/>
       <c r="AC26" s="94"/>
     </row>
-    <row r="27" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:33" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="94"/>
       <c r="C27" s="142"/>
       <c r="D27" s="154"/>
@@ -8238,34 +8183,44 @@
       <c r="AB27" s="94"/>
       <c r="AC27" s="94"/>
     </row>
-    <row r="28" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="94"/>
-      <c r="C28" s="142"/>
-      <c r="D28" s="154"/>
-      <c r="E28" s="143"/>
-      <c r="F28" s="144"/>
-      <c r="G28" s="144"/>
-      <c r="H28" s="144"/>
-      <c r="I28" s="144"/>
-      <c r="J28" s="144"/>
-      <c r="K28" s="144"/>
-      <c r="L28" s="144"/>
-      <c r="R28" s="110"/>
-      <c r="S28" s="110"/>
-      <c r="T28" s="110"/>
-      <c r="U28" s="110"/>
+    <row r="28" spans="2:33" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AB28" s="94"/>
       <c r="AC28" s="94"/>
-    </row>
-    <row r="29" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="AB29" s="94"/>
+      <c r="AD28" s="152"/>
+    </row>
+    <row r="29" spans="2:33" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AC29" s="94"/>
-      <c r="AD29" s="152"/>
-    </row>
-    <row r="30" spans="2:32" s="141" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="AC30" s="94"/>
-    </row>
-    <row r="31" spans="2:32" s="110" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="2:33" s="141" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="145"/>
+      <c r="C30" s="90"/>
+      <c r="D30" s="90"/>
+      <c r="E30" s="143"/>
+      <c r="F30" s="144"/>
+      <c r="G30" s="144"/>
+      <c r="H30" s="144"/>
+      <c r="I30" s="144"/>
+      <c r="J30" s="144"/>
+      <c r="K30" s="144"/>
+      <c r="L30" s="144"/>
+      <c r="R30" s="110"/>
+      <c r="S30" s="110"/>
+      <c r="T30" s="110"/>
+      <c r="U30" s="110"/>
+      <c r="V30" s="110"/>
+      <c r="W30" s="110"/>
+      <c r="X30" s="110"/>
+      <c r="Y30" s="110"/>
+      <c r="Z30" s="110"/>
+      <c r="AA30" s="110"/>
+      <c r="AB30" s="110"/>
+      <c r="AC30" s="110"/>
+      <c r="AD30" s="110"/>
+      <c r="AE30" s="110"/>
+      <c r="AF30" s="110"/>
+      <c r="AG30" s="110"/>
+    </row>
+    <row r="31" spans="2:33" s="110" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="145"/>
       <c r="C31" s="90"/>
       <c r="D31" s="90"/>
@@ -8282,11 +8237,27 @@
       <c r="O31" s="141"/>
       <c r="P31" s="141"/>
       <c r="Q31" s="141"/>
-    </row>
-    <row r="32" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="R31" s="88"/>
+      <c r="S31" s="88"/>
+      <c r="T31" s="88"/>
+      <c r="U31" s="88"/>
+      <c r="V31" s="88"/>
+      <c r="W31" s="88"/>
+      <c r="X31" s="88"/>
+      <c r="Y31" s="88"/>
+      <c r="Z31" s="88"/>
+      <c r="AA31" s="88"/>
+      <c r="AB31" s="88"/>
+      <c r="AC31" s="88"/>
+      <c r="AD31" s="88"/>
+      <c r="AE31" s="88"/>
+      <c r="AF31" s="88"/>
+      <c r="AG31" s="88"/>
+    </row>
+    <row r="32" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B32" s="145"/>
       <c r="C32" s="90"/>
-      <c r="D32" s="90"/>
+      <c r="D32" s="142"/>
       <c r="E32" s="143"/>
       <c r="F32" s="144"/>
       <c r="G32" s="144"/>
@@ -8302,22 +8273,19 @@
       <c r="Q32" s="141"/>
     </row>
     <row r="33" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B33" s="145"/>
-      <c r="C33" s="90"/>
-      <c r="D33" s="142"/>
-      <c r="E33" s="143"/>
-      <c r="F33" s="144"/>
-      <c r="G33" s="144"/>
-      <c r="H33" s="144"/>
-      <c r="I33" s="144"/>
-      <c r="J33" s="144"/>
-      <c r="K33" s="144"/>
-      <c r="L33" s="144"/>
-      <c r="M33" s="141"/>
-      <c r="N33" s="141"/>
-      <c r="O33" s="141"/>
-      <c r="P33" s="141"/>
-      <c r="Q33" s="141"/>
+      <c r="E33" s="145"/>
+      <c r="F33" s="106"/>
+      <c r="G33" s="106"/>
+      <c r="H33" s="106"/>
+      <c r="I33" s="106"/>
+      <c r="J33" s="106"/>
+      <c r="K33" s="106"/>
+      <c r="L33" s="106"/>
+      <c r="N33" s="164"/>
+      <c r="Q33" s="164"/>
+      <c r="AB33" s="90"/>
+      <c r="AC33" s="90"/>
+      <c r="AD33" s="151"/>
     </row>
     <row r="34" spans="2:30" x14ac:dyDescent="0.25">
       <c r="E34" s="145"/>
@@ -8330,9 +8298,10 @@
       <c r="L34" s="106"/>
       <c r="N34" s="164"/>
       <c r="Q34" s="164"/>
-      <c r="AB34" s="90"/>
-      <c r="AC34" s="90"/>
-      <c r="AD34" s="151"/>
+      <c r="Y34" s="110"/>
+      <c r="AA34" s="110"/>
+      <c r="AB34" s="111"/>
+      <c r="AC34" s="111"/>
     </row>
     <row r="35" spans="2:30" x14ac:dyDescent="0.25">
       <c r="E35" s="145"/>
@@ -8343,116 +8312,129 @@
       <c r="J35" s="106"/>
       <c r="K35" s="106"/>
       <c r="L35" s="106"/>
-      <c r="N35" s="164"/>
+      <c r="N35" s="107"/>
       <c r="Q35" s="164"/>
-      <c r="Y35" s="110"/>
-      <c r="AA35" s="110"/>
-      <c r="AB35" s="111"/>
-      <c r="AC35" s="111"/>
     </row>
     <row r="36" spans="2:30" x14ac:dyDescent="0.25">
       <c r="E36" s="145"/>
-      <c r="F36" s="106"/>
-      <c r="G36" s="106"/>
-      <c r="H36" s="106"/>
-      <c r="I36" s="106"/>
-      <c r="J36" s="106"/>
-      <c r="K36" s="106"/>
-      <c r="L36" s="106"/>
       <c r="N36" s="107"/>
+      <c r="O36" s="106"/>
       <c r="Q36" s="164"/>
     </row>
     <row r="37" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="E37" s="145"/>
+      <c r="B37" s="104"/>
+      <c r="C37" s="88" t="s">
+        <v>97</v>
+      </c>
       <c r="N37" s="107"/>
-      <c r="O37" s="106"/>
-      <c r="Q37" s="164"/>
     </row>
     <row r="38" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B38" s="104"/>
+      <c r="B38" s="108"/>
       <c r="C38" s="88" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N38" s="107"/>
     </row>
     <row r="39" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B39" s="108"/>
-      <c r="C39" s="88" t="s">
-        <v>98</v>
-      </c>
       <c r="N39" s="107"/>
     </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="N40" s="107"/>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="E43" s="21"/>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="E42" s="21"/>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B44" s="88" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="88" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="E44" s="88" t="s">
+        <v>105</v>
+      </c>
+      <c r="F44" s="88" t="s">
+        <v>140</v>
+      </c>
+      <c r="G44" s="88" t="s">
+        <v>140</v>
+      </c>
+      <c r="H44" s="88" t="s">
+        <v>140</v>
+      </c>
+      <c r="I44" s="88" t="s">
+        <v>140</v>
+      </c>
+      <c r="J44" s="88" t="s">
+        <v>140</v>
+      </c>
+      <c r="K44" s="88" t="s">
+        <v>140</v>
+      </c>
+      <c r="L44" s="88" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="45" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B45" s="88" t="s">
-        <v>39</v>
-      </c>
-      <c r="C45" s="88" t="s">
-        <v>32</v>
-      </c>
-      <c r="D45" s="88" t="s">
-        <v>33</v>
-      </c>
-      <c r="E45" s="88" t="s">
-        <v>105</v>
-      </c>
-      <c r="F45" s="88" t="s">
-        <v>140</v>
-      </c>
-      <c r="G45" s="88" t="s">
-        <v>140</v>
-      </c>
-      <c r="H45" s="88" t="s">
-        <v>140</v>
-      </c>
-      <c r="I45" s="88" t="s">
-        <v>140</v>
-      </c>
-      <c r="J45" s="88" t="s">
-        <v>140</v>
-      </c>
-      <c r="K45" s="88" t="s">
-        <v>140</v>
-      </c>
-      <c r="L45" s="88" t="s">
-        <v>140</v>
-      </c>
+      <c r="B45" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="C45" s="142"/>
+      <c r="D45" s="90"/>
+      <c r="E45" s="143" t="s">
+        <v>189</v>
+      </c>
+      <c r="F45" s="144" t="s">
+        <v>201</v>
+      </c>
+      <c r="G45" s="144" t="s">
+        <v>201</v>
+      </c>
+      <c r="H45" s="144" t="s">
+        <v>201</v>
+      </c>
+      <c r="I45" s="144" t="s">
+        <v>201</v>
+      </c>
+      <c r="J45" s="144" t="s">
+        <v>201</v>
+      </c>
+      <c r="K45" s="144" t="s">
+        <v>201</v>
+      </c>
+      <c r="L45" s="144" t="s">
+        <v>201</v>
+      </c>
+      <c r="M45" s="141"/>
+      <c r="N45" s="141"/>
+      <c r="O45" s="141"/>
+      <c r="P45" s="141"/>
+      <c r="Q45" s="141"/>
+      <c r="R45" s="141"/>
+      <c r="S45" s="141"/>
+      <c r="T45" s="141"/>
     </row>
     <row r="46" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B46" s="94" t="s">
-        <v>87</v>
-      </c>
-      <c r="C46" s="142"/>
-      <c r="D46" s="90"/>
-      <c r="E46" s="143" t="s">
-        <v>189</v>
-      </c>
-      <c r="F46" s="144" t="s">
-        <v>201</v>
-      </c>
-      <c r="G46" s="144" t="s">
-        <v>201</v>
-      </c>
-      <c r="H46" s="144" t="s">
-        <v>201</v>
-      </c>
-      <c r="I46" s="144" t="s">
-        <v>201</v>
-      </c>
-      <c r="J46" s="144" t="s">
-        <v>201</v>
-      </c>
-      <c r="K46" s="144" t="s">
-        <v>201</v>
-      </c>
-      <c r="L46" s="144" t="s">
-        <v>201</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C46" s="142" t="s">
+        <v>252</v>
+      </c>
+      <c r="D46" s="90" t="s">
+        <v>240</v>
+      </c>
+      <c r="E46" s="143"/>
+      <c r="F46" s="144">
+        <v>0.59</v>
+      </c>
+      <c r="G46" s="144"/>
+      <c r="H46" s="144"/>
+      <c r="I46" s="144"/>
+      <c r="J46" s="144"/>
+      <c r="K46" s="144"/>
+      <c r="L46" s="144"/>
       <c r="M46" s="141"/>
       <c r="N46" s="141"/>
       <c r="O46" s="141"/>
@@ -8463,75 +8445,78 @@
       <c r="T46" s="141"/>
     </row>
     <row r="47" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B47" s="94" t="s">
+      <c r="B47" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C47" s="142" t="s">
-        <v>252</v>
-      </c>
-      <c r="D47" s="90" t="s">
+      <c r="C47" s="88" t="s">
+        <v>253</v>
+      </c>
+      <c r="D47" s="88" t="s">
         <v>240</v>
       </c>
-      <c r="E47" s="143"/>
-      <c r="F47" s="144">
-        <v>0.59</v>
-      </c>
-      <c r="G47" s="144"/>
-      <c r="H47" s="144"/>
-      <c r="I47" s="144"/>
-      <c r="J47" s="144"/>
-      <c r="K47" s="144"/>
-      <c r="L47" s="144"/>
-      <c r="M47" s="141"/>
-      <c r="N47" s="141"/>
-      <c r="O47" s="141"/>
-      <c r="P47" s="141"/>
-      <c r="Q47" s="141"/>
-      <c r="R47" s="141"/>
-      <c r="S47" s="141"/>
-      <c r="T47" s="141"/>
+      <c r="F47" s="88">
+        <v>0.41136476969163144</v>
+      </c>
+      <c r="G47" s="88">
+        <v>0.23585310113354352</v>
+      </c>
+      <c r="H47" s="88">
+        <v>7.3264515611810618E-2</v>
+      </c>
+      <c r="I47" s="88">
+        <v>1.9847450096360672E-2</v>
+      </c>
+      <c r="J47" s="88">
+        <v>5.1598550415568115E-3</v>
+      </c>
+      <c r="K47" s="88">
+        <v>1.3267245984926927E-3</v>
+      </c>
+      <c r="L47" s="88">
+        <v>3.4015961616990566E-4</v>
+      </c>
     </row>
     <row r="48" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B48" s="88" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C48" s="88" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D48" s="88" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="F48" s="88">
-        <v>0.41136476969163144</v>
+        <v>1</v>
       </c>
       <c r="G48" s="88">
-        <v>0.23585310113354352</v>
+        <v>1</v>
       </c>
       <c r="H48" s="88">
-        <v>7.3264515611810618E-2</v>
+        <v>1</v>
       </c>
       <c r="I48" s="88">
-        <v>1.9847450096360672E-2</v>
+        <v>1</v>
       </c>
       <c r="J48" s="88">
-        <v>5.1598550415568115E-3</v>
+        <v>1</v>
       </c>
       <c r="K48" s="88">
-        <v>1.3267245984926927E-3</v>
+        <v>1</v>
       </c>
       <c r="L48" s="88">
-        <v>3.4015961616990566E-4</v>
-      </c>
-    </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B49" s="88" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C49" s="88" t="s">
-        <v>254</v>
+        <v>46</v>
       </c>
       <c r="D49" s="88" t="s">
-        <v>206</v>
+        <v>151</v>
       </c>
       <c r="F49" s="88">
         <v>1</v>
@@ -8555,62 +8540,91 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B50" s="88" t="s">
-        <v>151</v>
-      </c>
-      <c r="C50" s="88" t="s">
-        <v>46</v>
-      </c>
-      <c r="D50" s="88" t="s">
-        <v>151</v>
-      </c>
-      <c r="F50" s="88">
-        <v>1</v>
-      </c>
-      <c r="G50" s="88">
-        <v>1</v>
-      </c>
-      <c r="H50" s="88">
-        <v>1</v>
-      </c>
-      <c r="I50" s="88">
-        <v>1</v>
-      </c>
-      <c r="J50" s="88">
-        <v>1</v>
-      </c>
-      <c r="K50" s="88">
-        <v>1</v>
-      </c>
-      <c r="L50" s="88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="H51" s="178"/>
-      <c r="I51" s="179"/>
-    </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="H50" s="178"/>
+      <c r="I50" s="179"/>
+    </row>
+    <row r="53" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="G53" s="145"/>
+      <c r="I53" s="145"/>
+    </row>
+    <row r="54" spans="2:33" x14ac:dyDescent="0.25">
       <c r="G54" s="145"/>
-      <c r="I54" s="145"/>
-    </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="G55" s="145"/>
-    </row>
-    <row r="56" spans="2:12" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="H56" s="143"/>
-    </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F57" s="145"/>
-      <c r="G57" s="145"/>
-    </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B55" s="94"/>
+      <c r="C55" s="94"/>
+      <c r="D55" s="94"/>
+      <c r="E55" s="94"/>
+      <c r="F55" s="94"/>
+      <c r="G55" s="94"/>
+      <c r="H55" s="143"/>
+      <c r="I55" s="94"/>
+      <c r="J55" s="94"/>
+      <c r="K55" s="94"/>
+      <c r="L55" s="94"/>
+      <c r="M55" s="94"/>
+      <c r="N55" s="94"/>
+      <c r="O55" s="94"/>
+      <c r="P55" s="94"/>
+      <c r="Q55" s="94"/>
+      <c r="R55" s="94"/>
+      <c r="S55" s="94"/>
+      <c r="T55" s="94"/>
+      <c r="U55" s="94"/>
+      <c r="V55" s="94"/>
+      <c r="W55" s="94"/>
+      <c r="X55" s="94"/>
+      <c r="Y55" s="94"/>
+      <c r="Z55" s="94"/>
+      <c r="AA55" s="94"/>
+      <c r="AB55" s="94"/>
+      <c r="AC55" s="94"/>
+      <c r="AD55" s="94"/>
+      <c r="AE55" s="94"/>
+      <c r="AF55" s="94"/>
+      <c r="AG55" s="94"/>
+    </row>
+    <row r="56" spans="2:33" s="94" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="88"/>
+      <c r="C56" s="88"/>
+      <c r="D56" s="88"/>
+      <c r="E56" s="88"/>
+      <c r="F56" s="145"/>
+      <c r="G56" s="145"/>
+      <c r="H56" s="88"/>
+      <c r="I56" s="88"/>
+      <c r="J56" s="88"/>
+      <c r="K56" s="88"/>
+      <c r="L56" s="88"/>
+      <c r="M56" s="88"/>
+      <c r="N56" s="88"/>
+      <c r="O56" s="88"/>
+      <c r="P56" s="88"/>
+      <c r="Q56" s="88"/>
+      <c r="R56" s="88"/>
+      <c r="S56" s="88"/>
+      <c r="T56" s="88"/>
+      <c r="U56" s="88"/>
+      <c r="V56" s="88"/>
+      <c r="W56" s="88"/>
+      <c r="X56" s="88"/>
+      <c r="Y56" s="88"/>
+      <c r="Z56" s="88"/>
+      <c r="AA56" s="88"/>
+      <c r="AB56" s="88"/>
+      <c r="AC56" s="88"/>
+      <c r="AD56" s="88"/>
+      <c r="AE56" s="88"/>
+      <c r="AF56" s="88"/>
+      <c r="AG56" s="88"/>
+    </row>
+    <row r="58" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="F58" s="145"/>
+    </row>
+    <row r="59" spans="2:33" x14ac:dyDescent="0.25">
       <c r="F59" s="145"/>
-    </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F60" s="145"/>
-      <c r="H60" s="105"/>
+      <c r="H59" s="105"/>
     </row>
   </sheetData>
   <phoneticPr fontId="34" type="noConversion"/>
@@ -10954,7 +10968,7 @@
       </c>
       <c r="F6" s="126" t="str">
         <f>PRI_Sector_Fuels!O8</f>
-        <v>GRIDELC</v>
+        <v>ELC</v>
       </c>
       <c r="G6" s="126"/>
       <c r="H6" s="126"/>

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C27837-3BEC-429A-80B8-0A862CEB50AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F5A482-DD95-41B4-8C88-8CC938C32419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EBF TJ" sheetId="144" r:id="rId1"/>
@@ -7998,7 +7998,7 @@
       <c r="K22" s="102"/>
       <c r="L22" s="102"/>
       <c r="U22" s="104">
-        <v>0.34100000000000003</v>
+        <v>0.34749360000000001</v>
       </c>
       <c r="V22" s="104"/>
       <c r="W22" s="110"/>
@@ -8097,7 +8097,7 @@
       <c r="S24" s="110"/>
       <c r="T24" s="104"/>
       <c r="U24" s="104">
-        <v>0.25900000000000001</v>
+        <v>0.27951480000000001</v>
       </c>
       <c r="V24" s="104"/>
       <c r="AB24" s="94"/>

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F5A482-DD95-41B4-8C88-8CC938C32419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63B9BF33-9F39-4469-B22A-4C00BF649095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EBF TJ" sheetId="144" r:id="rId1"/>
@@ -2504,7 +2504,7 @@
     <numFmt numFmtId="167" formatCode="0.000000000"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="38" x14ac:knownFonts="1">
+  <fonts count="39" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2739,6 +2739,12 @@
     <font>
       <sz val="10"/>
       <color theme="7"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -3118,7 +3124,7 @@
     <xf numFmtId="0" fontId="31" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="193">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3477,6 +3483,7 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="16" borderId="0" xfId="9" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="9" applyFont="1"/>
+    <xf numFmtId="166" fontId="38" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="37">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
@@ -7383,14 +7390,14 @@
       <c r="K5" s="51"/>
       <c r="L5" s="51"/>
       <c r="M5" s="51"/>
-      <c r="X5" s="142" t="s">
+      <c r="X5" s="192" t="s">
         <v>82</v>
       </c>
-      <c r="Y5" s="142"/>
-      <c r="Z5" s="142" t="s">
+      <c r="Y5" s="192"/>
+      <c r="Z5" s="192" t="s">
         <v>206</v>
       </c>
-      <c r="AA5" s="142" t="s">
+      <c r="AA5" s="192" t="s">
         <v>204</v>
       </c>
       <c r="AB5" s="90" t="s">
@@ -7416,14 +7423,14 @@
       <c r="K6" s="51"/>
       <c r="L6" s="51"/>
       <c r="M6" s="51"/>
-      <c r="X6" s="90" t="s">
+      <c r="X6" s="192" t="s">
         <v>82</v>
       </c>
-      <c r="Y6" s="90"/>
-      <c r="Z6" s="90" t="s">
+      <c r="Y6" s="192"/>
+      <c r="Z6" s="192" t="s">
         <v>151</v>
       </c>
-      <c r="AA6" s="90" t="s">
+      <c r="AA6" s="192" t="s">
         <v>196</v>
       </c>
       <c r="AB6" s="90" t="s">
@@ -7437,15 +7444,15 @@
       <c r="AF6" s="90"/>
     </row>
     <row r="7" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="X7" s="90" t="s">
+      <c r="X7" s="192" t="s">
         <v>139</v>
       </c>
-      <c r="Y7" s="90"/>
-      <c r="Z7" s="90" t="str">
+      <c r="Y7" s="192"/>
+      <c r="Z7" s="192" t="str">
         <f>$B$2&amp;EBF!C53</f>
         <v>MANCO2</v>
       </c>
-      <c r="AA7" s="90" t="str">
+      <c r="AA7" s="192" t="str">
         <f>$C$2&amp;" "&amp;EBF!C53</f>
         <v>Manufacturing CO2</v>
       </c>
@@ -7459,14 +7466,14 @@
       <c r="AF7" s="90"/>
     </row>
     <row r="8" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="X8" s="142" t="s">
+      <c r="X8" s="192" t="s">
         <v>82</v>
       </c>
-      <c r="Y8" s="142"/>
-      <c r="Z8" s="142" t="s">
+      <c r="Y8" s="192"/>
+      <c r="Z8" s="192" t="s">
         <v>240</v>
       </c>
-      <c r="AA8" s="142" t="s">
+      <c r="AA8" s="192" t="s">
         <v>205</v>
       </c>
       <c r="AB8" s="154" t="s">

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63B9BF33-9F39-4469-B22A-4C00BF649095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E50D1CEA-9A17-46C2-B23E-5D9F5F44251D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EBF TJ" sheetId="144" r:id="rId1"/>
@@ -2313,81 +2313,6 @@
     <t>ktCO₂/GWh</t>
   </si>
   <si>
-    <r>
-      <t>Share-I~LO</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~2025</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Share-I~LO</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~2030</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Share-I~LO</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~2035</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Share-I~LO</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~2040</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Share-I~LO</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~2045</t>
-    </r>
-  </si>
-  <si>
     <t>CEMENTHEAT</t>
   </si>
   <si>
@@ -2431,21 +2356,6 @@
   </si>
   <si>
     <t>MANOILIMP</t>
-  </si>
-  <si>
-    <r>
-      <t>Share-I~LO</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~2050</t>
-    </r>
   </si>
   <si>
     <r>
@@ -2491,6 +2401,96 @@
   </si>
   <si>
     <t>ELE</t>
+  </si>
+  <si>
+    <r>
+      <t>Share-I~UP</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~2025</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Share-I~UP</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~2030</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Share-I~UP</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~2035</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Share-I~UP</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~2040</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Share-I~UP</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~2045</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Share-I~UP</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~2050</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -5141,13 +5141,13 @@
       </c>
       <c r="K2" s="20"/>
       <c r="O2" s="24" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="P2" s="7" t="s">
         <v>148</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
@@ -6162,7 +6162,7 @@
         <v>121</v>
       </c>
       <c r="C46" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D46" s="109">
         <f>D18/(D18+E18)</f>
@@ -6183,7 +6183,7 @@
         <v>121</v>
       </c>
       <c r="C47" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E47" s="109">
         <f>E18/(D18+E18)</f>
@@ -6204,7 +6204,7 @@
         <v>121</v>
       </c>
       <c r="C48" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="J48" s="109">
         <v>1</v>
@@ -6391,7 +6391,7 @@
     </row>
     <row r="4" spans="2:21" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C4" s="137" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>194</v>
@@ -6445,7 +6445,7 @@
         <v>198</v>
       </c>
       <c r="P5" s="136" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="Q5" s="64" t="s">
         <v>148</v>
@@ -6471,7 +6471,7 @@
         <v>199</v>
       </c>
       <c r="P6" s="136" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="Q6" s="64" t="s">
         <v>148</v>
@@ -6497,7 +6497,7 @@
         <v>200</v>
       </c>
       <c r="P7" s="136" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="Q7" s="64" t="s">
         <v>148</v>
@@ -6523,7 +6523,7 @@
         <v>46</v>
       </c>
       <c r="P8" s="136" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="Q8" s="64" t="s">
         <v>148</v>
@@ -6782,7 +6782,7 @@
         <v>GWh</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="I22" s="8" t="str">
         <f>$E$2</f>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K26" s="162"/>
       <c r="M26" s="137" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="N26" s="138"/>
       <c r="O26" s="68" t="str">
@@ -6968,7 +6968,7 @@
         <v>ELEGRID</v>
       </c>
       <c r="P26" s="140" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="Q26" t="s">
         <v>148</v>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="Y8" s="192"/>
       <c r="Z8" s="192" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AA8" s="192" t="s">
         <v>205</v>
@@ -7600,25 +7600,25 @@
         <v>207</v>
       </c>
       <c r="F17" s="96" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="G17" s="96" t="s">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="H17" s="96" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
       <c r="I17" s="96" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="J17" s="96" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="K17" s="96" t="s">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="L17" s="96" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="M17" s="95" t="s">
         <v>102</v>
@@ -7639,7 +7639,7 @@
         <v>154</v>
       </c>
       <c r="S17" s="95" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="T17" s="95" t="s">
         <v>149</v>
@@ -7648,7 +7648,7 @@
         <v>232</v>
       </c>
       <c r="V17" s="95" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="W17" s="155"/>
       <c r="X17" s="91" t="s">
@@ -7732,7 +7732,7 @@
         <v>156</v>
       </c>
       <c r="S18" s="98" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="T18" s="97" t="s">
         <v>150</v>
@@ -7741,7 +7741,7 @@
         <v>233</v>
       </c>
       <c r="V18" s="97" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="W18" s="156"/>
       <c r="X18" s="93" t="s">
@@ -7809,13 +7809,13 @@
       </c>
       <c r="P19" s="100"/>
       <c r="Q19" s="100" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="R19" s="100" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="S19" s="100" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="T19" s="100"/>
       <c r="U19" s="100" t="s">
@@ -8013,7 +8013,7 @@
         <v>109</v>
       </c>
       <c r="Z22" s="145" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="AA22" s="88" t="s">
         <v>195</v>
@@ -8427,10 +8427,10 @@
         <v>141</v>
       </c>
       <c r="C46" s="142" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D46" s="90" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E46" s="143"/>
       <c r="F46" s="144">
@@ -8456,10 +8456,10 @@
         <v>141</v>
       </c>
       <c r="C47" s="88" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D47" s="88" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F47" s="88">
         <v>0.41136476969163144</v>
@@ -8488,7 +8488,7 @@
         <v>143</v>
       </c>
       <c r="C48" s="88" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D48" s="88" t="s">
         <v>206</v>
@@ -8920,7 +8920,7 @@
         <v>162</v>
       </c>
       <c r="C11" s="175" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D11" s="175" t="s">
         <v>148</v>

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E50D1CEA-9A17-46C2-B23E-5D9F5F44251D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{182492D7-71CC-465A-B995-4A9D270F81C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EBF TJ" sheetId="144" r:id="rId1"/>
@@ -830,7 +830,7 @@
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="X3" authorId="0" shapeId="0" xr:uid="{2A0D7E80-5B80-433D-8263-BA3B897C06A1}">
+    <comment ref="R3" authorId="0" shapeId="0" xr:uid="{2A0D7E80-5B80-433D-8263-BA3B897C06A1}">
       <text>
         <r>
           <rPr>
@@ -944,7 +944,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC3" authorId="1" shapeId="0" xr:uid="{43B8DB13-97B8-4A90-8E0C-84FAE4CBD2EE}">
+    <comment ref="W3" authorId="1" shapeId="0" xr:uid="{43B8DB13-97B8-4A90-8E0C-84FAE4CBD2EE}">
       <text>
         <r>
           <rPr>
@@ -970,7 +970,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD3" authorId="2" shapeId="0" xr:uid="{2086376C-E954-4E0A-86A9-0D188820E5D4}">
+    <comment ref="X3" authorId="2" shapeId="0" xr:uid="{2086376C-E954-4E0A-86A9-0D188820E5D4}">
       <text>
         <r>
           <rPr>
@@ -1043,7 +1043,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE3" authorId="2" shapeId="0" xr:uid="{C18132A6-0DCC-46ED-9E3E-6E9D416748A3}">
+    <comment ref="Y3" authorId="2" shapeId="0" xr:uid="{C18132A6-0DCC-46ED-9E3E-6E9D416748A3}">
       <text>
         <r>
           <rPr>
@@ -1096,7 +1096,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF3" authorId="2" shapeId="0" xr:uid="{EFF6FA36-E1C1-4FF3-A44F-72D97BD59DA1}">
+    <comment ref="Z3" authorId="2" shapeId="0" xr:uid="{EFF6FA36-E1C1-4FF3-A44F-72D97BD59DA1}">
       <text>
         <r>
           <rPr>
@@ -1129,7 +1129,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD17" authorId="2" shapeId="0" xr:uid="{B8BF4189-7AEB-4804-8932-33CB73FCE7E5}">
+    <comment ref="X17" authorId="2" shapeId="0" xr:uid="{B8BF4189-7AEB-4804-8932-33CB73FCE7E5}">
       <text>
         <r>
           <rPr>
@@ -1222,7 +1222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE17" authorId="1" shapeId="0" xr:uid="{5D6B271C-ECB1-4F2A-B44A-CFC55CCC04E5}">
+    <comment ref="Y17" authorId="1" shapeId="0" xr:uid="{5D6B271C-ECB1-4F2A-B44A-CFC55CCC04E5}">
       <text>
         <r>
           <rPr>
@@ -1247,7 +1247,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF17" authorId="2" shapeId="0" xr:uid="{2D72E718-CBF9-42D3-993C-F0AD66976F32}">
+    <comment ref="Z17" authorId="2" shapeId="0" xr:uid="{2D72E718-CBF9-42D3-993C-F0AD66976F32}">
       <text>
         <r>
           <rPr>
@@ -1310,7 +1310,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X18" authorId="2" shapeId="0" xr:uid="{0B963EA5-F116-4DDE-B632-C6029837D6FB}">
+    <comment ref="R18" authorId="2" shapeId="0" xr:uid="{0B963EA5-F116-4DDE-B632-C6029837D6FB}">
       <text>
         <r>
           <rPr>
@@ -1558,7 +1558,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="258">
   <si>
     <t>CommName</t>
   </si>
@@ -2349,15 +2349,6 @@
     <t>% contribution</t>
   </si>
   <si>
-    <t>MANCOALMIN</t>
-  </si>
-  <si>
-    <t>MANCOALIMP</t>
-  </si>
-  <si>
-    <t>MANOILIMP</t>
-  </si>
-  <si>
     <r>
       <t>Share-I~FX</t>
     </r>
@@ -2402,106 +2393,15 @@
   <si>
     <t>ELE</t>
   </si>
-  <si>
-    <r>
-      <t>Share-I~UP</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~2025</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Share-I~UP</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~2030</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Share-I~UP</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~2035</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Share-I~UP</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~2040</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Share-I~UP</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~2045</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Share-I~UP</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~2050</t>
-    </r>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="General_)"/>
     <numFmt numFmtId="166" formatCode="\Te\x\t"/>
-    <numFmt numFmtId="167" formatCode="0.000000000"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
   <fonts count="39" x14ac:knownFonts="1">
@@ -3124,7 +3024,7 @@
     <xf numFmtId="0" fontId="31" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="193">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3465,9 +3365,6 @@
     <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="33" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="9" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="9" fillId="15" borderId="0" xfId="16" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="35" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="29" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="32" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3723,13 +3620,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>516548</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>65943</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>3771674</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>142143</xdr:rowOff>
@@ -5147,7 +5044,7 @@
         <v>148</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
@@ -6391,7 +6288,7 @@
     </row>
     <row r="4" spans="2:21" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C4" s="137" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>194</v>
@@ -6445,7 +6342,7 @@
         <v>198</v>
       </c>
       <c r="P5" s="136" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="Q5" s="64" t="s">
         <v>148</v>
@@ -6471,7 +6368,7 @@
         <v>199</v>
       </c>
       <c r="P6" s="136" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="Q6" s="64" t="s">
         <v>148</v>
@@ -6497,7 +6394,7 @@
         <v>200</v>
       </c>
       <c r="P7" s="136" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q7" s="64" t="s">
         <v>148</v>
@@ -6523,7 +6420,7 @@
         <v>46</v>
       </c>
       <c r="P8" s="136" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="Q8" s="64" t="s">
         <v>148</v>
@@ -6816,10 +6713,10 @@
         <v>2022</v>
       </c>
       <c r="F23" s="137"/>
-      <c r="G23" s="183">
+      <c r="G23" s="180">
         <v>3333333.3</v>
       </c>
-      <c r="H23" s="182">
+      <c r="H23" s="179">
         <v>8.0665446383744062</v>
       </c>
       <c r="I23" s="87"/>
@@ -6951,7 +6848,7 @@
         <v>2022</v>
       </c>
       <c r="F26" s="137"/>
-      <c r="H26" s="182">
+      <c r="H26" s="179">
         <v>100</v>
       </c>
       <c r="I26" s="87"/>
@@ -6960,7 +6857,7 @@
       </c>
       <c r="K26" s="162"/>
       <c r="M26" s="137" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="N26" s="138"/>
       <c r="O26" s="68" t="str">
@@ -6968,7 +6865,7 @@
         <v>ELEGRID</v>
       </c>
       <c r="P26" s="140" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Q26" t="s">
         <v>148</v>
@@ -6988,13 +6885,13 @@
       <c r="I27" s="166"/>
       <c r="J27" s="113"/>
       <c r="K27" s="163"/>
-      <c r="M27" s="190"/>
-      <c r="N27" s="190"/>
-      <c r="O27" s="190"/>
-      <c r="P27" s="190"/>
-      <c r="Q27" s="191"/>
-      <c r="R27" s="191"/>
-      <c r="S27" s="190"/>
+      <c r="M27" s="187"/>
+      <c r="N27" s="187"/>
+      <c r="O27" s="187"/>
+      <c r="P27" s="187"/>
+      <c r="Q27" s="188"/>
+      <c r="R27" s="188"/>
+      <c r="S27" s="187"/>
     </row>
     <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B28" s="147"/>
@@ -7208,7 +7105,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCAE1E4F-5A92-46AB-9A10-74ADD64337C0}">
-  <dimension ref="B1:AG59"/>
+  <dimension ref="B1:AA59"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="88" customWidth="1"/>
@@ -7217,27 +7114,25 @@
     <col min="4" max="4" width="15.88671875" style="88" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="88" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.109375" style="88" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.44140625" style="88" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="13.109375" style="88" customWidth="1"/>
-    <col min="13" max="13" width="12" style="88" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.88671875" style="88" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.109375" style="88" customWidth="1"/>
-    <col min="16" max="16" width="12.109375" style="88" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12" style="88" bestFit="1" customWidth="1"/>
-    <col min="18" max="23" width="8.109375" style="88" customWidth="1"/>
-    <col min="24" max="24" width="12.6640625" style="88" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.109375" style="88" customWidth="1"/>
-    <col min="26" max="26" width="15.88671875" style="88" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="63.88671875" style="88" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.33203125" style="88" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.6640625" style="88" customWidth="1"/>
-    <col min="30" max="30" width="13.44140625" style="88" customWidth="1"/>
-    <col min="31" max="31" width="13.88671875" style="88" customWidth="1"/>
-    <col min="32" max="32" width="8.44140625" style="88" customWidth="1"/>
-    <col min="33" max="16384" width="8.88671875" style="88"/>
+    <col min="7" max="7" width="12" style="88" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.88671875" style="88" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.109375" style="88" customWidth="1"/>
+    <col min="10" max="10" width="12.109375" style="88" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12" style="88" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="8.109375" style="88" customWidth="1"/>
+    <col min="18" max="18" width="12.6640625" style="88" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.109375" style="88" customWidth="1"/>
+    <col min="20" max="20" width="15.88671875" style="88" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="63.88671875" style="88" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.33203125" style="88" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.6640625" style="88" customWidth="1"/>
+    <col min="24" max="24" width="13.44140625" style="88" customWidth="1"/>
+    <col min="25" max="25" width="13.88671875" style="88" customWidth="1"/>
+    <col min="26" max="26" width="8.44140625" style="88" customWidth="1"/>
+    <col min="27" max="16384" width="8.88671875" style="88"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="6" t="s">
         <v>75</v>
       </c>
@@ -7254,17 +7149,11 @@
         <v>79</v>
       </c>
       <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="2:32" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:26" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="str">
         <f>EBF!B18</f>
         <v>MAN</v>
@@ -7286,307 +7175,277 @@
         <v>TH$2024</v>
       </c>
       <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="X2" s="89" t="s">
+      <c r="R2" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="Y2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="90"/>
+      <c r="U2" s="90"/>
+      <c r="V2" s="90"/>
+      <c r="W2" s="90"/>
+      <c r="X2" s="90"/>
+      <c r="Y2" s="90"/>
       <c r="Z2" s="90"/>
-      <c r="AA2" s="90"/>
-      <c r="AB2" s="90"/>
-      <c r="AC2" s="90"/>
-      <c r="AD2" s="90"/>
-      <c r="AE2" s="90"/>
-      <c r="AF2" s="90"/>
-    </row>
-    <row r="3" spans="2:32" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="R3" s="91" t="s">
+        <v>7</v>
+      </c>
+      <c r="S3" s="92" t="s">
+        <v>30</v>
+      </c>
+      <c r="T3" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="U3" s="91" t="s">
+        <v>3</v>
+      </c>
+      <c r="V3" s="91" t="s">
+        <v>4</v>
+      </c>
+      <c r="W3" s="91" t="s">
+        <v>8</v>
+      </c>
       <c r="X3" s="91" t="s">
-        <v>7</v>
-      </c>
-      <c r="Y3" s="92" t="s">
-        <v>30</v>
+        <v>9</v>
+      </c>
+      <c r="Y3" s="91" t="s">
+        <v>10</v>
       </c>
       <c r="Z3" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="91" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB3" s="91" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC3" s="91" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD3" s="91" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE3" s="91" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF3" s="91" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:32" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:26" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
       <c r="D4" s="51"/>
       <c r="E4" s="51"/>
       <c r="F4" s="51"/>
       <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="51"/>
+      <c r="R4" s="93" t="s">
+        <v>37</v>
+      </c>
+      <c r="S4" s="93" t="s">
+        <v>31</v>
+      </c>
+      <c r="T4" s="93" t="s">
+        <v>26</v>
+      </c>
+      <c r="U4" s="93" t="s">
+        <v>27</v>
+      </c>
+      <c r="V4" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="W4" s="93" t="s">
+        <v>40</v>
+      </c>
       <c r="X4" s="93" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="Y4" s="93" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Z4" s="93" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA4" s="93" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB4" s="93" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC4" s="93" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD4" s="93" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE4" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="AF4" s="93" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="51"/>
       <c r="C5" s="51"/>
       <c r="D5" s="51"/>
       <c r="E5" s="51"/>
       <c r="F5" s="51"/>
       <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="51"/>
-      <c r="X5" s="192" t="s">
+      <c r="R5" s="189" t="s">
         <v>82</v>
       </c>
-      <c r="Y5" s="192"/>
-      <c r="Z5" s="192" t="s">
+      <c r="S5" s="189"/>
+      <c r="T5" s="189" t="s">
         <v>206</v>
       </c>
-      <c r="AA5" s="192" t="s">
+      <c r="U5" s="189" t="s">
         <v>204</v>
       </c>
-      <c r="AB5" s="90" t="s">
+      <c r="V5" s="90" t="s">
         <v>148</v>
       </c>
-      <c r="AC5" s="90"/>
-      <c r="AD5" s="154" t="s">
+      <c r="W5" s="90"/>
+      <c r="X5" s="154" t="s">
         <v>197</v>
       </c>
-      <c r="AE5" s="90"/>
-      <c r="AF5" s="90"/>
-    </row>
-    <row r="6" spans="2:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Y5" s="90"/>
+      <c r="Z5" s="90"/>
+    </row>
+    <row r="6" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="51"/>
       <c r="C6" s="51"/>
       <c r="D6" s="51"/>
       <c r="E6" s="51"/>
       <c r="F6" s="51"/>
       <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="X6" s="192" t="s">
+      <c r="R6" s="189" t="s">
         <v>82</v>
       </c>
-      <c r="Y6" s="192"/>
-      <c r="Z6" s="192" t="s">
+      <c r="S6" s="189"/>
+      <c r="T6" s="189" t="s">
         <v>151</v>
       </c>
-      <c r="AA6" s="192" t="s">
+      <c r="U6" s="189" t="s">
         <v>196</v>
       </c>
-      <c r="AB6" s="90" t="s">
+      <c r="V6" s="90" t="s">
         <v>148</v>
       </c>
-      <c r="AC6" s="90"/>
-      <c r="AD6" s="154" t="s">
+      <c r="W6" s="90"/>
+      <c r="X6" s="154" t="s">
         <v>197</v>
       </c>
-      <c r="AE6" s="90"/>
-      <c r="AF6" s="90"/>
-    </row>
-    <row r="7" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="X7" s="192" t="s">
+      <c r="Y6" s="90"/>
+      <c r="Z6" s="90"/>
+    </row>
+    <row r="7" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="R7" s="189" t="s">
         <v>139</v>
       </c>
-      <c r="Y7" s="192"/>
-      <c r="Z7" s="192" t="str">
+      <c r="S7" s="189"/>
+      <c r="T7" s="189" t="str">
         <f>$B$2&amp;EBF!C53</f>
         <v>MANCO2</v>
       </c>
-      <c r="AA7" s="192" t="str">
+      <c r="U7" s="189" t="str">
         <f>$C$2&amp;" "&amp;EBF!C53</f>
         <v>Manufacturing CO2</v>
       </c>
-      <c r="AB7" s="90" t="str">
+      <c r="V7" s="90" t="str">
         <f>EBF!Q2</f>
         <v>kte</v>
       </c>
-      <c r="AC7" s="90"/>
-      <c r="AD7" s="90"/>
-      <c r="AE7" s="90"/>
-      <c r="AF7" s="90"/>
-    </row>
-    <row r="8" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="X8" s="192" t="s">
+      <c r="W7" s="90"/>
+      <c r="X7" s="90"/>
+      <c r="Y7" s="90"/>
+      <c r="Z7" s="90"/>
+    </row>
+    <row r="8" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="R8" s="189" t="s">
         <v>82</v>
       </c>
-      <c r="Y8" s="192"/>
-      <c r="Z8" s="192" t="s">
+      <c r="S8" s="189"/>
+      <c r="T8" s="189" t="s">
         <v>235</v>
       </c>
-      <c r="AA8" s="192" t="s">
+      <c r="U8" s="189" t="s">
         <v>205</v>
       </c>
-      <c r="AB8" s="154" t="s">
+      <c r="V8" s="154" t="s">
         <v>148</v>
       </c>
-      <c r="AC8" s="90"/>
-      <c r="AD8" s="154" t="s">
+      <c r="W8" s="90"/>
+      <c r="X8" s="154" t="s">
         <v>197</v>
       </c>
-      <c r="AE8" s="90"/>
-      <c r="AF8" s="90"/>
-    </row>
-    <row r="9" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="X9" s="139"/>
-      <c r="Y9" s="139"/>
-      <c r="Z9" s="139"/>
-      <c r="AA9" s="139"/>
-      <c r="AB9" s="64"/>
-      <c r="AC9" s="64"/>
-      <c r="AD9" s="137"/>
-      <c r="AE9" s="90"/>
-      <c r="AF9" s="90"/>
-    </row>
-    <row r="10" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="X10" s="165"/>
-      <c r="Y10" s="165"/>
-      <c r="Z10" s="165"/>
-      <c r="AA10" s="165"/>
-      <c r="AB10" s="154"/>
-      <c r="AC10" s="90"/>
-      <c r="AD10" s="90"/>
-      <c r="AE10" s="90"/>
-      <c r="AF10" s="90"/>
-    </row>
-    <row r="11" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="X11" s="154"/>
+      <c r="Y8" s="90"/>
+      <c r="Z8" s="90"/>
+    </row>
+    <row r="9" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="R9" s="139"/>
+      <c r="S9" s="139"/>
+      <c r="T9" s="139"/>
+      <c r="U9" s="139"/>
+      <c r="V9" s="64"/>
+      <c r="W9" s="64"/>
+      <c r="X9" s="137"/>
+      <c r="Y9" s="90"/>
+      <c r="Z9" s="90"/>
+    </row>
+    <row r="10" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="R10" s="165"/>
+      <c r="S10" s="165"/>
+      <c r="T10" s="165"/>
+      <c r="U10" s="165"/>
+      <c r="V10" s="154"/>
+      <c r="W10" s="90"/>
+      <c r="X10" s="90"/>
+      <c r="Y10" s="90"/>
+      <c r="Z10" s="90"/>
+    </row>
+    <row r="11" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="R11" s="154"/>
+      <c r="S11" s="90"/>
+      <c r="T11" s="154"/>
+      <c r="U11" s="154"/>
+      <c r="V11" s="154"/>
+      <c r="W11" s="90"/>
+      <c r="X11" s="90"/>
       <c r="Y11" s="90"/>
-      <c r="Z11" s="154"/>
-      <c r="AA11" s="154"/>
-      <c r="AB11" s="154"/>
-      <c r="AC11" s="90"/>
-      <c r="AD11" s="90"/>
-      <c r="AE11" s="90"/>
-      <c r="AF11" s="90"/>
-    </row>
-    <row r="12" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="X12" s="154"/>
+      <c r="Z11" s="90"/>
+    </row>
+    <row r="12" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="R12" s="154"/>
+      <c r="S12" s="90"/>
+      <c r="T12" s="154"/>
+      <c r="U12" s="154"/>
+      <c r="V12" s="154"/>
+      <c r="W12" s="90"/>
+      <c r="X12" s="90"/>
       <c r="Y12" s="90"/>
-      <c r="Z12" s="154"/>
-      <c r="AA12" s="154"/>
-      <c r="AB12" s="154"/>
-      <c r="AC12" s="90"/>
-      <c r="AD12" s="90"/>
-      <c r="AE12" s="90"/>
-      <c r="AF12" s="90"/>
-    </row>
-    <row r="13" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="X13" s="154"/>
+      <c r="Z12" s="90"/>
+    </row>
+    <row r="13" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="R13" s="154"/>
+      <c r="S13" s="90"/>
+      <c r="T13" s="154"/>
+      <c r="U13" s="154"/>
+      <c r="V13" s="154"/>
+      <c r="W13" s="90"/>
+      <c r="X13" s="90"/>
       <c r="Y13" s="90"/>
-      <c r="Z13" s="154"/>
-      <c r="AA13" s="154"/>
-      <c r="AB13" s="154"/>
-      <c r="AC13" s="90"/>
-      <c r="AD13" s="90"/>
-      <c r="AE13" s="90"/>
-      <c r="AF13" s="90"/>
-    </row>
-    <row r="14" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="X14" s="154"/>
+      <c r="Z13" s="90"/>
+    </row>
+    <row r="14" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="R14" s="154"/>
+      <c r="S14" s="90"/>
+      <c r="T14" s="154"/>
+      <c r="U14" s="154"/>
+      <c r="V14" s="154"/>
+      <c r="W14" s="90"/>
+      <c r="X14" s="90"/>
       <c r="Y14" s="90"/>
-      <c r="Z14" s="154"/>
-      <c r="AA14" s="154"/>
-      <c r="AB14" s="154"/>
-      <c r="AC14" s="90"/>
-      <c r="AD14" s="90"/>
-      <c r="AE14" s="90"/>
-      <c r="AF14" s="90"/>
-    </row>
-    <row r="16" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="Z14" s="90"/>
+    </row>
+    <row r="16" spans="2:26" x14ac:dyDescent="0.25">
       <c r="D16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="N16" s="3"/>
+      <c r="I16" s="94"/>
+      <c r="J16" s="94"/>
+      <c r="K16" s="94"/>
+      <c r="L16" s="94"/>
+      <c r="M16" s="94"/>
+      <c r="N16" s="94"/>
       <c r="O16" s="94"/>
       <c r="P16" s="94"/>
       <c r="Q16" s="94"/>
-      <c r="R16" s="94"/>
-      <c r="S16" s="94"/>
-      <c r="T16" s="94"/>
-      <c r="U16" s="94"/>
-      <c r="V16" s="94"/>
-      <c r="W16" s="94"/>
-      <c r="X16" s="89" t="s">
+      <c r="R16" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="Y16" s="89"/>
+      <c r="S16" s="89"/>
+      <c r="T16" s="90"/>
+      <c r="U16" s="90"/>
+      <c r="V16" s="90"/>
+      <c r="W16" s="90"/>
+      <c r="X16" s="90"/>
+      <c r="Y16" s="90"/>
       <c r="Z16" s="90"/>
-      <c r="AA16" s="90"/>
-      <c r="AB16" s="90"/>
-      <c r="AC16" s="90"/>
-      <c r="AD16" s="90"/>
-      <c r="AE16" s="90"/>
-      <c r="AF16" s="90"/>
-    </row>
-    <row r="17" spans="2:33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="2:27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="52" t="s">
         <v>1</v>
       </c>
@@ -7600,86 +7459,68 @@
         <v>207</v>
       </c>
       <c r="F17" s="96" t="s">
-        <v>250</v>
-      </c>
-      <c r="G17" s="96" t="s">
-        <v>261</v>
-      </c>
-      <c r="H17" s="96" t="s">
-        <v>262</v>
-      </c>
-      <c r="I17" s="96" t="s">
-        <v>263</v>
-      </c>
-      <c r="J17" s="96" t="s">
-        <v>264</v>
-      </c>
-      <c r="K17" s="96" t="s">
-        <v>265</v>
-      </c>
-      <c r="L17" s="96" t="s">
-        <v>266</v>
+        <v>247</v>
+      </c>
+      <c r="G17" s="95" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" s="95" t="s">
+        <v>103</v>
+      </c>
+      <c r="I17" s="95" t="s">
+        <v>104</v>
+      </c>
+      <c r="J17" s="95" t="s">
+        <v>202</v>
+      </c>
+      <c r="K17" s="95" t="s">
+        <v>153</v>
+      </c>
+      <c r="L17" s="95" t="s">
+        <v>154</v>
       </c>
       <c r="M17" s="95" t="s">
-        <v>102</v>
+        <v>242</v>
       </c>
       <c r="N17" s="95" t="s">
-        <v>103</v>
+        <v>149</v>
       </c>
       <c r="O17" s="95" t="s">
-        <v>104</v>
+        <v>232</v>
       </c>
       <c r="P17" s="95" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q17" s="95" t="s">
-        <v>153</v>
-      </c>
-      <c r="R17" s="95" t="s">
-        <v>154</v>
-      </c>
-      <c r="S17" s="95" t="s">
-        <v>242</v>
-      </c>
-      <c r="T17" s="95" t="s">
-        <v>149</v>
-      </c>
-      <c r="U17" s="95" t="s">
-        <v>232</v>
-      </c>
-      <c r="V17" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="W17" s="155"/>
+      <c r="Q17" s="155"/>
+      <c r="R17" s="91" t="s">
+        <v>11</v>
+      </c>
+      <c r="S17" s="92" t="s">
+        <v>30</v>
+      </c>
+      <c r="T17" s="91" t="s">
+        <v>1</v>
+      </c>
+      <c r="U17" s="91" t="s">
+        <v>2</v>
+      </c>
+      <c r="V17" s="91" t="s">
+        <v>16</v>
+      </c>
+      <c r="W17" s="91" t="s">
+        <v>17</v>
+      </c>
       <c r="X17" s="91" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y17" s="92" t="s">
-        <v>30</v>
+        <v>18</v>
+      </c>
+      <c r="Y17" s="91" t="s">
+        <v>19</v>
       </c>
       <c r="Z17" s="91" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="91" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB17" s="91" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC17" s="91" t="s">
-        <v>17</v>
-      </c>
-      <c r="AD17" s="91" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE17" s="91" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF17" s="91" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="2:33" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:27" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="97" t="s">
         <v>39</v>
       </c>
@@ -7696,83 +7537,65 @@
         <v>140</v>
       </c>
       <c r="G18" s="97" t="s">
-        <v>140</v>
-      </c>
-      <c r="H18" s="97" t="s">
-        <v>140</v>
+        <v>106</v>
+      </c>
+      <c r="H18" s="98" t="s">
+        <v>107</v>
       </c>
       <c r="I18" s="97" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="J18" s="97" t="s">
-        <v>140</v>
+        <v>203</v>
       </c>
       <c r="K18" s="97" t="s">
-        <v>140</v>
-      </c>
-      <c r="L18" s="97" t="s">
-        <v>140</v>
-      </c>
-      <c r="M18" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="N18" s="98" t="s">
-        <v>107</v>
+        <v>155</v>
+      </c>
+      <c r="L18" s="98" t="s">
+        <v>156</v>
+      </c>
+      <c r="M18" s="98" t="s">
+        <v>243</v>
+      </c>
+      <c r="N18" s="97" t="s">
+        <v>150</v>
       </c>
       <c r="O18" s="97" t="s">
-        <v>113</v>
+        <v>233</v>
       </c>
       <c r="P18" s="97" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q18" s="97" t="s">
-        <v>155</v>
-      </c>
-      <c r="R18" s="98" t="s">
-        <v>156</v>
-      </c>
-      <c r="S18" s="98" t="s">
-        <v>243</v>
-      </c>
-      <c r="T18" s="97" t="s">
-        <v>150</v>
-      </c>
-      <c r="U18" s="97" t="s">
-        <v>233</v>
-      </c>
-      <c r="V18" s="97" t="s">
         <v>246</v>
       </c>
-      <c r="W18" s="156"/>
+      <c r="Q18" s="156"/>
+      <c r="R18" s="93" t="s">
+        <v>38</v>
+      </c>
+      <c r="S18" s="93" t="s">
+        <v>31</v>
+      </c>
+      <c r="T18" s="93" t="s">
+        <v>21</v>
+      </c>
+      <c r="U18" s="93" t="s">
+        <v>22</v>
+      </c>
+      <c r="V18" s="93" t="s">
+        <v>23</v>
+      </c>
+      <c r="W18" s="93" t="s">
+        <v>24</v>
+      </c>
       <c r="X18" s="93" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="Y18" s="93" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Z18" s="93" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA18" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB18" s="93" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC18" s="93" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD18" s="93" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE18" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF18" s="93" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="2:33" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:27" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="99" t="s">
         <v>87</v>
       </c>
@@ -7784,60 +7607,42 @@
       <c r="F19" s="100" t="s">
         <v>201</v>
       </c>
-      <c r="G19" s="100" t="s">
-        <v>201</v>
-      </c>
-      <c r="H19" s="100" t="s">
-        <v>201</v>
-      </c>
+      <c r="G19" s="100"/>
+      <c r="H19" s="101"/>
       <c r="I19" s="100" t="s">
-        <v>201</v>
-      </c>
-      <c r="J19" s="100" t="s">
-        <v>201</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="J19" s="100"/>
       <c r="K19" s="100" t="s">
-        <v>201</v>
+        <v>241</v>
       </c>
       <c r="L19" s="100" t="s">
-        <v>201</v>
-      </c>
-      <c r="M19" s="100"/>
-      <c r="N19" s="101"/>
+        <v>244</v>
+      </c>
+      <c r="M19" s="100" t="s">
+        <v>249</v>
+      </c>
+      <c r="N19" s="100"/>
       <c r="O19" s="100" t="s">
-        <v>108</v>
+        <v>234</v>
       </c>
       <c r="P19" s="100"/>
-      <c r="Q19" s="100" t="s">
-        <v>241</v>
-      </c>
-      <c r="R19" s="100" t="s">
-        <v>244</v>
-      </c>
-      <c r="S19" s="100" t="s">
-        <v>252</v>
-      </c>
-      <c r="T19" s="100"/>
-      <c r="U19" s="100" t="s">
-        <v>234</v>
-      </c>
-      <c r="V19" s="100"/>
-      <c r="W19" s="157"/>
-      <c r="X19" s="93" t="s">
+      <c r="Q19" s="157"/>
+      <c r="R19" s="93" t="s">
         <v>81</v>
       </c>
+      <c r="S19" s="93"/>
+      <c r="T19" s="93"/>
+      <c r="U19" s="93"/>
+      <c r="V19" s="93"/>
+      <c r="W19" s="93"/>
+      <c r="X19" s="93"/>
       <c r="Y19" s="93"/>
       <c r="Z19" s="93"/>
-      <c r="AA19" s="93"/>
-      <c r="AB19" s="93"/>
-      <c r="AC19" s="93"/>
-      <c r="AD19" s="93"/>
-      <c r="AE19" s="93"/>
-      <c r="AF19" s="93"/>
-    </row>
-    <row r="20" spans="2:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B20" s="88" t="str">
-        <f>Z$20</f>
+        <f>T$20</f>
         <v>Kiln</v>
       </c>
       <c r="C20" s="88" t="str">
@@ -7845,69 +7650,63 @@
         <v>MANCOALMIN</v>
       </c>
       <c r="D20" s="90" t="str">
-        <f>Z8</f>
+        <f>T8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="E20" s="105"/>
       <c r="F20" s="102">
         <v>0.59</v>
       </c>
-      <c r="G20" s="180"/>
-      <c r="H20" s="180"/>
-      <c r="I20" s="180"/>
-      <c r="J20" s="180"/>
-      <c r="K20" s="180"/>
-      <c r="L20" s="180"/>
-      <c r="M20" s="103">
+      <c r="G20" s="103">
         <v>0.55600000000000005</v>
       </c>
-      <c r="N20" s="103">
+      <c r="H20" s="103">
         <v>1</v>
       </c>
-      <c r="O20" s="121">
+      <c r="I20" s="121">
         <v>25</v>
       </c>
-      <c r="P20" s="121"/>
-      <c r="Q20" s="188">
+      <c r="J20" s="121"/>
+      <c r="K20" s="185">
         <v>628.9</v>
       </c>
-      <c r="R20" s="189">
+      <c r="L20" s="186">
         <v>4.46</v>
       </c>
-      <c r="S20" s="189">
+      <c r="M20" s="186">
         <v>0.45</v>
       </c>
-      <c r="T20" s="104">
+      <c r="N20" s="104">
         <v>8.76</v>
       </c>
-      <c r="U20" s="104"/>
-      <c r="V20" s="104"/>
-      <c r="W20" s="110"/>
-      <c r="X20" s="145" t="s">
+      <c r="O20" s="104"/>
+      <c r="P20" s="104"/>
+      <c r="Q20" s="110"/>
+      <c r="R20" s="145" t="s">
         <v>109</v>
       </c>
-      <c r="Z20" s="88" t="s">
+      <c r="T20" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="AA20" s="88" t="s">
+      <c r="U20" s="88" t="s">
         <v>190</v>
       </c>
-      <c r="AB20" s="90" t="str">
+      <c r="V20" s="90" t="str">
         <f>$E$2</f>
         <v>GWh</v>
       </c>
-      <c r="AC20" s="90" t="s">
+      <c r="W20" s="90" t="s">
         <v>142</v>
       </c>
-      <c r="AD20" s="154" t="s">
+      <c r="X20" s="154" t="s">
         <v>197</v>
       </c>
-      <c r="AE20" s="154"/>
-      <c r="AF20" s="90"/>
-    </row>
-    <row r="21" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="Y20" s="154"/>
+      <c r="Z20" s="90"/>
+    </row>
+    <row r="21" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B21" s="88" t="str">
-        <f>Z$20</f>
+        <f>T$20</f>
         <v>Kiln</v>
       </c>
       <c r="C21" s="88" t="str">
@@ -7915,122 +7714,98 @@
         <v>MANCOALIMP</v>
       </c>
       <c r="D21" s="90" t="str">
-        <f>Z$8</f>
+        <f>T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="E21" s="105"/>
       <c r="F21" s="109">
         <v>0.41136476969163144</v>
       </c>
-      <c r="G21" s="109">
-        <v>0.25</v>
-      </c>
-      <c r="H21" s="109">
-        <v>0.25</v>
-      </c>
-      <c r="I21" s="109">
-        <v>0.25</v>
-      </c>
-      <c r="J21" s="109">
-        <v>0.25</v>
-      </c>
-      <c r="K21" s="109">
-        <v>0.25</v>
-      </c>
-      <c r="L21" s="109">
-        <v>0.25</v>
-      </c>
-      <c r="M21" s="103">
+      <c r="G21" s="103">
         <v>0.55600000000000005</v>
       </c>
-      <c r="N21" s="103">
+      <c r="H21" s="103">
         <v>1</v>
       </c>
-      <c r="O21" s="121">
+      <c r="I21" s="121">
         <v>25</v>
       </c>
-      <c r="P21" s="121"/>
-      <c r="Q21" s="188">
+      <c r="J21" s="121"/>
+      <c r="K21" s="185">
         <v>628.9</v>
       </c>
-      <c r="R21" s="189">
+      <c r="L21" s="186">
         <v>4.46</v>
       </c>
-      <c r="S21" s="189">
+      <c r="M21" s="186">
         <v>0.45</v>
       </c>
-      <c r="T21" s="104">
+      <c r="N21" s="104">
         <v>8.76</v>
       </c>
-      <c r="U21" s="104"/>
-      <c r="V21" s="104"/>
-      <c r="W21" s="110"/>
-      <c r="X21" s="145" t="s">
+      <c r="O21" s="104"/>
+      <c r="P21" s="104"/>
+      <c r="Q21" s="110"/>
+      <c r="R21" s="145" t="s">
         <v>109</v>
       </c>
-      <c r="Z21" s="88" t="s">
+      <c r="T21" s="88" t="s">
         <v>143</v>
       </c>
-      <c r="AA21" s="88" t="s">
+      <c r="U21" s="88" t="s">
         <v>144</v>
       </c>
-      <c r="AB21" s="90" t="str">
+      <c r="V21" s="90" t="str">
         <f>$E$2</f>
         <v>GWh</v>
       </c>
-      <c r="AC21" s="90" t="s">
+      <c r="W21" s="90" t="s">
         <v>142</v>
       </c>
-      <c r="AD21" s="154" t="s">
+      <c r="X21" s="154" t="s">
         <v>197</v>
       </c>
-      <c r="AE21" s="154"/>
-      <c r="AF21" s="90"/>
-    </row>
-    <row r="22" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="Y21" s="154"/>
+      <c r="Z21" s="90"/>
+    </row>
+    <row r="22" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B22" s="88" t="str">
-        <f>Z$20</f>
+        <f>T$20</f>
         <v>Kiln</v>
       </c>
       <c r="D22" s="90" t="str">
-        <f>Z$7</f>
+        <f>T$7</f>
         <v>MANCO2</v>
       </c>
       <c r="E22" s="105"/>
       <c r="F22" s="102"/>
-      <c r="G22" s="102"/>
-      <c r="H22" s="102"/>
-      <c r="I22" s="102"/>
-      <c r="J22" s="102"/>
-      <c r="K22" s="102"/>
-      <c r="L22" s="102"/>
-      <c r="U22" s="104">
+      <c r="O22" s="104">
         <v>0.34749360000000001</v>
       </c>
-      <c r="V22" s="104"/>
-      <c r="W22" s="110"/>
-      <c r="X22" s="88" t="s">
+      <c r="P22" s="104"/>
+      <c r="Q22" s="110"/>
+      <c r="R22" s="88" t="s">
         <v>109</v>
       </c>
-      <c r="Z22" s="145" t="s">
-        <v>251</v>
-      </c>
-      <c r="AA22" s="88" t="s">
+      <c r="T22" s="145" t="s">
+        <v>248</v>
+      </c>
+      <c r="U22" s="88" t="s">
         <v>195</v>
       </c>
-      <c r="AB22" s="88" t="s">
+      <c r="V22" s="88" t="s">
         <v>148</v>
       </c>
-      <c r="AC22" s="88" t="s">
+      <c r="W22" s="88" t="s">
         <v>142</v>
       </c>
-      <c r="AD22" s="154" t="s">
+      <c r="X22" s="154" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="23" spans="2:33" s="141" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:27" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="94" t="str">
-        <f>Z21</f>
+        <f>T21</f>
         <v>Boiler</v>
       </c>
       <c r="C23" s="142" t="str">
@@ -8038,81 +7813,69 @@
         <v>MANOILIMP</v>
       </c>
       <c r="D23" s="90" t="str">
-        <f>Z5</f>
+        <f>T5</f>
         <v>MANHEAT</v>
       </c>
       <c r="E23" s="105"/>
       <c r="F23" s="144">
         <v>1</v>
       </c>
-      <c r="G23" s="144"/>
-      <c r="H23" s="144"/>
-      <c r="I23" s="144"/>
-      <c r="J23" s="144"/>
-      <c r="K23" s="144"/>
-      <c r="L23" s="144"/>
-      <c r="M23" s="103">
+      <c r="G23" s="103">
         <v>0.8</v>
       </c>
-      <c r="N23" s="105">
+      <c r="H23" s="105">
         <v>1</v>
       </c>
-      <c r="O23" s="104">
+      <c r="I23" s="104">
         <v>25</v>
       </c>
-      <c r="P23" s="121"/>
-      <c r="Q23" s="188">
+      <c r="J23" s="121"/>
+      <c r="K23" s="185">
         <v>62.9</v>
       </c>
-      <c r="R23" s="189">
+      <c r="L23" s="186">
         <v>2.2999999999999998</v>
       </c>
-      <c r="S23" s="189">
+      <c r="M23" s="186">
         <v>1.82</v>
       </c>
-      <c r="T23" s="104">
+      <c r="N23" s="104">
         <v>8.76</v>
       </c>
-      <c r="V23" s="104"/>
-      <c r="X23" s="190"/>
-      <c r="Y23" s="190"/>
-      <c r="Z23" s="190"/>
-      <c r="AA23" s="190"/>
-      <c r="AB23" s="191"/>
-      <c r="AC23" s="191"/>
-      <c r="AD23" s="190"/>
-    </row>
-    <row r="24" spans="2:33" s="141" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P23" s="104"/>
+      <c r="R23" s="187"/>
+      <c r="S23" s="187"/>
+      <c r="T23" s="187"/>
+      <c r="U23" s="187"/>
+      <c r="V23" s="188"/>
+      <c r="W23" s="188"/>
+      <c r="X23" s="187"/>
+    </row>
+    <row r="24" spans="2:27" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="94" t="str">
-        <f>Z21</f>
+        <f>T21</f>
         <v>Boiler</v>
       </c>
       <c r="C24" s="142"/>
       <c r="D24" s="154" t="str">
-        <f>Z7</f>
+        <f>T7</f>
         <v>MANCO2</v>
       </c>
       <c r="E24" s="143"/>
       <c r="F24" s="144"/>
-      <c r="G24" s="144"/>
-      <c r="H24" s="144"/>
-      <c r="I24" s="144"/>
-      <c r="J24" s="144"/>
-      <c r="K24" s="144"/>
-      <c r="L24" s="144"/>
-      <c r="R24" s="110"/>
-      <c r="S24" s="110"/>
-      <c r="T24" s="104"/>
-      <c r="U24" s="104">
+      <c r="L24" s="110"/>
+      <c r="M24" s="110"/>
+      <c r="N24" s="104"/>
+      <c r="O24" s="104">
         <v>0.27951480000000001</v>
       </c>
-      <c r="V24" s="104"/>
-      <c r="AB24" s="94"/>
-      <c r="AC24" s="94"/>
-    </row>
-    <row r="25" spans="2:33" s="141" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P24" s="104"/>
+      <c r="V24" s="94"/>
+      <c r="W24" s="94"/>
+    </row>
+    <row r="25" spans="2:27" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="94" t="str">
-        <f>Z22</f>
+        <f>T22</f>
         <v>MANELC_TECH</v>
       </c>
       <c r="C25" s="142" t="str">
@@ -8120,96 +7883,78 @@
         <v>ELC</v>
       </c>
       <c r="D25" s="154" t="str">
-        <f>Z6</f>
+        <f>T6</f>
         <v>MANELC</v>
       </c>
       <c r="E25" s="143"/>
       <c r="F25" s="144">
         <v>1</v>
       </c>
-      <c r="G25" s="144"/>
-      <c r="H25" s="144"/>
-      <c r="I25" s="144"/>
-      <c r="J25" s="144"/>
-      <c r="K25" s="144"/>
-      <c r="L25" s="144"/>
-      <c r="M25" s="141">
+      <c r="G25" s="141">
         <v>1</v>
       </c>
-      <c r="N25" s="141">
+      <c r="H25" s="141">
         <v>1</v>
       </c>
-      <c r="O25" s="141">
+      <c r="I25" s="141">
         <v>50</v>
       </c>
-      <c r="R25" s="110"/>
-      <c r="S25" s="110"/>
-      <c r="T25" s="104">
+      <c r="L25" s="110"/>
+      <c r="M25" s="110"/>
+      <c r="N25" s="104">
         <v>8.76</v>
       </c>
-      <c r="U25" s="104"/>
-      <c r="V25" s="104"/>
-      <c r="AB25" s="94"/>
-      <c r="AC25" s="94"/>
-    </row>
-    <row r="26" spans="2:33" s="141" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O25" s="104"/>
+      <c r="P25" s="104"/>
+      <c r="V25" s="94"/>
+      <c r="W25" s="94"/>
+    </row>
+    <row r="26" spans="2:27" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="94"/>
       <c r="C26" s="142"/>
       <c r="D26" s="154"/>
       <c r="E26" s="143"/>
       <c r="F26" s="144"/>
-      <c r="G26" s="144"/>
-      <c r="H26" s="144"/>
-      <c r="I26" s="144"/>
-      <c r="J26" s="144"/>
-      <c r="K26" s="144"/>
-      <c r="L26" s="144"/>
-      <c r="R26" s="110"/>
-      <c r="S26" s="110"/>
-      <c r="T26" s="110"/>
-      <c r="U26" s="110"/>
-      <c r="AB26" s="94"/>
-      <c r="AC26" s="94"/>
-    </row>
-    <row r="27" spans="2:33" s="141" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L26" s="110"/>
+      <c r="M26" s="110"/>
+      <c r="N26" s="110"/>
+      <c r="O26" s="110"/>
+      <c r="V26" s="94"/>
+      <c r="W26" s="94"/>
+    </row>
+    <row r="27" spans="2:27" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="94"/>
       <c r="C27" s="142"/>
       <c r="D27" s="154"/>
       <c r="E27" s="143"/>
       <c r="F27" s="144"/>
-      <c r="G27" s="144"/>
-      <c r="H27" s="144"/>
-      <c r="I27" s="144"/>
-      <c r="J27" s="144"/>
-      <c r="K27" s="144"/>
-      <c r="L27" s="144"/>
-      <c r="R27" s="110"/>
-      <c r="S27" s="110"/>
-      <c r="T27" s="110"/>
-      <c r="U27" s="110"/>
-      <c r="AB27" s="94"/>
-      <c r="AC27" s="94"/>
-    </row>
-    <row r="28" spans="2:33" s="141" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="AB28" s="94"/>
-      <c r="AC28" s="94"/>
-      <c r="AD28" s="152"/>
-    </row>
-    <row r="29" spans="2:33" s="141" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="AC29" s="94"/>
-    </row>
-    <row r="30" spans="2:33" s="141" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L27" s="110"/>
+      <c r="M27" s="110"/>
+      <c r="N27" s="110"/>
+      <c r="O27" s="110"/>
+      <c r="V27" s="94"/>
+      <c r="W27" s="94"/>
+    </row>
+    <row r="28" spans="2:27" s="141" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="V28" s="94"/>
+      <c r="W28" s="94"/>
+      <c r="X28" s="152"/>
+    </row>
+    <row r="29" spans="2:27" s="141" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="W29" s="94"/>
+    </row>
+    <row r="30" spans="2:27" s="141" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="145"/>
       <c r="C30" s="90"/>
       <c r="D30" s="90"/>
       <c r="E30" s="143"/>
       <c r="F30" s="144"/>
-      <c r="G30" s="144"/>
-      <c r="H30" s="144"/>
-      <c r="I30" s="144"/>
-      <c r="J30" s="144"/>
-      <c r="K30" s="144"/>
-      <c r="L30" s="144"/>
+      <c r="L30" s="110"/>
+      <c r="M30" s="110"/>
+      <c r="N30" s="110"/>
+      <c r="O30" s="110"/>
+      <c r="P30" s="110"/>
+      <c r="Q30" s="110"/>
       <c r="R30" s="110"/>
       <c r="S30" s="110"/>
       <c r="T30" s="110"/>
@@ -8220,30 +7965,24 @@
       <c r="Y30" s="110"/>
       <c r="Z30" s="110"/>
       <c r="AA30" s="110"/>
-      <c r="AB30" s="110"/>
-      <c r="AC30" s="110"/>
-      <c r="AD30" s="110"/>
-      <c r="AE30" s="110"/>
-      <c r="AF30" s="110"/>
-      <c r="AG30" s="110"/>
-    </row>
-    <row r="31" spans="2:33" s="110" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="2:27" s="110" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="145"/>
       <c r="C31" s="90"/>
       <c r="D31" s="90"/>
       <c r="E31" s="143"/>
       <c r="F31" s="144"/>
-      <c r="G31" s="144"/>
-      <c r="H31" s="144"/>
-      <c r="I31" s="144"/>
-      <c r="J31" s="144"/>
-      <c r="K31" s="144"/>
-      <c r="L31" s="144"/>
-      <c r="M31" s="141"/>
-      <c r="N31" s="141"/>
-      <c r="O31" s="141"/>
-      <c r="P31" s="141"/>
-      <c r="Q31" s="141"/>
+      <c r="G31" s="141"/>
+      <c r="H31" s="141"/>
+      <c r="I31" s="141"/>
+      <c r="J31" s="141"/>
+      <c r="K31" s="141"/>
+      <c r="L31" s="88"/>
+      <c r="M31" s="88"/>
+      <c r="N31" s="88"/>
+      <c r="O31" s="88"/>
+      <c r="P31" s="88"/>
+      <c r="Q31" s="88"/>
       <c r="R31" s="88"/>
       <c r="S31" s="88"/>
       <c r="T31" s="88"/>
@@ -8254,318 +7993,108 @@
       <c r="Y31" s="88"/>
       <c r="Z31" s="88"/>
       <c r="AA31" s="88"/>
-      <c r="AB31" s="88"/>
-      <c r="AC31" s="88"/>
-      <c r="AD31" s="88"/>
-      <c r="AE31" s="88"/>
-      <c r="AF31" s="88"/>
-      <c r="AG31" s="88"/>
-    </row>
-    <row r="32" spans="2:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B32" s="145"/>
       <c r="C32" s="90"/>
       <c r="D32" s="142"/>
       <c r="E32" s="143"/>
       <c r="F32" s="144"/>
-      <c r="G32" s="144"/>
-      <c r="H32" s="144"/>
-      <c r="I32" s="144"/>
-      <c r="J32" s="144"/>
-      <c r="K32" s="144"/>
-      <c r="L32" s="144"/>
-      <c r="M32" s="141"/>
-      <c r="N32" s="141"/>
-      <c r="O32" s="141"/>
-      <c r="P32" s="141"/>
-      <c r="Q32" s="141"/>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="G32" s="141"/>
+      <c r="H32" s="141"/>
+      <c r="I32" s="141"/>
+      <c r="J32" s="141"/>
+      <c r="K32" s="141"/>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.25">
       <c r="E33" s="145"/>
       <c r="F33" s="106"/>
-      <c r="G33" s="106"/>
-      <c r="H33" s="106"/>
-      <c r="I33" s="106"/>
-      <c r="J33" s="106"/>
-      <c r="K33" s="106"/>
-      <c r="L33" s="106"/>
-      <c r="N33" s="164"/>
-      <c r="Q33" s="164"/>
-      <c r="AB33" s="90"/>
-      <c r="AC33" s="90"/>
-      <c r="AD33" s="151"/>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="H33" s="164"/>
+      <c r="K33" s="164"/>
+      <c r="V33" s="90"/>
+      <c r="W33" s="90"/>
+      <c r="X33" s="151"/>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.25">
       <c r="E34" s="145"/>
       <c r="F34" s="106"/>
-      <c r="G34" s="106"/>
-      <c r="H34" s="106"/>
-      <c r="I34" s="106"/>
-      <c r="J34" s="106"/>
-      <c r="K34" s="106"/>
-      <c r="L34" s="106"/>
-      <c r="N34" s="164"/>
-      <c r="Q34" s="164"/>
-      <c r="Y34" s="110"/>
-      <c r="AA34" s="110"/>
-      <c r="AB34" s="111"/>
-      <c r="AC34" s="111"/>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="H34" s="164"/>
+      <c r="K34" s="164"/>
+      <c r="S34" s="110"/>
+      <c r="U34" s="110"/>
+      <c r="V34" s="111"/>
+      <c r="W34" s="111"/>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.25">
       <c r="E35" s="145"/>
       <c r="F35" s="106"/>
-      <c r="G35" s="106"/>
-      <c r="H35" s="106"/>
-      <c r="I35" s="106"/>
-      <c r="J35" s="106"/>
-      <c r="K35" s="106"/>
-      <c r="L35" s="106"/>
-      <c r="N35" s="107"/>
-      <c r="Q35" s="164"/>
-    </row>
-    <row r="36" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="H35" s="107"/>
+      <c r="K35" s="164"/>
+    </row>
+    <row r="36" spans="2:24" x14ac:dyDescent="0.25">
       <c r="E36" s="145"/>
-      <c r="N36" s="107"/>
-      <c r="O36" s="106"/>
-      <c r="Q36" s="164"/>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="H36" s="107"/>
+      <c r="I36" s="106"/>
+      <c r="K36" s="164"/>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B37" s="104"/>
       <c r="C37" s="88" t="s">
         <v>97</v>
       </c>
-      <c r="N37" s="107"/>
-    </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="H37" s="107"/>
+    </row>
+    <row r="38" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B38" s="108"/>
       <c r="C38" s="88" t="s">
         <v>98</v>
       </c>
-      <c r="N38" s="107"/>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="N39" s="107"/>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="H38" s="107"/>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="H39" s="107"/>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.25">
       <c r="E42" s="21"/>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B44" s="88" t="s">
-        <v>39</v>
-      </c>
-      <c r="C44" s="88" t="s">
-        <v>32</v>
-      </c>
-      <c r="D44" s="88" t="s">
-        <v>33</v>
-      </c>
-      <c r="E44" s="88" t="s">
-        <v>105</v>
-      </c>
-      <c r="F44" s="88" t="s">
-        <v>140</v>
-      </c>
-      <c r="G44" s="88" t="s">
-        <v>140</v>
-      </c>
-      <c r="H44" s="88" t="s">
-        <v>140</v>
-      </c>
-      <c r="I44" s="88" t="s">
-        <v>140</v>
-      </c>
-      <c r="J44" s="88" t="s">
-        <v>140</v>
-      </c>
-      <c r="K44" s="88" t="s">
-        <v>140</v>
-      </c>
-      <c r="L44" s="88" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B45" s="94" t="s">
-        <v>87</v>
-      </c>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B45" s="94"/>
       <c r="C45" s="142"/>
       <c r="D45" s="90"/>
-      <c r="E45" s="143" t="s">
-        <v>189</v>
-      </c>
-      <c r="F45" s="144" t="s">
-        <v>201</v>
-      </c>
-      <c r="G45" s="144" t="s">
-        <v>201</v>
-      </c>
-      <c r="H45" s="144" t="s">
-        <v>201</v>
-      </c>
-      <c r="I45" s="144" t="s">
-        <v>201</v>
-      </c>
-      <c r="J45" s="144" t="s">
-        <v>201</v>
-      </c>
-      <c r="K45" s="144" t="s">
-        <v>201</v>
-      </c>
-      <c r="L45" s="144" t="s">
-        <v>201</v>
-      </c>
+      <c r="E45" s="143"/>
+      <c r="F45" s="144"/>
+      <c r="G45" s="141"/>
+      <c r="H45" s="141"/>
+      <c r="I45" s="141"/>
+      <c r="J45" s="141"/>
+      <c r="K45" s="141"/>
+      <c r="L45" s="141"/>
       <c r="M45" s="141"/>
       <c r="N45" s="141"/>
-      <c r="O45" s="141"/>
-      <c r="P45" s="141"/>
-      <c r="Q45" s="141"/>
-      <c r="R45" s="141"/>
-      <c r="S45" s="141"/>
-      <c r="T45" s="141"/>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B46" s="94" t="s">
-        <v>141</v>
-      </c>
-      <c r="C46" s="142" t="s">
-        <v>247</v>
-      </c>
-      <c r="D46" s="90" t="s">
-        <v>235</v>
-      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B46" s="94"/>
+      <c r="C46" s="142"/>
+      <c r="D46" s="90"/>
       <c r="E46" s="143"/>
-      <c r="F46" s="144">
-        <v>0.59</v>
-      </c>
-      <c r="G46" s="144"/>
-      <c r="H46" s="144"/>
-      <c r="I46" s="144"/>
-      <c r="J46" s="144"/>
-      <c r="K46" s="144"/>
-      <c r="L46" s="144"/>
+      <c r="F46" s="144"/>
+      <c r="G46" s="141"/>
+      <c r="H46" s="141"/>
+      <c r="I46" s="141"/>
+      <c r="J46" s="141"/>
+      <c r="K46" s="141"/>
+      <c r="L46" s="141"/>
       <c r="M46" s="141"/>
       <c r="N46" s="141"/>
-      <c r="O46" s="141"/>
-      <c r="P46" s="141"/>
-      <c r="Q46" s="141"/>
-      <c r="R46" s="141"/>
-      <c r="S46" s="141"/>
-      <c r="T46" s="141"/>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B47" s="88" t="s">
-        <v>141</v>
-      </c>
-      <c r="C47" s="88" t="s">
-        <v>248</v>
-      </c>
-      <c r="D47" s="88" t="s">
-        <v>235</v>
-      </c>
-      <c r="F47" s="88">
-        <v>0.41136476969163144</v>
-      </c>
-      <c r="G47" s="88">
-        <v>0.23585310113354352</v>
-      </c>
-      <c r="H47" s="88">
-        <v>7.3264515611810618E-2</v>
-      </c>
-      <c r="I47" s="88">
-        <v>1.9847450096360672E-2</v>
-      </c>
-      <c r="J47" s="88">
-        <v>5.1598550415568115E-3</v>
-      </c>
-      <c r="K47" s="88">
-        <v>1.3267245984926927E-3</v>
-      </c>
-      <c r="L47" s="88">
-        <v>3.4015961616990566E-4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B48" s="88" t="s">
-        <v>143</v>
-      </c>
-      <c r="C48" s="88" t="s">
-        <v>249</v>
-      </c>
-      <c r="D48" s="88" t="s">
-        <v>206</v>
-      </c>
-      <c r="F48" s="88">
-        <v>1</v>
-      </c>
-      <c r="G48" s="88">
-        <v>1</v>
-      </c>
-      <c r="H48" s="88">
-        <v>1</v>
-      </c>
-      <c r="I48" s="88">
-        <v>1</v>
-      </c>
-      <c r="J48" s="88">
-        <v>1</v>
-      </c>
-      <c r="K48" s="88">
-        <v>1</v>
-      </c>
-      <c r="L48" s="88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B49" s="88" t="s">
-        <v>151</v>
-      </c>
-      <c r="C49" s="88" t="s">
-        <v>46</v>
-      </c>
-      <c r="D49" s="88" t="s">
-        <v>151</v>
-      </c>
-      <c r="F49" s="88">
-        <v>1</v>
-      </c>
-      <c r="G49" s="88">
-        <v>1</v>
-      </c>
-      <c r="H49" s="88">
-        <v>1</v>
-      </c>
-      <c r="I49" s="88">
-        <v>1</v>
-      </c>
-      <c r="J49" s="88">
-        <v>1</v>
-      </c>
-      <c r="K49" s="88">
-        <v>1</v>
-      </c>
-      <c r="L49" s="88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="H50" s="178"/>
-      <c r="I50" s="179"/>
-    </row>
-    <row r="53" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="G53" s="145"/>
-      <c r="I53" s="145"/>
-    </row>
-    <row r="54" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="G54" s="145"/>
-    </row>
-    <row r="55" spans="2:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B55" s="94"/>
       <c r="C55" s="94"/>
       <c r="D55" s="94"/>
       <c r="E55" s="94"/>
       <c r="F55" s="94"/>
       <c r="G55" s="94"/>
-      <c r="H55" s="143"/>
+      <c r="H55" s="94"/>
       <c r="I55" s="94"/>
       <c r="J55" s="94"/>
       <c r="K55" s="94"/>
@@ -8585,20 +8114,14 @@
       <c r="Y55" s="94"/>
       <c r="Z55" s="94"/>
       <c r="AA55" s="94"/>
-      <c r="AB55" s="94"/>
-      <c r="AC55" s="94"/>
-      <c r="AD55" s="94"/>
-      <c r="AE55" s="94"/>
-      <c r="AF55" s="94"/>
-      <c r="AG55" s="94"/>
-    </row>
-    <row r="56" spans="2:33" s="94" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="2:27" s="94" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B56" s="88"/>
       <c r="C56" s="88"/>
       <c r="D56" s="88"/>
       <c r="E56" s="88"/>
       <c r="F56" s="145"/>
-      <c r="G56" s="145"/>
+      <c r="G56" s="88"/>
       <c r="H56" s="88"/>
       <c r="I56" s="88"/>
       <c r="J56" s="88"/>
@@ -8619,19 +8142,12 @@
       <c r="Y56" s="88"/>
       <c r="Z56" s="88"/>
       <c r="AA56" s="88"/>
-      <c r="AB56" s="88"/>
-      <c r="AC56" s="88"/>
-      <c r="AD56" s="88"/>
-      <c r="AE56" s="88"/>
-      <c r="AF56" s="88"/>
-      <c r="AG56" s="88"/>
-    </row>
-    <row r="58" spans="2:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="2:27" x14ac:dyDescent="0.25">
       <c r="F58" s="145"/>
     </row>
-    <row r="59" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:27" x14ac:dyDescent="0.25">
       <c r="F59" s="145"/>
-      <c r="H59" s="105"/>
     </row>
   </sheetData>
   <phoneticPr fontId="34" type="noConversion"/>
@@ -8878,40 +8394,40 @@
         <v>164</v>
       </c>
       <c r="I10" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J10" s="145" t="s">
         <v>208</v>
       </c>
-      <c r="K10" s="185">
+      <c r="K10" s="182">
         <v>3.3566276423652626E-2</v>
       </c>
-      <c r="L10" s="186"/>
+      <c r="L10" s="183"/>
       <c r="M10" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N10" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O10" s="145" t="s">
         <v>208</v>
       </c>
-      <c r="P10" s="185">
+      <c r="P10" s="182">
         <v>3.3566276423652626E-2</v>
       </c>
       <c r="R10" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S10" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T10" s="145" t="s">
         <v>208</v>
       </c>
-      <c r="U10" s="185">
+      <c r="U10" s="182">
         <v>3.3566276423652626E-2</v>
       </c>
     </row>
@@ -8935,40 +8451,40 @@
         <v>164</v>
       </c>
       <c r="I11" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J11" s="176" t="s">
         <v>209</v>
       </c>
-      <c r="K11" s="185">
+      <c r="K11" s="182">
         <v>3.3302706089073604E-2</v>
       </c>
-      <c r="L11" s="187"/>
+      <c r="L11" s="184"/>
       <c r="M11" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N11" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O11" s="176" t="s">
         <v>209</v>
       </c>
-      <c r="P11" s="185">
+      <c r="P11" s="182">
         <v>3.3302706089073604E-2</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S11" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T11" s="176" t="s">
         <v>209</v>
       </c>
-      <c r="U11" s="185">
+      <c r="U11" s="182">
         <v>3.3302706089073604E-2</v>
       </c>
     </row>
@@ -8981,40 +8497,40 @@
         <v>164</v>
       </c>
       <c r="I12" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J12" s="145" t="s">
         <v>210</v>
       </c>
-      <c r="K12" s="185">
+      <c r="K12" s="182">
         <v>3.3481814338032219E-2</v>
       </c>
-      <c r="L12" s="184"/>
+      <c r="L12" s="181"/>
       <c r="M12" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N12" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O12" s="145" t="s">
         <v>210</v>
       </c>
-      <c r="P12" s="185">
+      <c r="P12" s="182">
         <v>3.3481814338032219E-2</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S12" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T12" s="145" t="s">
         <v>210</v>
       </c>
-      <c r="U12" s="185">
+      <c r="U12" s="182">
         <v>3.3481814338032219E-2</v>
       </c>
     </row>
@@ -9023,40 +8539,40 @@
         <v>164</v>
       </c>
       <c r="I13" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J13" s="176" t="s">
         <v>211</v>
       </c>
-      <c r="K13" s="185">
+      <c r="K13" s="182">
         <v>3.3611381763990082E-2</v>
       </c>
-      <c r="L13" s="184"/>
+      <c r="L13" s="181"/>
       <c r="M13" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N13" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O13" s="176" t="s">
         <v>211</v>
       </c>
-      <c r="P13" s="185">
+      <c r="P13" s="182">
         <v>3.3611381763990082E-2</v>
       </c>
       <c r="R13" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S13" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T13" s="176" t="s">
         <v>211</v>
       </c>
-      <c r="U13" s="185">
+      <c r="U13" s="182">
         <v>3.3611381763990082E-2</v>
       </c>
     </row>
@@ -9065,40 +8581,40 @@
         <v>164</v>
       </c>
       <c r="I14" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J14" s="145" t="s">
         <v>212</v>
       </c>
-      <c r="K14" s="185">
+      <c r="K14" s="182">
         <v>3.4004820718610197E-2</v>
       </c>
-      <c r="L14" s="184"/>
+      <c r="L14" s="181"/>
       <c r="M14" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N14" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O14" s="145" t="s">
         <v>212</v>
       </c>
-      <c r="P14" s="185">
+      <c r="P14" s="182">
         <v>3.4004820718610197E-2</v>
       </c>
       <c r="R14" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S14" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T14" s="145" t="s">
         <v>212</v>
       </c>
-      <c r="U14" s="185">
+      <c r="U14" s="182">
         <v>3.4004820718610197E-2</v>
       </c>
     </row>
@@ -9107,40 +8623,40 @@
         <v>164</v>
       </c>
       <c r="I15" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J15" s="176" t="s">
         <v>213</v>
       </c>
-      <c r="K15" s="185">
+      <c r="K15" s="182">
         <v>3.4081384083392653E-2</v>
       </c>
-      <c r="L15" s="184"/>
+      <c r="L15" s="181"/>
       <c r="M15" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N15" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O15" s="176" t="s">
         <v>213</v>
       </c>
-      <c r="P15" s="185">
+      <c r="P15" s="182">
         <v>3.4081384083392653E-2</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S15" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T15" s="176" t="s">
         <v>213</v>
       </c>
-      <c r="U15" s="185">
+      <c r="U15" s="182">
         <v>3.4081384083392653E-2</v>
       </c>
     </row>
@@ -9149,40 +8665,40 @@
         <v>164</v>
       </c>
       <c r="I16" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J16" s="145" t="s">
         <v>214</v>
       </c>
-      <c r="K16" s="185">
+      <c r="K16" s="182">
         <v>3.3156795624830704E-2</v>
       </c>
-      <c r="L16" s="184"/>
+      <c r="L16" s="181"/>
       <c r="M16" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N16" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O16" s="145" t="s">
         <v>214</v>
       </c>
-      <c r="P16" s="185">
+      <c r="P16" s="182">
         <v>3.3156795624830704E-2</v>
       </c>
       <c r="R16" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S16" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T16" s="145" t="s">
         <v>214</v>
       </c>
-      <c r="U16" s="185">
+      <c r="U16" s="182">
         <v>3.3156795624830704E-2</v>
       </c>
     </row>
@@ -9191,40 +8707,40 @@
         <v>164</v>
       </c>
       <c r="I17" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J17" t="s">
         <v>215</v>
       </c>
-      <c r="K17" s="185">
+      <c r="K17" s="182">
         <v>3.6518070997817571E-2</v>
       </c>
-      <c r="L17" s="184"/>
+      <c r="L17" s="181"/>
       <c r="M17" t="s">
         <v>164</v>
       </c>
       <c r="N17" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O17" t="s">
         <v>215</v>
       </c>
-      <c r="P17" s="185">
+      <c r="P17" s="182">
         <v>3.6518070997817571E-2</v>
       </c>
       <c r="R17" t="s">
         <v>164</v>
       </c>
       <c r="S17" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T17" t="s">
         <v>215</v>
       </c>
-      <c r="U17" s="185">
+      <c r="U17" s="182">
         <v>3.6518070997817571E-2</v>
       </c>
     </row>
@@ -9233,40 +8749,40 @@
         <v>164</v>
       </c>
       <c r="I18" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J18" s="145" t="s">
         <v>216</v>
       </c>
-      <c r="K18" s="185">
+      <c r="K18" s="182">
         <v>4.7257353018906531E-2</v>
       </c>
-      <c r="L18" s="184"/>
+      <c r="L18" s="181"/>
       <c r="M18" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N18" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O18" s="145" t="s">
         <v>216</v>
       </c>
-      <c r="P18" s="185">
+      <c r="P18" s="182">
         <v>4.7257353018906531E-2</v>
       </c>
       <c r="R18" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S18" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T18" s="145" t="s">
         <v>216</v>
       </c>
-      <c r="U18" s="185">
+      <c r="U18" s="182">
         <v>4.7257353018906531E-2</v>
       </c>
     </row>
@@ -9275,40 +8791,40 @@
         <v>164</v>
       </c>
       <c r="I19" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J19" t="s">
         <v>217</v>
       </c>
-      <c r="K19" s="185">
+      <c r="K19" s="182">
         <v>5.6756578785819259E-2</v>
       </c>
-      <c r="L19" s="184"/>
+      <c r="L19" s="181"/>
       <c r="M19" t="s">
         <v>164</v>
       </c>
       <c r="N19" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O19" t="s">
         <v>217</v>
       </c>
-      <c r="P19" s="185">
+      <c r="P19" s="182">
         <v>5.6756578785819259E-2</v>
       </c>
       <c r="R19" t="s">
         <v>164</v>
       </c>
       <c r="S19" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T19" t="s">
         <v>217</v>
       </c>
-      <c r="U19" s="185">
+      <c r="U19" s="182">
         <v>5.6756578785819259E-2</v>
       </c>
     </row>
@@ -9317,40 +8833,40 @@
         <v>164</v>
       </c>
       <c r="I20" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J20" t="s">
         <v>218</v>
       </c>
-      <c r="K20" s="185">
+      <c r="K20" s="182">
         <v>5.5715023853427123E-2</v>
       </c>
-      <c r="L20" s="184"/>
+      <c r="L20" s="181"/>
       <c r="M20" t="s">
         <v>164</v>
       </c>
       <c r="N20" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O20" t="s">
         <v>218</v>
       </c>
-      <c r="P20" s="185">
+      <c r="P20" s="182">
         <v>5.5715023853427123E-2</v>
       </c>
       <c r="R20" t="s">
         <v>164</v>
       </c>
       <c r="S20" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T20" t="s">
         <v>218</v>
       </c>
-      <c r="U20" s="185">
+      <c r="U20" s="182">
         <v>5.5715023853427123E-2</v>
       </c>
     </row>
@@ -9359,40 +8875,40 @@
         <v>164</v>
       </c>
       <c r="I21" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J21" t="s">
         <v>219</v>
       </c>
-      <c r="K21" s="185">
+      <c r="K21" s="182">
         <v>5.6345483069498978E-2</v>
       </c>
-      <c r="L21" s="184"/>
+      <c r="L21" s="181"/>
       <c r="M21" t="s">
         <v>164</v>
       </c>
       <c r="N21" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O21" t="s">
         <v>219</v>
       </c>
-      <c r="P21" s="185">
+      <c r="P21" s="182">
         <v>5.6345483069498978E-2</v>
       </c>
       <c r="R21" t="s">
         <v>164</v>
       </c>
       <c r="S21" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T21" t="s">
         <v>219</v>
       </c>
-      <c r="U21" s="185">
+      <c r="U21" s="182">
         <v>5.6345483069498978E-2</v>
       </c>
     </row>
@@ -9401,40 +8917,40 @@
         <v>164</v>
       </c>
       <c r="I22" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J22" t="s">
         <v>220</v>
       </c>
-      <c r="K22" s="185">
+      <c r="K22" s="182">
         <v>4.8662133827205516E-2</v>
       </c>
-      <c r="L22" s="184"/>
+      <c r="L22" s="181"/>
       <c r="M22" t="s">
         <v>164</v>
       </c>
       <c r="N22" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O22" t="s">
         <v>220</v>
       </c>
-      <c r="P22" s="185">
+      <c r="P22" s="182">
         <v>4.8662133827205516E-2</v>
       </c>
       <c r="R22" t="s">
         <v>164</v>
       </c>
       <c r="S22" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T22" t="s">
         <v>220</v>
       </c>
-      <c r="U22" s="185">
+      <c r="U22" s="182">
         <v>4.8662133827205516E-2</v>
       </c>
     </row>
@@ -9443,40 +8959,40 @@
         <v>164</v>
       </c>
       <c r="I23" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J23" t="s">
         <v>221</v>
       </c>
-      <c r="K23" s="185">
+      <c r="K23" s="182">
         <v>5.0293526586567008E-2</v>
       </c>
-      <c r="L23" s="184"/>
+      <c r="L23" s="181"/>
       <c r="M23" t="s">
         <v>164</v>
       </c>
       <c r="N23" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O23" t="s">
         <v>221</v>
       </c>
-      <c r="P23" s="185">
+      <c r="P23" s="182">
         <v>5.0293526586567008E-2</v>
       </c>
       <c r="R23" t="s">
         <v>164</v>
       </c>
       <c r="S23" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T23" t="s">
         <v>221</v>
       </c>
-      <c r="U23" s="185">
+      <c r="U23" s="182">
         <v>5.0293526586567008E-2</v>
       </c>
     </row>
@@ -9485,40 +9001,40 @@
         <v>164</v>
       </c>
       <c r="I24" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J24" t="s">
         <v>222</v>
       </c>
-      <c r="K24" s="185">
+      <c r="K24" s="182">
         <v>5.2523087098903048E-2</v>
       </c>
-      <c r="L24" s="184"/>
+      <c r="L24" s="181"/>
       <c r="M24" t="s">
         <v>164</v>
       </c>
       <c r="N24" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O24" t="s">
         <v>222</v>
       </c>
-      <c r="P24" s="185">
+      <c r="P24" s="182">
         <v>5.2523087098903048E-2</v>
       </c>
       <c r="R24" t="s">
         <v>164</v>
       </c>
       <c r="S24" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T24" t="s">
         <v>222</v>
       </c>
-      <c r="U24" s="185">
+      <c r="U24" s="182">
         <v>5.2523087098903048E-2</v>
       </c>
     </row>
@@ -9527,40 +9043,40 @@
         <v>164</v>
       </c>
       <c r="I25" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J25" t="s">
         <v>223</v>
       </c>
-      <c r="K25" s="185">
+      <c r="K25" s="182">
         <v>5.4966761848993004E-2</v>
       </c>
-      <c r="L25" s="184"/>
+      <c r="L25" s="181"/>
       <c r="M25" t="s">
         <v>164</v>
       </c>
       <c r="N25" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O25" t="s">
         <v>223</v>
       </c>
-      <c r="P25" s="185">
+      <c r="P25" s="182">
         <v>5.4966761848993004E-2</v>
       </c>
       <c r="R25" t="s">
         <v>164</v>
       </c>
       <c r="S25" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T25" t="s">
         <v>223</v>
       </c>
-      <c r="U25" s="185">
+      <c r="U25" s="182">
         <v>5.4966761848993004E-2</v>
       </c>
     </row>
@@ -9570,40 +9086,40 @@
         <v>164</v>
       </c>
       <c r="I26" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J26" t="s">
         <v>224</v>
       </c>
-      <c r="K26" s="185">
+      <c r="K26" s="182">
         <v>5.3016988893511453E-2</v>
       </c>
-      <c r="L26" s="184"/>
+      <c r="L26" s="181"/>
       <c r="M26" t="s">
         <v>164</v>
       </c>
       <c r="N26" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O26" t="s">
         <v>224</v>
       </c>
-      <c r="P26" s="185">
+      <c r="P26" s="182">
         <v>5.3016988893511453E-2</v>
       </c>
       <c r="R26" t="s">
         <v>164</v>
       </c>
       <c r="S26" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T26" t="s">
         <v>224</v>
       </c>
-      <c r="U26" s="185">
+      <c r="U26" s="182">
         <v>5.3016988893511453E-2</v>
       </c>
     </row>
@@ -9614,40 +9130,40 @@
         <v>164</v>
       </c>
       <c r="I27" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J27" t="s">
         <v>225</v>
       </c>
-      <c r="K27" s="185">
+      <c r="K27" s="182">
         <v>4.4273060594597062E-2</v>
       </c>
-      <c r="L27" s="184"/>
+      <c r="L27" s="181"/>
       <c r="M27" t="s">
         <v>164</v>
       </c>
       <c r="N27" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O27" t="s">
         <v>225</v>
       </c>
-      <c r="P27" s="185">
+      <c r="P27" s="182">
         <v>4.4273060594597062E-2</v>
       </c>
       <c r="R27" t="s">
         <v>164</v>
       </c>
       <c r="S27" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T27" t="s">
         <v>225</v>
       </c>
-      <c r="U27" s="185">
+      <c r="U27" s="182">
         <v>4.4273060594597062E-2</v>
       </c>
     </row>
@@ -9659,40 +9175,40 @@
         <v>164</v>
       </c>
       <c r="I28" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J28" t="s">
         <v>226</v>
       </c>
-      <c r="K28" s="185">
+      <c r="K28" s="182">
         <v>3.6258449498494133E-2</v>
       </c>
-      <c r="L28" s="184"/>
+      <c r="L28" s="181"/>
       <c r="M28" t="s">
         <v>164</v>
       </c>
       <c r="N28" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O28" t="s">
         <v>226</v>
       </c>
-      <c r="P28" s="185">
+      <c r="P28" s="182">
         <v>3.6258449498494133E-2</v>
       </c>
       <c r="R28" t="s">
         <v>164</v>
       </c>
       <c r="S28" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T28" t="s">
         <v>226</v>
       </c>
-      <c r="U28" s="185">
+      <c r="U28" s="182">
         <v>3.6258449498494133E-2</v>
       </c>
     </row>
@@ -9704,40 +9220,40 @@
         <v>164</v>
       </c>
       <c r="I29" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J29" t="s">
         <v>227</v>
       </c>
-      <c r="K29" s="185">
+      <c r="K29" s="182">
         <v>3.6040655779430726E-2</v>
       </c>
-      <c r="L29" s="184"/>
+      <c r="L29" s="181"/>
       <c r="M29" t="s">
         <v>164</v>
       </c>
       <c r="N29" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O29" t="s">
         <v>227</v>
       </c>
-      <c r="P29" s="185">
+      <c r="P29" s="182">
         <v>3.6040655779430726E-2</v>
       </c>
       <c r="R29" t="s">
         <v>164</v>
       </c>
       <c r="S29" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T29" t="s">
         <v>227</v>
       </c>
-      <c r="U29" s="185">
+      <c r="U29" s="182">
         <v>3.6040655779430726E-2</v>
       </c>
     </row>
@@ -9746,40 +9262,40 @@
         <v>164</v>
       </c>
       <c r="I30" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J30" s="145" t="s">
         <v>228</v>
       </c>
-      <c r="K30" s="185">
+      <c r="K30" s="182">
         <v>3.5097781406108856E-2</v>
       </c>
-      <c r="L30" s="184"/>
+      <c r="L30" s="181"/>
       <c r="M30" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N30" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O30" s="145" t="s">
         <v>228</v>
       </c>
-      <c r="P30" s="185">
+      <c r="P30" s="182">
         <v>3.5097781406108856E-2</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S30" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T30" s="145" t="s">
         <v>228</v>
       </c>
-      <c r="U30" s="185">
+      <c r="U30" s="182">
         <v>3.5097781406108856E-2</v>
       </c>
     </row>
@@ -9788,40 +9304,40 @@
         <v>164</v>
       </c>
       <c r="I31" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J31" s="176" t="s">
         <v>229</v>
       </c>
-      <c r="K31" s="185">
+      <c r="K31" s="182">
         <v>3.482493578674286E-2</v>
       </c>
-      <c r="L31" s="184"/>
+      <c r="L31" s="181"/>
       <c r="M31" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N31" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O31" s="176" t="s">
         <v>229</v>
       </c>
-      <c r="P31" s="185">
+      <c r="P31" s="182">
         <v>3.482493578674286E-2</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S31" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T31" s="176" t="s">
         <v>229</v>
       </c>
-      <c r="U31" s="185">
+      <c r="U31" s="182">
         <v>3.482493578674286E-2</v>
       </c>
     </row>
@@ -9831,40 +9347,40 @@
         <v>164</v>
       </c>
       <c r="I32" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J32" s="145" t="s">
         <v>230</v>
       </c>
-      <c r="K32" s="185">
+      <c r="K32" s="182">
         <v>3.2564766705734945E-2</v>
       </c>
-      <c r="L32" s="184"/>
+      <c r="L32" s="181"/>
       <c r="M32" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N32" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O32" s="145" t="s">
         <v>230</v>
       </c>
-      <c r="P32" s="185">
+      <c r="P32" s="182">
         <v>3.2564766705734945E-2</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S32" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T32" s="145" t="s">
         <v>230</v>
       </c>
-      <c r="U32" s="185">
+      <c r="U32" s="182">
         <v>3.2564766705734945E-2</v>
       </c>
     </row>
@@ -9875,40 +9391,40 @@
         <v>164</v>
       </c>
       <c r="I33" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J33" s="176" t="s">
         <v>231</v>
       </c>
-      <c r="K33" s="185">
+      <c r="K33" s="182">
         <v>3.3680163206659841E-2</v>
       </c>
-      <c r="L33" s="184"/>
+      <c r="L33" s="181"/>
       <c r="M33" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N33" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O33" s="176" t="s">
         <v>231</v>
       </c>
-      <c r="P33" s="185">
+      <c r="P33" s="182">
         <v>3.3680163206659841E-2</v>
       </c>
       <c r="R33" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S33" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T33" s="176" t="s">
         <v>231</v>
       </c>
-      <c r="U33" s="185">
+      <c r="U33" s="182">
         <v>3.3680163206659841E-2</v>
       </c>
     </row>
@@ -9918,39 +9434,39 @@
         <v>164</v>
       </c>
       <c r="I34" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J34" t="s">
         <v>165</v>
       </c>
-      <c r="K34" s="185">
+      <c r="K34" s="182">
         <v>3.0835149280259575E-2</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N34" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O34" t="s">
         <v>165</v>
       </c>
-      <c r="P34" s="185">
+      <c r="P34" s="182">
         <v>3.0835149280259575E-2</v>
       </c>
       <c r="R34" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S34" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T34" t="s">
         <v>165</v>
       </c>
-      <c r="U34" s="185">
+      <c r="U34" s="182">
         <v>3.0835149280259575E-2</v>
       </c>
     </row>
@@ -9959,39 +9475,39 @@
         <v>164</v>
       </c>
       <c r="I35" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J35" t="s">
         <v>166</v>
       </c>
-      <c r="K35" s="185">
+      <c r="K35" s="182">
         <v>3.1306102192535441E-2</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N35" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O35" t="s">
         <v>166</v>
       </c>
-      <c r="P35" s="185">
+      <c r="P35" s="182">
         <v>3.1306102192535441E-2</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S35" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T35" t="s">
         <v>166</v>
       </c>
-      <c r="U35" s="185">
+      <c r="U35" s="182">
         <v>3.1306102192535441E-2</v>
       </c>
     </row>
@@ -10004,39 +9520,39 @@
         <v>164</v>
       </c>
       <c r="I36" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J36" t="s">
         <v>167</v>
       </c>
-      <c r="K36" s="185">
+      <c r="K36" s="182">
         <v>3.0732055812390149E-2</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N36" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O36" t="s">
         <v>167</v>
       </c>
-      <c r="P36" s="185">
+      <c r="P36" s="182">
         <v>3.0732055812390149E-2</v>
       </c>
       <c r="R36" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S36" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T36" t="s">
         <v>167</v>
       </c>
-      <c r="U36" s="185">
+      <c r="U36" s="182">
         <v>3.0732055812390149E-2</v>
       </c>
     </row>
@@ -10049,39 +9565,39 @@
         <v>164</v>
       </c>
       <c r="I37" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J37" t="s">
         <v>168</v>
       </c>
-      <c r="K37" s="185">
+      <c r="K37" s="182">
         <v>3.1026498894933252E-2</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N37" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O37" t="s">
         <v>168</v>
       </c>
-      <c r="P37" s="185">
+      <c r="P37" s="182">
         <v>3.1026498894933252E-2</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S37" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T37" t="s">
         <v>168</v>
       </c>
-      <c r="U37" s="185">
+      <c r="U37" s="182">
         <v>3.1026498894933252E-2</v>
       </c>
     </row>
@@ -10090,39 +9606,39 @@
         <v>164</v>
       </c>
       <c r="I38" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J38" t="s">
         <v>169</v>
       </c>
-      <c r="K38" s="185">
+      <c r="K38" s="182">
         <v>3.1056840848101456E-2</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N38" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O38" t="s">
         <v>169</v>
       </c>
-      <c r="P38" s="185">
+      <c r="P38" s="182">
         <v>3.1056840848101456E-2</v>
       </c>
       <c r="R38" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S38" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T38" t="s">
         <v>169</v>
       </c>
-      <c r="U38" s="185">
+      <c r="U38" s="182">
         <v>3.1056840848101456E-2</v>
       </c>
     </row>
@@ -10131,39 +9647,39 @@
         <v>164</v>
       </c>
       <c r="I39" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J39" t="s">
         <v>170</v>
       </c>
-      <c r="K39" s="185">
+      <c r="K39" s="182">
         <v>3.1761574865503496E-2</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N39" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O39" t="s">
         <v>170</v>
       </c>
-      <c r="P39" s="185">
+      <c r="P39" s="182">
         <v>3.1761574865503496E-2</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S39" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T39" t="s">
         <v>170</v>
       </c>
-      <c r="U39" s="185">
+      <c r="U39" s="182">
         <v>3.1761574865503496E-2</v>
       </c>
     </row>
@@ -10172,39 +9688,39 @@
         <v>164</v>
       </c>
       <c r="I40" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J40" t="s">
         <v>171</v>
       </c>
-      <c r="K40" s="185">
+      <c r="K40" s="182">
         <v>3.2141299558210122E-2</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N40" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O40" t="s">
         <v>171</v>
       </c>
-      <c r="P40" s="185">
+      <c r="P40" s="182">
         <v>3.2141299558210122E-2</v>
       </c>
       <c r="R40" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S40" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T40" t="s">
         <v>171</v>
       </c>
-      <c r="U40" s="185">
+      <c r="U40" s="182">
         <v>3.2141299558210122E-2</v>
       </c>
     </row>
@@ -10213,39 +9729,39 @@
         <v>164</v>
       </c>
       <c r="I41" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J41" t="s">
         <v>172</v>
       </c>
-      <c r="K41" s="185">
+      <c r="K41" s="182">
         <v>3.5213642686520726E-2</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N41" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O41" t="s">
         <v>172</v>
       </c>
-      <c r="P41" s="185">
+      <c r="P41" s="182">
         <v>3.5213642686520726E-2</v>
       </c>
       <c r="R41" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S41" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T41" t="s">
         <v>172</v>
       </c>
-      <c r="U41" s="185">
+      <c r="U41" s="182">
         <v>3.5213642686520726E-2</v>
       </c>
     </row>
@@ -10254,39 +9770,39 @@
         <v>164</v>
       </c>
       <c r="I42" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J42" t="s">
         <v>173</v>
       </c>
-      <c r="K42" s="185">
+      <c r="K42" s="182">
         <v>5.1117433203485711E-2</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N42" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O42" t="s">
         <v>173</v>
       </c>
-      <c r="P42" s="185">
+      <c r="P42" s="182">
         <v>5.1117433203485711E-2</v>
       </c>
       <c r="R42" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S42" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T42" t="s">
         <v>173</v>
       </c>
-      <c r="U42" s="185">
+      <c r="U42" s="182">
         <v>5.1117433203485711E-2</v>
       </c>
     </row>
@@ -10295,39 +9811,39 @@
         <v>164</v>
       </c>
       <c r="I43" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J43" t="s">
         <v>174</v>
       </c>
-      <c r="K43" s="185">
+      <c r="K43" s="182">
         <v>6.2773677380098022E-2</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N43" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O43" t="s">
         <v>174</v>
       </c>
-      <c r="P43" s="185">
+      <c r="P43" s="182">
         <v>6.2773677380098022E-2</v>
       </c>
       <c r="R43" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S43" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T43" t="s">
         <v>174</v>
       </c>
-      <c r="U43" s="185">
+      <c r="U43" s="182">
         <v>6.2773677380098022E-2</v>
       </c>
     </row>
@@ -10336,39 +9852,39 @@
         <v>164</v>
       </c>
       <c r="I44" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J44" t="s">
         <v>175</v>
       </c>
-      <c r="K44" s="185">
+      <c r="K44" s="182">
         <v>6.1766758236552227E-2</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N44" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O44" t="s">
         <v>175</v>
       </c>
-      <c r="P44" s="185">
+      <c r="P44" s="182">
         <v>6.1766758236552227E-2</v>
       </c>
       <c r="R44" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S44" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T44" t="s">
         <v>175</v>
       </c>
-      <c r="U44" s="185">
+      <c r="U44" s="182">
         <v>6.1766758236552227E-2</v>
       </c>
     </row>
@@ -10377,39 +9893,39 @@
         <v>164</v>
       </c>
       <c r="I45" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J45" t="s">
         <v>176</v>
       </c>
-      <c r="K45" s="185">
+      <c r="K45" s="182">
         <v>6.4177423190962854E-2</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N45" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O45" t="s">
         <v>176</v>
       </c>
-      <c r="P45" s="185">
+      <c r="P45" s="182">
         <v>6.4177423190962854E-2</v>
       </c>
       <c r="R45" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S45" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T45" t="s">
         <v>176</v>
       </c>
-      <c r="U45" s="185">
+      <c r="U45" s="182">
         <v>6.4177423190962854E-2</v>
       </c>
     </row>
@@ -10418,39 +9934,39 @@
         <v>164</v>
       </c>
       <c r="I46" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J46" t="s">
         <v>177</v>
       </c>
-      <c r="K46" s="185">
+      <c r="K46" s="182">
         <v>5.0829723942040425E-2</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N46" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O46" t="s">
         <v>177</v>
       </c>
-      <c r="P46" s="185">
+      <c r="P46" s="182">
         <v>5.0829723942040425E-2</v>
       </c>
       <c r="R46" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S46" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T46" t="s">
         <v>177</v>
       </c>
-      <c r="U46" s="185">
+      <c r="U46" s="182">
         <v>5.0829723942040425E-2</v>
       </c>
     </row>
@@ -10459,39 +9975,39 @@
         <v>164</v>
       </c>
       <c r="I47" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J47" t="s">
         <v>178</v>
       </c>
-      <c r="K47" s="185">
+      <c r="K47" s="182">
         <v>5.4268458827148723E-2</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N47" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O47" t="s">
         <v>178</v>
       </c>
-      <c r="P47" s="185">
+      <c r="P47" s="182">
         <v>5.4268458827148723E-2</v>
       </c>
       <c r="R47" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S47" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T47" t="s">
         <v>178</v>
       </c>
-      <c r="U47" s="185">
+      <c r="U47" s="182">
         <v>5.4268458827148723E-2</v>
       </c>
     </row>
@@ -10500,39 +10016,39 @@
         <v>164</v>
       </c>
       <c r="I48" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J48" t="s">
         <v>179</v>
       </c>
-      <c r="K48" s="185">
+      <c r="K48" s="182">
         <v>5.9589636409466136E-2</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N48" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O48" t="s">
         <v>179</v>
       </c>
-      <c r="P48" s="185">
+      <c r="P48" s="182">
         <v>5.9589636409466136E-2</v>
       </c>
       <c r="R48" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S48" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T48" t="s">
         <v>179</v>
       </c>
-      <c r="U48" s="185">
+      <c r="U48" s="182">
         <v>5.9589636409466136E-2</v>
       </c>
     </row>
@@ -10541,39 +10057,39 @@
         <v>164</v>
       </c>
       <c r="I49" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J49" t="s">
         <v>180</v>
       </c>
-      <c r="K49" s="185">
+      <c r="K49" s="182">
         <v>5.9904363990350699E-2</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N49" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O49" t="s">
         <v>180</v>
       </c>
-      <c r="P49" s="185">
+      <c r="P49" s="182">
         <v>5.9904363990350699E-2</v>
       </c>
       <c r="R49" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S49" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T49" t="s">
         <v>180</v>
       </c>
-      <c r="U49" s="185">
+      <c r="U49" s="182">
         <v>5.9904363990350699E-2</v>
       </c>
     </row>
@@ -10582,39 +10098,39 @@
         <v>164</v>
       </c>
       <c r="I50" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J50" t="s">
         <v>181</v>
       </c>
-      <c r="K50" s="185">
+      <c r="K50" s="182">
         <v>5.4602121019645386E-2</v>
       </c>
       <c r="M50" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N50" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O50" t="s">
         <v>181</v>
       </c>
-      <c r="P50" s="185">
+      <c r="P50" s="182">
         <v>5.4602121019645386E-2</v>
       </c>
       <c r="R50" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S50" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T50" t="s">
         <v>181</v>
       </c>
-      <c r="U50" s="185">
+      <c r="U50" s="182">
         <v>5.4602121019645386E-2</v>
       </c>
     </row>
@@ -10623,39 +10139,39 @@
         <v>164</v>
       </c>
       <c r="I51" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J51" t="s">
         <v>182</v>
       </c>
-      <c r="K51" s="185">
+      <c r="K51" s="182">
         <v>4.095098396869809E-2</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N51" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O51" t="s">
         <v>182</v>
       </c>
-      <c r="P51" s="185">
+      <c r="P51" s="182">
         <v>4.095098396869809E-2</v>
       </c>
       <c r="R51" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S51" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T51" t="s">
         <v>182</v>
       </c>
-      <c r="U51" s="185">
+      <c r="U51" s="182">
         <v>4.095098396869809E-2</v>
       </c>
     </row>
@@ -10664,39 +10180,39 @@
         <v>164</v>
       </c>
       <c r="I52" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J52" t="s">
         <v>183</v>
       </c>
-      <c r="K52" s="185">
+      <c r="K52" s="182">
         <v>3.2728922255458537E-2</v>
       </c>
       <c r="M52" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N52" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O52" t="s">
         <v>183</v>
       </c>
-      <c r="P52" s="185">
+      <c r="P52" s="182">
         <v>3.2728922255458537E-2</v>
       </c>
       <c r="R52" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S52" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T52" t="s">
         <v>183</v>
       </c>
-      <c r="U52" s="185">
+      <c r="U52" s="182">
         <v>3.2728922255458537E-2</v>
       </c>
     </row>
@@ -10705,39 +10221,39 @@
         <v>164</v>
       </c>
       <c r="I53" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J53" t="s">
         <v>184</v>
       </c>
-      <c r="K53" s="185">
+      <c r="K53" s="182">
         <v>3.1731181617130018E-2</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N53" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O53" t="s">
         <v>184</v>
       </c>
-      <c r="P53" s="185">
+      <c r="P53" s="182">
         <v>3.1731181617130018E-2</v>
       </c>
       <c r="R53" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S53" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T53" t="s">
         <v>184</v>
       </c>
-      <c r="U53" s="185">
+      <c r="U53" s="182">
         <v>3.1731181617130018E-2</v>
       </c>
     </row>
@@ -10746,39 +10262,39 @@
         <v>164</v>
       </c>
       <c r="I54" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J54" t="s">
         <v>185</v>
       </c>
-      <c r="K54" s="185">
+      <c r="K54" s="182">
         <v>3.0924439128636003E-2</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N54" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O54" t="s">
         <v>185</v>
       </c>
-      <c r="P54" s="185">
+      <c r="P54" s="182">
         <v>3.0924439128636003E-2</v>
       </c>
       <c r="R54" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S54" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T54" t="s">
         <v>185</v>
       </c>
-      <c r="U54" s="185">
+      <c r="U54" s="182">
         <v>3.0924439128636003E-2</v>
       </c>
     </row>
@@ -10787,39 +10303,39 @@
         <v>164</v>
       </c>
       <c r="I55" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J55" t="s">
         <v>186</v>
       </c>
-      <c r="K55" s="185">
+      <c r="K55" s="182">
         <v>3.0529213441903326E-2</v>
       </c>
       <c r="M55" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N55" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O55" t="s">
         <v>186</v>
       </c>
-      <c r="P55" s="185">
+      <c r="P55" s="182">
         <v>3.0529213441903326E-2</v>
       </c>
       <c r="R55" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S55" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T55" t="s">
         <v>186</v>
       </c>
-      <c r="U55" s="185">
+      <c r="U55" s="182">
         <v>3.0529213441903326E-2</v>
       </c>
     </row>
@@ -10828,39 +10344,39 @@
         <v>164</v>
       </c>
       <c r="I56" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J56" t="s">
         <v>187</v>
       </c>
-      <c r="K56" s="185">
+      <c r="K56" s="182">
         <v>2.9792391830107463E-2</v>
       </c>
       <c r="M56" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N56" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O56" t="s">
         <v>187</v>
       </c>
-      <c r="P56" s="185">
+      <c r="P56" s="182">
         <v>2.9792391830107463E-2</v>
       </c>
       <c r="R56" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S56" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T56" t="s">
         <v>187</v>
       </c>
-      <c r="U56" s="185">
+      <c r="U56" s="182">
         <v>2.9792391830107463E-2</v>
       </c>
     </row>
@@ -10869,39 +10385,39 @@
         <v>164</v>
       </c>
       <c r="I57" s="1" t="str">
-        <f>DemTechs_INDF!Z$6</f>
+        <f>DemTechs_INDF!T$6</f>
         <v>MANELC</v>
       </c>
       <c r="J57" t="s">
         <v>188</v>
       </c>
-      <c r="K57" s="185">
+      <c r="K57" s="182">
         <v>3.0240107419862172E-2</v>
       </c>
       <c r="M57" s="1" t="s">
         <v>164</v>
       </c>
       <c r="N57" s="1" t="str">
-        <f>DemTechs_INDF!Z$5</f>
+        <f>DemTechs_INDF!T$5</f>
         <v>MANHEAT</v>
       </c>
       <c r="O57" t="s">
         <v>188</v>
       </c>
-      <c r="P57" s="185">
+      <c r="P57" s="182">
         <v>3.0240107419862172E-2</v>
       </c>
       <c r="R57" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S57" s="1" t="str">
-        <f>DemTechs_INDF!Z$8</f>
+        <f>DemTechs_INDF!T$8</f>
         <v>CEMENTHEAT</v>
       </c>
       <c r="T57" t="s">
         <v>188</v>
       </c>
-      <c r="U57" s="185">
+      <c r="U57" s="182">
         <v>3.0240107419862172E-2</v>
       </c>
     </row>
@@ -10909,7 +10425,7 @@
       <c r="H58" s="1"/>
       <c r="I58" s="137"/>
       <c r="J58" s="137"/>
-      <c r="K58" s="181"/>
+      <c r="K58" s="178"/>
     </row>
     <row r="59" spans="8:21" x14ac:dyDescent="0.25">
       <c r="K59" s="137"/>
@@ -11013,7 +10529,7 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" s="128" t="str">
-        <f>DemTechs_INDF!Z7</f>
+        <f>DemTechs_INDF!T7</f>
         <v>MANCO2</v>
       </c>
       <c r="C9" s="129">
